--- a/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
+++ b/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
@@ -19,7 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ABOUT" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'STUDY QUEUE'!$A$1:$L$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'STUDY QUEUE'!$A$1:$L$132</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ROADMAP'!$A$1:$U$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TOPIC DETAIL'!$A$1:$Q$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'WRITTEN BY TOPIC'!$A$1:$H$361</definedName>
@@ -1570,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1784,55 +1784,108 @@
     <row r="20">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>Study sessions</t>
-        </is>
-      </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>docs/study/TOPIC_01_STATUTORY_SURVEYS_AND_CLASS.md</t>
-        </is>
-      </c>
+          <t>Topic packs pinned</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="n"/>
       <c r="C20" s="26" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
-        <is>
-          <t>Sessions vs pack</t>
-        </is>
-      </c>
+      <c r="A21" s="26" t="inlineStr"/>
       <c r="B21" s="26" t="inlineStr">
         <is>
-          <t>CURRENT</t>
-        </is>
-      </c>
-      <c r="C21" s="26" t="n"/>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>docs/study/TOPIC_01_STATUTORY_SURVEYS_AND_CLASS.md  (CURRENT)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
-        <is>
-          <t>Checked routes</t>
-        </is>
-      </c>
+      <c r="A22" s="26" t="inlineStr"/>
       <c r="B22" s="26" t="inlineStr">
         <is>
-          <t>407, of which 0 could not be resolved</t>
-        </is>
-      </c>
-      <c r="C22" s="26" t="n"/>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>docs/study/TOPIC_03_MARINE_INSURANCE_COMMERCIAL_LAW.md  (CURRENT)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="26" t="inlineStr"/>
-      <c r="B23" s="26" t="n"/>
-      <c r="C23" s="26" t="n"/>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>docs/study/TOPIC_02_HUMAN_ELEMENT_ISM_MANAGEMENT.md  (CURRENT)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
-        <is>
-          <t>Every number in this workbook is derived from a governed repository artefact. Nothing here is typed by hand, and the renderer classifies nothing itself. Every hyperlink was resolved against the repository at generation time: a route that did not exist renders as NOT YET AVAILABLE rather than as a link into nothing.</t>
-        </is>
-      </c>
+      <c r="A24" s="26" t="inlineStr"/>
       <c r="B24" s="26" t="n"/>
       <c r="C24" s="26" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>Study sessions</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>15 session(s) across 3 topic pack(s)</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>Sessions vs pack</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>Checked routes</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>466, of which 0 could not be resolved</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr"/>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>Every number in this workbook is derived from a governed repository artefact. Nothing here is typed by hand, and the renderer classifies nothing itself. Every hyperlink was resolved against the repository at generation time: a route that did not exist renders as NOT YET AVAILABLE rather than as a link into nothing.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1845,7 +1898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1935,7 +1988,7 @@
       </c>
       <c r="C2" s="22" t="inlineStr">
         <is>
-          <t>S1 — Foundations — hierarchy, class and the survey system</t>
+          <t>D01-S01 — Foundations — hierarchy, class and the survey system</t>
         </is>
       </c>
       <c r="D2" s="21" t="inlineStr">
@@ -1991,7 +2044,7 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t>S1 — Foundations — hierarchy, class and the survey system</t>
+          <t>D01-S01 — Foundations — hierarchy, class and the survey system</t>
         </is>
       </c>
       <c r="D3" s="21" t="inlineStr">
@@ -2051,7 +2104,7 @@
       </c>
       <c r="C4" s="22" t="inlineStr">
         <is>
-          <t>S1 — Foundations — hierarchy, class and the survey system</t>
+          <t>D01-S01 — Foundations — hierarchy, class and the survey system</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -2111,7 +2164,7 @@
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>S1 — Foundations — hierarchy, class and the survey system</t>
+          <t>D01-S01 — Foundations — hierarchy, class and the survey system</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -2171,7 +2224,7 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>S1 — Foundations — hierarchy, class and the survey system</t>
+          <t>D01-S01 — Foundations — hierarchy, class and the survey system</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -2231,7 +2284,7 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>S1 — Foundations — hierarchy, class and the survey system</t>
+          <t>D01-S01 — Foundations — hierarchy, class and the survey system</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -2291,7 +2344,7 @@
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>S1 — Foundations — hierarchy, class and the survey system</t>
+          <t>D01-S01 — Foundations — hierarchy, class and the survey system</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -2351,7 +2404,7 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>S1 — Foundations — hierarchy, class and the survey system</t>
+          <t>D01-S01 — Foundations — hierarchy, class and the survey system</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -2411,7 +2464,7 @@
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>S1 — Foundations — hierarchy, class and the survey system</t>
+          <t>D01-S01 — Foundations — hierarchy, class and the survey system</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -2471,7 +2524,7 @@
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>S1 — Foundations — hierarchy, class and the survey system</t>
+          <t>D01-S01 — Foundations — hierarchy, class and the survey system</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -2527,7 +2580,7 @@
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>S1 — Foundations — hierarchy, class and the survey system</t>
+          <t>D01-S01 — Foundations — hierarchy, class and the survey system</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -2583,7 +2636,7 @@
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>S1 — Foundations — hierarchy, class and the survey system</t>
+          <t>D01-S01 — Foundations — hierarchy, class and the survey system</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -2639,7 +2692,7 @@
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>S1 — Foundations — hierarchy, class and the survey system</t>
+          <t>D01-S01 — Foundations — hierarchy, class and the survey system</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -2695,7 +2748,7 @@
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>S1 — Foundations — hierarchy, class and the survey system</t>
+          <t>D01-S01 — Foundations — hierarchy, class and the survey system</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -2751,7 +2804,7 @@
       </c>
       <c r="C16" s="26" t="inlineStr">
         <is>
-          <t>S2 — The survey regime</t>
+          <t>D01-S02 — The survey regime</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
@@ -2811,7 +2864,7 @@
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
-          <t>S2 — The survey regime</t>
+          <t>D01-S02 — The survey regime</t>
         </is>
       </c>
       <c r="D17" s="25" t="inlineStr">
@@ -2871,7 +2924,7 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>S2 — The survey regime</t>
+          <t>D01-S02 — The survey regime</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
@@ -2931,7 +2984,7 @@
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>S2 — The survey regime</t>
+          <t>D01-S02 — The survey regime</t>
         </is>
       </c>
       <c r="D19" s="25" t="inlineStr">
@@ -2991,7 +3044,7 @@
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>S2 — The survey regime</t>
+          <t>D01-S02 — The survey regime</t>
         </is>
       </c>
       <c r="D20" s="25" t="inlineStr">
@@ -3051,7 +3104,7 @@
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>S2 — The survey regime</t>
+          <t>D01-S02 — The survey regime</t>
         </is>
       </c>
       <c r="D21" s="25" t="inlineStr">
@@ -3111,7 +3164,7 @@
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>S2 — The survey regime</t>
+          <t>D01-S02 — The survey regime</t>
         </is>
       </c>
       <c r="D22" s="25" t="inlineStr">
@@ -3171,7 +3224,7 @@
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>S3 — Hull condition &amp; drydock</t>
+          <t>D01-S03 — Hull condition &amp; drydock</t>
         </is>
       </c>
       <c r="D23" s="25" t="inlineStr">
@@ -3231,7 +3284,7 @@
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>S3 — Hull condition &amp; drydock</t>
+          <t>D01-S03 — Hull condition &amp; drydock</t>
         </is>
       </c>
       <c r="D24" s="25" t="inlineStr">
@@ -3291,7 +3344,7 @@
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>S3 — Hull condition &amp; drydock</t>
+          <t>D01-S03 — Hull condition &amp; drydock</t>
         </is>
       </c>
       <c r="D25" s="25" t="inlineStr">
@@ -3351,7 +3404,7 @@
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>S3 — Hull condition &amp; drydock</t>
+          <t>D01-S03 — Hull condition &amp; drydock</t>
         </is>
       </c>
       <c r="D26" s="25" t="inlineStr">
@@ -3411,7 +3464,7 @@
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>S3 — Hull condition &amp; drydock</t>
+          <t>D01-S03 — Hull condition &amp; drydock</t>
         </is>
       </c>
       <c r="D27" s="25" t="inlineStr">
@@ -3471,7 +3524,7 @@
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>S3 — Hull condition &amp; drydock</t>
+          <t>D01-S03 — Hull condition &amp; drydock</t>
         </is>
       </c>
       <c r="D28" s="25" t="inlineStr">
@@ -3531,7 +3584,7 @@
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>S4 — Certificates, flag &amp; PSC</t>
+          <t>D01-S04 — Certificates, flag &amp; PSC</t>
         </is>
       </c>
       <c r="D29" s="25" t="inlineStr">
@@ -3591,7 +3644,7 @@
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
-          <t>S4 — Certificates, flag &amp; PSC</t>
+          <t>D01-S04 — Certificates, flag &amp; PSC</t>
         </is>
       </c>
       <c r="D30" s="25" t="inlineStr">
@@ -3651,7 +3704,7 @@
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>S4 — Certificates, flag &amp; PSC</t>
+          <t>D01-S04 — Certificates, flag &amp; PSC</t>
         </is>
       </c>
       <c r="D31" s="25" t="inlineStr">
@@ -3711,7 +3764,7 @@
       </c>
       <c r="C32" s="26" t="inlineStr">
         <is>
-          <t>S5 — Follow-ups &amp; closed-book mock</t>
+          <t>D01-S05 — Follow-ups &amp; closed-book mock</t>
         </is>
       </c>
       <c r="D32" s="25" t="inlineStr">
@@ -3771,7 +3824,7 @@
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>S5 — Follow-ups &amp; closed-book mock</t>
+          <t>D01-S05 — Follow-ups &amp; closed-book mock</t>
         </is>
       </c>
       <c r="D33" s="25" t="inlineStr">
@@ -3820,15 +3873,5787 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
+        </is>
+      </c>
+      <c r="D34" s="25" t="inlineStr">
+        <is>
+          <t>READ_SKELETON</t>
+        </is>
+      </c>
+      <c r="E34" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="26" t="inlineStr"/>
+      <c r="G34" s="26" t="inlineStr">
+        <is>
+          <t>Branches 1-3 carry the examiner chain; you cannot rank the 210 orals without them.</t>
+        </is>
+      </c>
+      <c r="H34" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="25" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_COLD_ATTEMPT</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="inlineStr">
+        <is>
+          <t>QB4_A#q1</t>
+        </is>
+      </c>
+      <c r="F35" s="26" t="inlineStr">
+        <is>
+          <t>State the objective and functional requirements of the ISM Code. What must a Safety Management System contain?</t>
+        </is>
+      </c>
+      <c r="G35" s="26" t="inlineStr">
+        <is>
+          <t>The ISM frame every other D03 answer hangs on. Examiners: Nair, Srivastava.</t>
+        </is>
+      </c>
+      <c r="H35" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Srivastava</t>
+        </is>
+      </c>
+      <c r="I35" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J35" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K35" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L35" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="25" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
+        </is>
+      </c>
+      <c r="D36" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_COLD_ATTEMPT</t>
+        </is>
+      </c>
+      <c r="E36" s="25" t="inlineStr">
+        <is>
+          <t>QB4_E#q5</t>
+        </is>
+      </c>
+      <c r="F36" s="26" t="inlineStr">
+        <is>
+          <t>ISM Code elements — list all 12 elements and explain the key ones.</t>
+        </is>
+      </c>
+      <c r="G36" s="26" t="inlineStr">
+        <is>
+          <t>The twelve elements. Three examiners: Nair, Simon, Srivastava.</t>
+        </is>
+      </c>
+      <c r="H36" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Simon, Srivastava</t>
+        </is>
+      </c>
+      <c r="I36" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J36" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K36" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="25" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
+        </is>
+      </c>
+      <c r="D37" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_COLD_ATTEMPT</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
+        <is>
+          <t>QB4_C#q16</t>
+        </is>
+      </c>
+      <c r="F37" s="26" t="inlineStr">
+        <is>
+          <t>Master's authority under ISM?</t>
+        </is>
+      </c>
+      <c r="G37" s="26" t="inlineStr">
+        <is>
+          <t>Broadest examiner evidence in the whole topic — Nair, Rajappan, Simon, Srivastava.</t>
+        </is>
+      </c>
+      <c r="H37" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Rajappan, Simon, Srivastava</t>
+        </is>
+      </c>
+      <c r="I37" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J37" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K37" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="25" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
+        </is>
+      </c>
+      <c r="D38" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E38" s="25" t="inlineStr">
+        <is>
+          <t>QB4_A#q1</t>
+        </is>
+      </c>
+      <c r="F38" s="26" t="inlineStr">
+        <is>
+          <t>State the objective and functional requirements of the ISM Code. What must a Safety Management System contain?</t>
+        </is>
+      </c>
+      <c r="G38" s="26" t="inlineStr">
+        <is>
+          <t>Branch 1, first half.</t>
+        </is>
+      </c>
+      <c r="H38" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Srivastava</t>
+        </is>
+      </c>
+      <c r="I38" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J38" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K38" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="25" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="inlineStr">
+        <is>
+          <t>QB4_E#q5</t>
+        </is>
+      </c>
+      <c r="F39" s="26" t="inlineStr">
+        <is>
+          <t>ISM Code elements — list all 12 elements and explain the key ones.</t>
+        </is>
+      </c>
+      <c r="G39" s="26" t="inlineStr">
+        <is>
+          <t>Branch 1, the element list.</t>
+        </is>
+      </c>
+      <c r="H39" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Simon, Srivastava</t>
+        </is>
+      </c>
+      <c r="I39" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J39" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K39" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="25" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
+        </is>
+      </c>
+      <c r="D40" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E40" s="25" t="inlineStr">
+        <is>
+          <t>QB4_C#q16</t>
+        </is>
+      </c>
+      <c r="F40" s="26" t="inlineStr">
+        <is>
+          <t>Master's authority under ISM?</t>
+        </is>
+      </c>
+      <c r="G40" s="26" t="inlineStr">
+        <is>
+          <t>Branch 1, the Master's overriding authority.</t>
+        </is>
+      </c>
+      <c r="H40" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Rajappan, Simon, Srivastava</t>
+        </is>
+      </c>
+      <c r="I40" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J40" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K40" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="25" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="inlineStr">
+        <is>
+          <t>QP2406-Q5</t>
+        </is>
+      </c>
+      <c r="F41" s="26" t="inlineStr">
+        <is>
+          <t>A) What are the functional requirements of ISM Code. (4) B) What are the objectives of an ISM internal Audit of a ship? How an internal Audit helps in External Audit of a vessel? Name the salient issues addressed in Inte</t>
+        </is>
+      </c>
+      <c r="G41" s="26" t="inlineStr">
+        <is>
+          <t>Functional requirements, internal audit and non-conformities — branches 1 to 3 in one answer.</t>
+        </is>
+      </c>
+      <c r="H41" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="26" t="inlineStr">
+        <is>
+          <t>UNIQUE ×1 (June 2024 → June 2024)</t>
+        </is>
+      </c>
+      <c r="J41" s="26" t="inlineStr">
+        <is>
+          <t>Not on temporal watch</t>
+        </is>
+      </c>
+      <c r="K41" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="25" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
+        </is>
+      </c>
+      <c r="D42" s="25" t="inlineStr">
+        <is>
+          <t>CLOSED_BOOK_RECALL</t>
+        </is>
+      </c>
+      <c r="E42" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="26" t="inlineStr"/>
+      <c r="G42" s="26" t="inlineStr">
+        <is>
+          <t>Delayed recall is the point of the session, not the reading.</t>
+        </is>
+      </c>
+      <c r="H42" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K42" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L42" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="25" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
+        </is>
+      </c>
+      <c r="D43" s="25" t="inlineStr">
+        <is>
+          <t>CLOSED_BOOK_RECALL</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="26" t="inlineStr"/>
+      <c r="G43" s="26" t="inlineStr">
+        <is>
+          <t>The list is the index to every ISM follow-up.</t>
+        </is>
+      </c>
+      <c r="H43" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K43" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="25" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
+        </is>
+      </c>
+      <c r="D44" s="25" t="inlineStr">
+        <is>
+          <t>CLOSED_BOOK_RECALL</t>
+        </is>
+      </c>
+      <c r="E44" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="26" t="inlineStr"/>
+      <c r="G44" s="26" t="inlineStr">
+        <is>
+          <t>The most examiner-broad question in D03.</t>
+        </is>
+      </c>
+      <c r="H44" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K44" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="25" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="inlineStr">
+        <is>
+          <t>CLOSED_BOOK_RECALL</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="26" t="inlineStr"/>
+      <c r="G45" s="26" t="inlineStr">
+        <is>
+          <t>Session 2 opens by re-answering this cold.</t>
+        </is>
+      </c>
+      <c r="H45" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J45" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K45" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="25" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="E46" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="26" t="inlineStr"/>
+      <c r="G46" s="26" t="inlineStr">
+        <is>
+          <t>Spacing, not volume, is what moves a 60-second answer into recall.</t>
+        </is>
+      </c>
+      <c r="H46" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K46" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="25" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="inlineStr">
+        <is>
+          <t>CLOSED_BOOK_RECALL</t>
+        </is>
+      </c>
+      <c r="E47" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="26" t="inlineStr"/>
+      <c r="G47" s="26" t="inlineStr">
+        <is>
+          <t>Delayed recall from Session 1 step 12.</t>
+        </is>
+      </c>
+      <c r="H47" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K47" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="25" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
+        </is>
+      </c>
+      <c r="D48" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E48" s="25" t="inlineStr">
+        <is>
+          <t>QB4_J#q7</t>
+        </is>
+      </c>
+      <c r="F48" s="26" t="inlineStr">
+        <is>
+          <t>Difference between ISM survey and ISM audit.</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="inlineStr">
+        <is>
+          <t>Chain A step 2 — the D01/D03 hinge in one question.</t>
+        </is>
+      </c>
+      <c r="H48" s="25" t="inlineStr">
+        <is>
+          <t>Simon</t>
+        </is>
+      </c>
+      <c r="I48" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J48" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K48" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L48" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="25" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
+        </is>
+      </c>
+      <c r="D49" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="inlineStr">
+        <is>
+          <t>QB4_A#q4</t>
+        </is>
+      </c>
+      <c r="F49" s="26" t="inlineStr">
+        <is>
+          <t>Describe the internal audit procedure under the ISM Code. Who conducts it, what is checked, and what is the outcome?</t>
+        </is>
+      </c>
+      <c r="G49" s="26" t="inlineStr">
+        <is>
+          <t>Chain A step 3. Node 02 names internal auditing explicitly.</t>
+        </is>
+      </c>
+      <c r="H49" s="25" t="inlineStr">
+        <is>
+          <t>Nair</t>
+        </is>
+      </c>
+      <c r="I49" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J49" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K49" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L49" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
+        </is>
+      </c>
+      <c r="D50" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E50" s="25" t="inlineStr">
+        <is>
+          <t>QB4_C#q10</t>
+        </is>
+      </c>
+      <c r="F50" s="26" t="inlineStr">
+        <is>
+          <t>NC vs MNC?</t>
+        </is>
+      </c>
+      <c r="G50" s="26" t="inlineStr">
+        <is>
+          <t>Chain A step 4. Short question, high failure rate.</t>
+        </is>
+      </c>
+      <c r="H50" s="25" t="inlineStr">
+        <is>
+          <t>Simon</t>
+        </is>
+      </c>
+      <c r="I50" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J50" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K50" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L50" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C51" s="26" t="inlineStr">
+        <is>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
+        </is>
+      </c>
+      <c r="D51" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="inlineStr">
+        <is>
+          <t>QB4_A#q3</t>
+        </is>
+      </c>
+      <c r="F51" s="26" t="inlineStr">
+        <is>
+          <t>An ISM non-conformity or deficiency is raised during an audit. What are the timescales for corrective action and how does the process work?</t>
+        </is>
+      </c>
+      <c r="G51" s="26" t="inlineStr">
+        <is>
+          <t>Chain A step 5 — corrective action WITH the timescales.</t>
+        </is>
+      </c>
+      <c r="H51" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Srivastava</t>
+        </is>
+      </c>
+      <c r="I51" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J51" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K51" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L51" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="25" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
+        </is>
+      </c>
+      <c r="D52" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E52" s="25" t="inlineStr">
+        <is>
+          <t>QB4_E#q6</t>
+        </is>
+      </c>
+      <c r="F52" s="26" t="inlineStr">
+        <is>
+          <t>Master's review and authority under ISM Code — overriding authority?</t>
+        </is>
+      </c>
+      <c r="G52" s="26" t="inlineStr">
+        <is>
+          <t>Chain A step 6 — master's review. Three examiners.</t>
+        </is>
+      </c>
+      <c r="H52" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Simon, Srivastava</t>
+        </is>
+      </c>
+      <c r="I52" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J52" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K52" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L52" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="25" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
+        </is>
+      </c>
+      <c r="D53" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E53" s="25" t="inlineStr">
+        <is>
+          <t>QB4_E#q7</t>
+        </is>
+      </c>
+      <c r="F53" s="26" t="inlineStr">
+        <is>
+          <t>How is continuous improvement achieved under the ISM Code?</t>
+        </is>
+      </c>
+      <c r="G53" s="26" t="inlineStr">
+        <is>
+          <t>Chain A terminus — the answer examiners wait for.</t>
+        </is>
+      </c>
+      <c r="H53" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Simon, Srivastava</t>
+        </is>
+      </c>
+      <c r="I53" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J53" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K53" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L53" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="25" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="inlineStr">
+        <is>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
+        </is>
+      </c>
+      <c r="D54" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E54" s="25" t="inlineStr">
+        <is>
+          <t>QB4_C#q7</t>
+        </is>
+      </c>
+      <c r="F54" s="26" t="inlineStr">
+        <is>
+          <t>DOC cancellation — grounds?</t>
+        </is>
+      </c>
+      <c r="G54" s="26" t="inlineStr">
+        <is>
+          <t>Chain A consequence limb — what makes a DOC withdrawable.</t>
+        </is>
+      </c>
+      <c r="H54" s="25" t="inlineStr">
+        <is>
+          <t>Srivastava</t>
+        </is>
+      </c>
+      <c r="I54" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J54" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K54" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L54" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="25" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
+        </is>
+      </c>
+      <c r="D55" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="inlineStr">
+        <is>
+          <t>QP2309-Q7</t>
+        </is>
+      </c>
+      <c r="F55" s="26" t="inlineStr">
+        <is>
+          <t>(a) State the difference between an audit and survey. (4) (b) State the action taken by a recognized organization carrying out ISM certification on behalf of the Administration towards handling of an ISM certificate in c</t>
+        </is>
+      </c>
+      <c r="G55" s="26" t="inlineStr">
+        <is>
+          <t>Audit versus survey, and RO action on ISM certificates — the written form of Chain A.</t>
+        </is>
+      </c>
+      <c r="H55" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I55" s="26" t="inlineStr">
+        <is>
+          <t>NEAR_REPEAT ×2 (September 2023 → April 2024)</t>
+        </is>
+      </c>
+      <c r="J55" s="26" t="inlineStr">
+        <is>
+          <t>TEMPORAL WATCH — law moved under this family</t>
+        </is>
+      </c>
+      <c r="K55" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L55" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="inlineStr">
+        <is>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
+        </is>
+      </c>
+      <c r="D56" s="25" t="inlineStr">
+        <is>
+          <t>BUILD_NOTE</t>
+        </is>
+      </c>
+      <c r="E56" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="26" t="inlineStr"/>
+      <c r="G56" s="26" t="inlineStr">
+        <is>
+          <t>Nothing in the corpus assembles the chain in one place, and every branch 1-3 answer leans on it.</t>
+        </is>
+      </c>
+      <c r="H56" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J56" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K56" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="25" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
+        </is>
+      </c>
+      <c r="D57" s="25" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="E57" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="26" t="inlineStr"/>
+      <c r="G57" s="26" t="inlineStr">
+        <is>
+          <t>The chain is the unit of recall, not the individual questions.</t>
+        </is>
+      </c>
+      <c r="H57" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J57" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K57" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="25" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr">
+        <is>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
+        </is>
+      </c>
+      <c r="D58" s="25" t="inlineStr">
+        <is>
+          <t>CLOSED_BOOK_RECALL</t>
+        </is>
+      </c>
+      <c r="E58" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="26" t="inlineStr"/>
+      <c r="G58" s="26" t="inlineStr">
+        <is>
+          <t>Delayed recall from Session 2.</t>
+        </is>
+      </c>
+      <c r="H58" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I58" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J58" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K58" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L58" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="25" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
+        </is>
+      </c>
+      <c r="D59" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E59" s="25" t="inlineStr">
+        <is>
+          <t>QB4_B#q5</t>
+        </is>
+      </c>
+      <c r="F59" s="26" t="inlineStr">
+        <is>
+          <t>What is the human element in shipping? Explain its key dimensions — navigation, safety, fatigue, communication, and organisational factors.</t>
+        </is>
+      </c>
+      <c r="G59" s="26" t="inlineStr">
+        <is>
+          <t>Branch 4's opening answer.</t>
+        </is>
+      </c>
+      <c r="H59" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Srivastava</t>
+        </is>
+      </c>
+      <c r="I59" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J59" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K59" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L59" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="25" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
+        </is>
+      </c>
+      <c r="D60" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E60" s="25" t="inlineStr">
+        <is>
+          <t>QB4_A#q17</t>
+        </is>
+      </c>
+      <c r="F60" s="26" t="inlineStr">
+        <is>
+          <t>Explain STCW Chapter VIII — Fitness for Duty, watch composition, and fatigue management.</t>
+        </is>
+      </c>
+      <c r="G60" s="26" t="inlineStr">
+        <is>
+          <t>Directly under the 11-question written cluster. Examiner: Rajappan.</t>
+        </is>
+      </c>
+      <c r="H60" s="25" t="inlineStr">
+        <is>
+          <t>Rajappan</t>
+        </is>
+      </c>
+      <c r="I60" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J60" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K60" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L60" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="inlineStr">
+        <is>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
+        </is>
+      </c>
+      <c r="D61" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E61" s="25" t="inlineStr">
+        <is>
+          <t>QB4_A#q15</t>
+        </is>
+      </c>
+      <c r="F61" s="26" t="inlineStr">
+        <is>
+          <t>What are the hours of work and rest limits under MLC 2006 and STCW, and how is rest splitting governed?</t>
+        </is>
+      </c>
+      <c r="G61" s="26" t="inlineStr">
+        <is>
+          <t>The numbers examiners test.</t>
+        </is>
+      </c>
+      <c r="H61" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Srivastava</t>
+        </is>
+      </c>
+      <c r="I61" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J61" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K61" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L61" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="25" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="inlineStr">
+        <is>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
+        </is>
+      </c>
+      <c r="D62" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E62" s="25" t="inlineStr">
+        <is>
+          <t>QB4_A#q14</t>
+        </is>
+      </c>
+      <c r="F62" s="26" t="inlineStr">
+        <is>
+          <t>Explain DMLC Part I and Part II under MLC 2006 — who issues each and what do they contain?</t>
+        </is>
+      </c>
+      <c r="G62" s="26" t="inlineStr">
+        <is>
+          <t>The most-confused point in the MLC cluster.</t>
+        </is>
+      </c>
+      <c r="H62" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Srivastava</t>
+        </is>
+      </c>
+      <c r="I62" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J62" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K62" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L62" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="25" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="inlineStr">
+        <is>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
+        </is>
+      </c>
+      <c r="D63" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
+        <is>
+          <t>QP2601-Q9</t>
+        </is>
+      </c>
+      <c r="F63" s="26" t="inlineStr">
+        <is>
+          <t>A). How is Human Element issue addressed in STCW code. B). Discuss the IMO guidance on fatigue mitigation and management on board ships</t>
+        </is>
+      </c>
+      <c r="G63" s="26" t="inlineStr">
+        <is>
+          <t>Most recent occurrence of the largest family in D03 — the current wording.</t>
+        </is>
+      </c>
+      <c r="H63" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I63" s="26" t="inlineStr">
+        <is>
+          <t>NEAR_REPEAT ×8 (January 2023 → April 2026)</t>
+        </is>
+      </c>
+      <c r="J63" s="26" t="inlineStr">
+        <is>
+          <t>TEMPORAL WATCH — law moved under this family</t>
+        </is>
+      </c>
+      <c r="K63" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L63" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="25" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="inlineStr">
+        <is>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
+        </is>
+      </c>
+      <c r="D64" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E64" s="25" t="inlineStr">
+        <is>
+          <t>QP2301-Q8</t>
+        </is>
+      </c>
+      <c r="F64" s="26" t="inlineStr">
+        <is>
+          <t>A). How is Human Element issue addressed in STCW code. B). Discuss the IMO guidance on fatigue mitigation and management on board ships</t>
+        </is>
+      </c>
+      <c r="G64" s="26" t="inlineStr">
+        <is>
+          <t>Read against QP2601-Q9 to see what the family does and does not change.</t>
+        </is>
+      </c>
+      <c r="H64" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I64" s="26" t="inlineStr">
+        <is>
+          <t>NEAR_REPEAT ×8 (January 2023 → April 2026)</t>
+        </is>
+      </c>
+      <c r="J64" s="26" t="inlineStr">
+        <is>
+          <t>TEMPORAL WATCH — law moved under this family</t>
+        </is>
+      </c>
+      <c r="K64" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L64" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="25" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="inlineStr">
+        <is>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
+        </is>
+      </c>
+      <c r="D65" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E65" s="25" t="inlineStr">
+        <is>
+          <t>QP2302-Q8</t>
+        </is>
+      </c>
+      <c r="F65" s="26" t="inlineStr">
+        <is>
+          <t>Referring to the Maritime Labour Convention (MLC) 2006, discuss: a) Flag State &amp; Port State responsibilities. b) On-board &amp; On-shore Compliant Procedures. c) Detainable deficiencies. d) Grievance Redressal Mechanisms for</t>
+        </is>
+      </c>
+      <c r="G65" s="26" t="inlineStr">
+        <is>
+          <t>The widest MLC answer held — flag and port State duties, complaint procedure, detainable deficiencies, Indian grievance redressal.</t>
+        </is>
+      </c>
+      <c r="H65" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" s="26" t="inlineStr">
+        <is>
+          <t>NEAR_REPEAT ×4 (November 2022 → July 2024)</t>
+        </is>
+      </c>
+      <c r="J65" s="26" t="inlineStr">
+        <is>
+          <t>Not on temporal watch</t>
+        </is>
+      </c>
+      <c r="K65" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L65" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C66" s="26" t="inlineStr">
+        <is>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
+        </is>
+      </c>
+      <c r="D66" s="25" t="inlineStr">
+        <is>
+          <t>BUILD_NOTE</t>
+        </is>
+      </c>
+      <c r="E66" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="26" t="inlineStr"/>
+      <c r="G66" s="26" t="inlineStr">
+        <is>
+          <t>Asked eleven times in writing. The numbers must be exact.</t>
+        </is>
+      </c>
+      <c r="H66" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J66" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K66" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="25" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C67" s="26" t="inlineStr">
+        <is>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
+        </is>
+      </c>
+      <c r="D67" s="25" t="inlineStr">
+        <is>
+          <t>BUILD_NOTE</t>
+        </is>
+      </c>
+      <c r="E67" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="26" t="inlineStr"/>
+      <c r="G67" s="26" t="inlineStr">
+        <is>
+          <t>The single most confused point in the MLC cluster.</t>
+        </is>
+      </c>
+      <c r="H67" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J67" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="25" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C68" s="26" t="inlineStr">
+        <is>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
+        </is>
+      </c>
+      <c r="D68" s="25" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="E68" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="26" t="inlineStr"/>
+      <c r="G68" s="26" t="inlineStr">
+        <is>
+          <t>Numbers decay fastest; space them.</t>
+        </is>
+      </c>
+      <c r="H68" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J68" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="25" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C69" s="26" t="inlineStr">
+        <is>
+          <t>D03-S04 — Human element, communication and risk</t>
+        </is>
+      </c>
+      <c r="D69" s="25" t="inlineStr">
+        <is>
+          <t>CLOSED_BOOK_RECALL</t>
+        </is>
+      </c>
+      <c r="E69" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="26" t="inlineStr"/>
+      <c r="G69" s="26" t="inlineStr">
+        <is>
+          <t>Delayed recall from Session 3.</t>
+        </is>
+      </c>
+      <c r="H69" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J69" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="25" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C70" s="26" t="inlineStr">
+        <is>
+          <t>D03-S04 — Human element, communication and risk</t>
+        </is>
+      </c>
+      <c r="D70" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E70" s="25" t="inlineStr">
+        <is>
+          <t>QB4_B#q9</t>
+        </is>
+      </c>
+      <c r="F70" s="26" t="inlineStr">
+        <is>
+          <t>Explain Maslow's Hierarchy of Needs and how it applies to crew motivation onboard.</t>
+        </is>
+      </c>
+      <c r="G70" s="26" t="inlineStr">
+        <is>
+          <t>Branch 8, and the answer donor behind QP2512-Q4.</t>
+        </is>
+      </c>
+      <c r="H70" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Srivastava</t>
+        </is>
+      </c>
+      <c r="I70" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J70" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K70" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L70" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C71" s="26" t="inlineStr">
+        <is>
+          <t>D03-S04 — Human element, communication and risk</t>
+        </is>
+      </c>
+      <c r="D71" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E71" s="25" t="inlineStr">
+        <is>
+          <t>QB5_E#q2</t>
+        </is>
+      </c>
+      <c r="F71" s="26" t="inlineStr">
+        <is>
+          <t>Hazard vs risk — what is the difference? Give examples from shipboard context.</t>
+        </is>
+      </c>
+      <c r="G71" s="26" t="inlineStr">
+        <is>
+          <t>Branch 10's gateway. Three examiners: Paul, Senthil, Simon.</t>
+        </is>
+      </c>
+      <c r="H71" s="25" t="inlineStr">
+        <is>
+          <t>Paul, Senthil, Simon</t>
+        </is>
+      </c>
+      <c r="I71" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J71" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K71" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L71" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="25" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C72" s="26" t="inlineStr">
+        <is>
+          <t>D03-S04 — Human element, communication and risk</t>
+        </is>
+      </c>
+      <c r="D72" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E72" s="25" t="inlineStr">
+        <is>
+          <t>QP2608-Q8</t>
+        </is>
+      </c>
+      <c r="F72" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="26" t="inlineStr">
+        <is>
+          <t>Adjudicated this session: the question belongs to two families because its limbs do. "Q8 is a repeat" is false for the larger limb.</t>
+        </is>
+      </c>
+      <c r="H72" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J72" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L72" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C73" s="26" t="inlineStr">
+        <is>
+          <t>D03-S04 — Human element, communication and risk</t>
+        </is>
+      </c>
+      <c r="D73" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E73" s="25" t="inlineStr">
+        <is>
+          <t>QP2606-Q5</t>
+        </is>
+      </c>
+      <c r="F73" s="26" t="inlineStr">
+        <is>
+          <t>a) Examine the role of the Safety Management System (SMS) in the implementation of the ISM Code, highlighting its components and significance of continuous improvement. (8) b) Examine the evolution of the ISM Code in res</t>
+        </is>
+      </c>
+      <c r="G73" s="26" t="inlineStr">
+        <is>
+          <t>The Code evolution including MSC.428(98) cyber risk — the currentness limb of branch 1.</t>
+        </is>
+      </c>
+      <c r="H73" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="26" t="inlineStr">
+        <is>
+          <t>EXACT_REPEAT ×3 (December 2023 → June 2026)</t>
+        </is>
+      </c>
+      <c r="J73" s="26" t="inlineStr">
+        <is>
+          <t>Not on temporal watch</t>
+        </is>
+      </c>
+      <c r="K73" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L73" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="25" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C74" s="26" t="inlineStr">
+        <is>
+          <t>D03-S04 — Human element, communication and risk</t>
+        </is>
+      </c>
+      <c r="D74" s="25" t="inlineStr">
+        <is>
+          <t>BUILD_NOTE</t>
+        </is>
+      </c>
+      <c r="E74" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="26" t="inlineStr"/>
+      <c r="G74" s="26" t="inlineStr">
+        <is>
+          <t>Two written questions test the distinctions directly.</t>
+        </is>
+      </c>
+      <c r="H74" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J74" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L74" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="25" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C75" s="26" t="inlineStr">
+        <is>
+          <t>D03-S04 — Human element, communication and risk</t>
+        </is>
+      </c>
+      <c r="D75" s="25" t="inlineStr">
+        <is>
+          <t>BUILD_NOTE</t>
+        </is>
+      </c>
+      <c r="E75" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="26" t="inlineStr"/>
+      <c r="G75" s="26" t="inlineStr">
+        <is>
+          <t>ALARP appears in four written questions and the tools are asked by name.</t>
+        </is>
+      </c>
+      <c r="H75" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J75" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L75" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="25" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C76" s="26" t="inlineStr">
+        <is>
+          <t>D03-S04 — Human element, communication and risk</t>
+        </is>
+      </c>
+      <c r="D76" s="25" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="E76" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="26" t="inlineStr"/>
+      <c r="G76" s="26" t="inlineStr">
+        <is>
+          <t>Sessions 1-4 read what exists; Session 5 writes what does not.</t>
+        </is>
+      </c>
+      <c r="H76" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J76" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L76" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C77" s="26" t="inlineStr">
+        <is>
+          <t>D03-S05 — Gaps and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D77" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E77" s="25" t="inlineStr">
+        <is>
+          <t>QB4_E#q8</t>
+        </is>
+      </c>
+      <c r="F77" s="26" t="inlineStr">
+        <is>
+          <t>PSC — appeal process, codes involved, and process after detention?</t>
+        </is>
+      </c>
+      <c r="G77" s="26" t="inlineStr">
+        <is>
+          <t>B-priority, three examiners — PSC appeal and post-detention process.</t>
+        </is>
+      </c>
+      <c r="H77" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Simon, Srivastava</t>
+        </is>
+      </c>
+      <c r="I77" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J77" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K77" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L77" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="25" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C78" s="26" t="inlineStr">
+        <is>
+          <t>D03-S05 — Gaps and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D78" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E78" s="25" t="inlineStr">
+        <is>
+          <t>QB4_C#q6</t>
+        </is>
+      </c>
+      <c r="F78" s="26" t="inlineStr">
+        <is>
+          <t>MLC 2006 — 5 Titles and flag/port state duties?</t>
+        </is>
+      </c>
+      <c r="G78" s="26" t="inlineStr">
+        <is>
+          <t>The five MLC Titles — the frame for the whole MLC cluster.</t>
+        </is>
+      </c>
+      <c r="H78" s="25" t="inlineStr">
+        <is>
+          <t>Rajappan</t>
+        </is>
+      </c>
+      <c r="I78" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J78" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K78" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L78" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="25" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C79" s="26" t="inlineStr">
+        <is>
+          <t>D03-S05 — Gaps and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D79" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E79" s="25" t="inlineStr">
+        <is>
+          <t>QB5_A#q11</t>
+        </is>
+      </c>
+      <c r="F79" s="26" t="inlineStr">
+        <is>
+          <t>Risk Assessment — How to Carry Out. How to Decide Risk Category.</t>
+        </is>
+      </c>
+      <c r="G79" s="26" t="inlineStr">
+        <is>
+          <t>How to actually carry out a risk assessment and decide a risk category.</t>
+        </is>
+      </c>
+      <c r="H79" s="25" t="inlineStr">
+        <is>
+          <t>Simon</t>
+        </is>
+      </c>
+      <c r="I79" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J79" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K79" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L79" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="25" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C80" s="26" t="inlineStr">
+        <is>
+          <t>D03-S05 — Gaps and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D80" s="25" t="inlineStr">
+        <is>
+          <t>BUILD_NOTE</t>
+        </is>
+      </c>
+      <c r="E80" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="26" t="inlineStr"/>
+      <c r="G80" s="26" t="inlineStr">
+        <is>
+          <t>Corpus coverage is 0 orals, 0 examiners. "Standing orders" and "night order book" return ZERO hits anywhere in the corpus — the clearest content gap in D03.</t>
+        </is>
+      </c>
+      <c r="H80" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J80" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L80" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="25" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C81" s="26" t="inlineStr">
+        <is>
+          <t>D03-S05 — Gaps and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D81" s="25" t="inlineStr">
+        <is>
+          <t>BUILD_NOTE</t>
+        </is>
+      </c>
+      <c r="E81" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="26" t="inlineStr"/>
+      <c r="G81" s="26" t="inlineStr">
+        <is>
+          <t>One oral, one examiner. "Low BN" returns zero hits despite being named in the official item.</t>
+        </is>
+      </c>
+      <c r="H81" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J81" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L81" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="25" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C82" s="26" t="inlineStr">
+        <is>
+          <t>D03-S05 — Gaps and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D82" s="25" t="inlineStr">
+        <is>
+          <t>MOCK</t>
+        </is>
+      </c>
+      <c r="E82" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="26" t="inlineStr"/>
+      <c r="G82" s="26" t="inlineStr">
+        <is>
+          <t>The completion test is the exit condition for the topic, not a warm-up.</t>
+        </is>
+      </c>
+      <c r="H82" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J82" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L82" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="25" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="25" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C83" s="26" t="inlineStr">
+        <is>
+          <t>D03-S05 — Gaps and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D83" s="25" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="E83" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="26" t="inlineStr"/>
+      <c r="G83" s="26" t="inlineStr">
+        <is>
+          <t>Progress is an input to the workbook, never an output.</t>
+        </is>
+      </c>
+      <c r="H83" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J83" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K83" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L83" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="25" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C84" s="26" t="inlineStr">
+        <is>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
+        </is>
+      </c>
+      <c r="D84" s="25" t="inlineStr">
+        <is>
+          <t>READ_SKELETON</t>
+        </is>
+      </c>
+      <c r="E84" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="26" t="inlineStr"/>
+      <c r="G84" s="26" t="inlineStr">
+        <is>
+          <t>Almost every D02 question is a relationship between two concepts; the skeleton is the pair list.</t>
+        </is>
+      </c>
+      <c r="H84" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J84" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K84" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L84" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="25" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C85" s="26" t="inlineStr">
+        <is>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
+        </is>
+      </c>
+      <c r="D85" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_COLD_ATTEMPT</t>
+        </is>
+      </c>
+      <c r="E85" s="25" t="inlineStr">
+        <is>
+          <t>QB9_C#q5</t>
+        </is>
+      </c>
+      <c r="F85" s="26" t="inlineStr">
+        <is>
+          <t>Insurance principles — list all principles of marine insurance and explain each.</t>
+        </is>
+      </c>
+      <c r="G85" s="26" t="inlineStr">
+        <is>
+          <t>Branch 1 entire. Three examiners: Nair, Rajappan, Simon.</t>
+        </is>
+      </c>
+      <c r="H85" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Rajappan, Simon</t>
+        </is>
+      </c>
+      <c r="I85" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J85" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K85" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L85" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="25" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C86" s="26" t="inlineStr">
+        <is>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
+        </is>
+      </c>
+      <c r="D86" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_COLD_ATTEMPT</t>
+        </is>
+      </c>
+      <c r="E86" s="25" t="inlineStr">
+        <is>
+          <t>QB1_B#q20</t>
+        </is>
+      </c>
+      <c r="F86" s="26" t="inlineStr">
+        <is>
+          <t>What is subrogation in the context of marine insurance/P&amp;I claims?</t>
+        </is>
+      </c>
+      <c r="G86" s="26" t="inlineStr">
+        <is>
+          <t>Branch 1's most-missed principle. Three examiners.</t>
+        </is>
+      </c>
+      <c r="H86" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Rajappan, Simon</t>
+        </is>
+      </c>
+      <c r="I86" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J86" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K86" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L86" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="25" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C87" s="26" t="inlineStr">
+        <is>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
+        </is>
+      </c>
+      <c r="D87" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_COLD_ATTEMPT</t>
+        </is>
+      </c>
+      <c r="E87" s="25" t="inlineStr">
+        <is>
+          <t>QB9_C#q1</t>
+        </is>
+      </c>
+      <c r="F87" s="26" t="inlineStr">
+        <is>
+          <t>Constructive total loss — define and explain the criteria for declaring CTL in marine insurance.</t>
+        </is>
+      </c>
+      <c r="G87" s="26" t="inlineStr">
+        <is>
+          <t>Branch 3 — the CTL test, with the numbers.</t>
+        </is>
+      </c>
+      <c r="H87" s="25" t="inlineStr">
+        <is>
+          <t>Srivastava</t>
+        </is>
+      </c>
+      <c r="I87" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J87" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K87" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L87" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="25" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C88" s="26" t="inlineStr">
+        <is>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
+        </is>
+      </c>
+      <c r="D88" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E88" s="25" t="inlineStr">
+        <is>
+          <t>QB9_C#q5</t>
+        </is>
+      </c>
+      <c r="F88" s="26" t="inlineStr">
+        <is>
+          <t>Insurance principles — list all principles of marine insurance and explain each.</t>
+        </is>
+      </c>
+      <c r="G88" s="26" t="inlineStr">
+        <is>
+          <t>Branch 1.</t>
+        </is>
+      </c>
+      <c r="H88" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Rajappan, Simon</t>
+        </is>
+      </c>
+      <c r="I88" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J88" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K88" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L88" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="25" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C89" s="26" t="inlineStr">
+        <is>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
+        </is>
+      </c>
+      <c r="D89" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E89" s="25" t="inlineStr">
+        <is>
+          <t>QB1_B#q20</t>
+        </is>
+      </c>
+      <c r="F89" s="26" t="inlineStr">
+        <is>
+          <t>What is subrogation in the context of marine insurance/P&amp;I claims?</t>
+        </is>
+      </c>
+      <c r="G89" s="26" t="inlineStr">
+        <is>
+          <t>Subrogation vs contribution is a standard follow-up pair.</t>
+        </is>
+      </c>
+      <c r="H89" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Rajappan, Simon</t>
+        </is>
+      </c>
+      <c r="I89" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J89" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K89" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L89" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="25" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C90" s="26" t="inlineStr">
+        <is>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
+        </is>
+      </c>
+      <c r="D90" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E90" s="25" t="inlineStr">
+        <is>
+          <t>QB9_C#q1</t>
+        </is>
+      </c>
+      <c r="F90" s="26" t="inlineStr">
+        <is>
+          <t>Constructive total loss — define and explain the criteria for declaring CTL in marine insurance.</t>
+        </is>
+      </c>
+      <c r="G90" s="26" t="inlineStr">
+        <is>
+          <t>CTL is the gateway to the whole loss-classification tree.</t>
+        </is>
+      </c>
+      <c r="H90" s="25" t="inlineStr">
+        <is>
+          <t>Srivastava</t>
+        </is>
+      </c>
+      <c r="I90" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J90" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K90" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L90" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="25" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C91" s="26" t="inlineStr">
+        <is>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
+        </is>
+      </c>
+      <c r="D91" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E91" s="25" t="inlineStr">
+        <is>
+          <t>QP2512-Q3</t>
+        </is>
+      </c>
+      <c r="F91" s="26" t="inlineStr">
+        <is>
+          <t>Discuss the principles of Marine Insurance. Explain each of the principle with suitable examples.</t>
+        </is>
+      </c>
+      <c r="G91" s="26" t="inlineStr">
+        <is>
+          <t>Branch 1 in a single answer.</t>
+        </is>
+      </c>
+      <c r="H91" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="26" t="inlineStr">
+        <is>
+          <t>EXACT_REPEAT ×2 (March 2021 → December 2025)</t>
+        </is>
+      </c>
+      <c r="J91" s="26" t="inlineStr">
+        <is>
+          <t>Not on temporal watch</t>
+        </is>
+      </c>
+      <c r="K91" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L91" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="25" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C92" s="26" t="inlineStr">
+        <is>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
+        </is>
+      </c>
+      <c r="D92" s="25" t="inlineStr">
+        <is>
+          <t>CLOSED_BOOK_RECALL</t>
+        </is>
+      </c>
+      <c r="E92" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" s="26" t="inlineStr"/>
+      <c r="G92" s="26" t="inlineStr">
+        <is>
+          <t>Everything else in D02 is built on these.</t>
+        </is>
+      </c>
+      <c r="H92" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I92" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J92" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K92" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L92" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="25" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C93" s="26" t="inlineStr">
+        <is>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
+        </is>
+      </c>
+      <c r="D93" s="25" t="inlineStr">
+        <is>
+          <t>CLOSED_BOOK_RECALL</t>
+        </is>
+      </c>
+      <c r="E93" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="26" t="inlineStr"/>
+      <c r="G93" s="26" t="inlineStr">
+        <is>
+          <t>The timing point separates a memorised list from an understood one.</t>
+        </is>
+      </c>
+      <c r="H93" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J93" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K93" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L93" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="25" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C94" s="26" t="inlineStr">
+        <is>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
+        </is>
+      </c>
+      <c r="D94" s="25" t="inlineStr">
+        <is>
+          <t>CLOSED_BOOK_RECALL</t>
+        </is>
+      </c>
+      <c r="E94" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" s="26" t="inlineStr"/>
+      <c r="G94" s="26" t="inlineStr">
+        <is>
+          <t>Session 2 opens by re-answering this cold.</t>
+        </is>
+      </c>
+      <c r="H94" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I94" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J94" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K94" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L94" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="25" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C95" s="26" t="inlineStr">
+        <is>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
+        </is>
+      </c>
+      <c r="D95" s="25" t="inlineStr">
+        <is>
+          <t>CLOSED_BOOK_RECALL</t>
+        </is>
+      </c>
+      <c r="E95" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F95" s="26" t="inlineStr"/>
+      <c r="G95" s="26" t="inlineStr">
+        <is>
+          <t>A boundary question, which is how D02 is examined.</t>
+        </is>
+      </c>
+      <c r="H95" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I95" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J95" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K95" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L95" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="25" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C96" s="26" t="inlineStr">
+        <is>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
+        </is>
+      </c>
+      <c r="D96" s="25" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="E96" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" s="26" t="inlineStr"/>
+      <c r="G96" s="26" t="inlineStr">
+        <is>
+          <t>Spacing, not volume.</t>
+        </is>
+      </c>
+      <c r="H96" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I96" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J96" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K96" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L96" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="25" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C97" s="26" t="inlineStr">
+        <is>
+          <t>D02-S02 — General Average</t>
+        </is>
+      </c>
+      <c r="D97" s="25" t="inlineStr">
+        <is>
+          <t>CLOSED_BOOK_RECALL</t>
+        </is>
+      </c>
+      <c r="E97" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" s="26" t="inlineStr"/>
+      <c r="G97" s="26" t="inlineStr">
+        <is>
+          <t>Delayed recall from Session 1 step 11.</t>
+        </is>
+      </c>
+      <c r="H97" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I97" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J97" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K97" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L97" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="25" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C98" s="26" t="inlineStr">
+        <is>
+          <t>D02-S02 — General Average</t>
+        </is>
+      </c>
+      <c r="D98" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E98" s="25" t="inlineStr">
+        <is>
+          <t>QB1_B#q14</t>
+        </is>
+      </c>
+      <c r="F98" s="26" t="inlineStr">
+        <is>
+          <t>What is General Average, and what is the procedure followed onboard when GA is declared?</t>
+        </is>
+      </c>
+      <c r="G98" s="26" t="inlineStr">
+        <is>
+          <t>Branch 4, and the procedural limb the CE actually owns. Three examiners.</t>
+        </is>
+      </c>
+      <c r="H98" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Rajappan, Simon</t>
+        </is>
+      </c>
+      <c r="I98" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J98" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K98" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L98" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="25" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C99" s="26" t="inlineStr">
+        <is>
+          <t>D02-S02 — General Average</t>
+        </is>
+      </c>
+      <c r="D99" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E99" s="25" t="inlineStr">
+        <is>
+          <t>QB1_A#q9</t>
+        </is>
+      </c>
+      <c r="F99" s="26" t="inlineStr">
+        <is>
+          <t>General Average — Explain including act and procedure followed.</t>
+        </is>
+      </c>
+      <c r="G99" s="26" t="inlineStr">
+        <is>
+          <t>The same ask from a second file — read the two together.</t>
+        </is>
+      </c>
+      <c r="H99" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Simon</t>
+        </is>
+      </c>
+      <c r="I99" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J99" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K99" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L99" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="25" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C100" s="26" t="inlineStr">
+        <is>
+          <t>D02-S02 — General Average</t>
+        </is>
+      </c>
+      <c r="D100" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E100" s="25" t="inlineStr">
+        <is>
+          <t>QB9_G#q7</t>
+        </is>
+      </c>
+      <c r="F100" s="26" t="inlineStr">
+        <is>
+          <t>What is the difference between General Average and Particular Average?</t>
+        </is>
+      </c>
+      <c r="G100" s="26" t="inlineStr">
+        <is>
+          <t>The boundary the follow-up always reaches for.</t>
+        </is>
+      </c>
+      <c r="H100" s="25" t="inlineStr">
+        <is>
+          <t>Nair</t>
+        </is>
+      </c>
+      <c r="I100" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J100" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K100" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L100" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C101" s="26" t="inlineStr">
+        <is>
+          <t>D02-S02 — General Average</t>
+        </is>
+      </c>
+      <c r="D101" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E101" s="25" t="inlineStr">
+        <is>
+          <t>QP2602-Q6</t>
+        </is>
+      </c>
+      <c r="F101" s="26" t="inlineStr">
+        <is>
+          <t>a)" General average is based on certain essential features" -Discuss the statement. b) A large vessel ran aground. Main engine was used in ahead and astern directions to shake the vessel loose from the ground. Due to exc</t>
+        </is>
+      </c>
+      <c r="G101" s="26" t="inlineStr">
+        <is>
+          <t>The most recent full GA-and-refloating answer — the current wording of the cluster.</t>
+        </is>
+      </c>
+      <c r="H101" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I101" s="26" t="inlineStr">
+        <is>
+          <t>NEAR_REPEAT ×6 (January 2023 → February 2026)</t>
+        </is>
+      </c>
+      <c r="J101" s="26" t="inlineStr">
+        <is>
+          <t>Not on temporal watch</t>
+        </is>
+      </c>
+      <c r="K101" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L101" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="25" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C102" s="26" t="inlineStr">
+        <is>
+          <t>D02-S02 — General Average</t>
+        </is>
+      </c>
+      <c r="D102" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E102" s="25" t="inlineStr">
+        <is>
+          <t>QP2304-Q3</t>
+        </is>
+      </c>
+      <c r="F102" s="26" t="inlineStr">
+        <is>
+          <t>A. What are the principles of modern salvage law? B. What is General Average, C. Explain with context to General Average, i. Entitlement; ii. Artificial; iii. Adjustment; iv. Contestation</t>
+        </is>
+      </c>
+      <c r="G102" s="26" t="inlineStr">
+        <is>
+          <t>Particular vs general average and the adjuster — the boundary, which is what the follow-up asks.</t>
+        </is>
+      </c>
+      <c r="H102" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I102" s="26" t="inlineStr">
+        <is>
+          <t>NEAR_REPEAT ×8 (February 2021 → July 2026)</t>
+        </is>
+      </c>
+      <c r="J102" s="26" t="inlineStr">
+        <is>
+          <t>Not on temporal watch</t>
+        </is>
+      </c>
+      <c r="K102" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L102" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="25" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C103" s="26" t="inlineStr">
+        <is>
+          <t>D02-S02 — General Average</t>
+        </is>
+      </c>
+      <c r="D103" s="25" t="inlineStr">
+        <is>
+          <t>BUILD_NOTE</t>
+        </is>
+      </c>
+      <c r="E103" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F103" s="26" t="inlineStr"/>
+      <c r="G103" s="26" t="inlineStr">
+        <is>
+          <t>Branches 3 to 5 all hang off it. Highest-value note in the topic.</t>
+        </is>
+      </c>
+      <c r="H103" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I103" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J103" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K103" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L103" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="25" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C104" s="26" t="inlineStr">
+        <is>
+          <t>D02-S02 — General Average</t>
+        </is>
+      </c>
+      <c r="D104" s="25" t="inlineStr">
+        <is>
+          <t>BUILD_NOTE</t>
+        </is>
+      </c>
+      <c r="E104" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F104" s="26" t="inlineStr"/>
+      <c r="G104" s="26" t="inlineStr">
+        <is>
+          <t>Nineteen written questions reward one well-built skeleton.</t>
+        </is>
+      </c>
+      <c r="H104" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I104" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J104" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K104" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L104" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="25" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C105" s="26" t="inlineStr">
+        <is>
+          <t>D02-S02 — General Average</t>
+        </is>
+      </c>
+      <c r="D105" s="25" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="E105" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" s="26" t="inlineStr"/>
+      <c r="G105" s="26" t="inlineStr">
+        <is>
+          <t>The tree is the unit of recall.</t>
+        </is>
+      </c>
+      <c r="H105" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I105" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J105" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K105" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L105" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="25" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C106" s="26" t="inlineStr">
+        <is>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+        </is>
+      </c>
+      <c r="D106" s="25" t="inlineStr">
+        <is>
+          <t>CLOSED_BOOK_RECALL</t>
+        </is>
+      </c>
+      <c r="E106" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="26" t="inlineStr"/>
+      <c r="G106" s="26" t="inlineStr">
+        <is>
+          <t>Delayed recall from Session 2.</t>
+        </is>
+      </c>
+      <c r="H106" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I106" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J106" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K106" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L106" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="25" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C107" s="26" t="inlineStr">
+        <is>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+        </is>
+      </c>
+      <c r="D107" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E107" s="25" t="inlineStr">
+        <is>
+          <t>QB1_A#q1</t>
+        </is>
+      </c>
+      <c r="F107" s="26" t="inlineStr">
+        <is>
+          <t>P&amp;I Club — What is Protection &amp; Indemnity? How does it differ from other marine insurance?</t>
+        </is>
+      </c>
+      <c r="G107" s="26" t="inlineStr">
+        <is>
+          <t>Branch 5 opening — the most-asked insurance question in the corpus.</t>
+        </is>
+      </c>
+      <c r="H107" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Rajappan</t>
+        </is>
+      </c>
+      <c r="I107" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J107" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K107" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L107" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="25" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C108" s="26" t="inlineStr">
+        <is>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+        </is>
+      </c>
+      <c r="D108" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E108" s="25" t="inlineStr">
+        <is>
+          <t>QB1_A#q10</t>
+        </is>
+      </c>
+      <c r="F108" s="26" t="inlineStr">
+        <is>
+          <t>Sue and Labour Clause — Explain.</t>
+        </is>
+      </c>
+      <c r="G108" s="26" t="inlineStr">
+        <is>
+          <t>Branches 2 and 3 — small, precise, frequently asked.</t>
+        </is>
+      </c>
+      <c r="H108" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Rajappan</t>
+        </is>
+      </c>
+      <c r="I108" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J108" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K108" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L108" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="25" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C109" s="26" t="inlineStr">
+        <is>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+        </is>
+      </c>
+      <c r="D109" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E109" s="25" t="inlineStr">
+        <is>
+          <t>QB1_A#q11</t>
+        </is>
+      </c>
+      <c r="F109" s="26" t="inlineStr">
+        <is>
+          <t>Salvage and SCOPIC — Different types of salvage. What is SCOPIC?</t>
+        </is>
+      </c>
+      <c r="G109" s="26" t="inlineStr">
+        <is>
+          <t>Branch 6. Three examiners: Nair, Rajappan, Simon.</t>
+        </is>
+      </c>
+      <c r="H109" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Rajappan, Simon</t>
+        </is>
+      </c>
+      <c r="I109" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J109" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K109" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L109" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="25" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C110" s="26" t="inlineStr">
+        <is>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+        </is>
+      </c>
+      <c r="D110" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E110" s="25" t="inlineStr">
+        <is>
+          <t>QB1_B#q11</t>
+        </is>
+      </c>
+      <c r="F110" s="26" t="inlineStr">
+        <is>
+          <t>What is Salvage, and explain SCOPIC (Special Compensation P&amp;I Clause)</t>
+        </is>
+      </c>
+      <c r="G110" s="26" t="inlineStr">
+        <is>
+          <t>The same ask from a second file — confirms the examiners really do ask it.</t>
+        </is>
+      </c>
+      <c r="H110" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Rajappan, Simon</t>
+        </is>
+      </c>
+      <c r="I110" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J110" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K110" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L110" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="25" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C111" s="26" t="inlineStr">
+        <is>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+        </is>
+      </c>
+      <c r="D111" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E111" s="25" t="inlineStr">
+        <is>
+          <t>QP2411-Q6</t>
+        </is>
+      </c>
+      <c r="F111" s="26" t="inlineStr">
+        <is>
+          <t>a) Define P&amp;I insurance and H&amp;M insurance, outlining the main differences between them in terms of coverage and purpose within the maritime industry. Why are both types of insurance essential for shipowners? (8) b) Discu</t>
+        </is>
+      </c>
+      <c r="G111" s="26" t="inlineStr">
+        <is>
+          <t>The comparison in one answer, including the 3/4ths collision split.</t>
+        </is>
+      </c>
+      <c r="H111" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I111" s="26" t="inlineStr">
+        <is>
+          <t>UNIQUE ×1 (November 2024 → November 2024)</t>
+        </is>
+      </c>
+      <c r="J111" s="26" t="inlineStr">
+        <is>
+          <t>Not on temporal watch</t>
+        </is>
+      </c>
+      <c r="K111" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L111" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="25" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C112" s="26" t="inlineStr">
+        <is>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+        </is>
+      </c>
+      <c r="D112" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E112" s="25" t="inlineStr">
+        <is>
+          <t>QP2406-Q8</t>
+        </is>
+      </c>
+      <c r="F112" s="26" t="inlineStr">
+        <is>
+          <t>A. What are the principles of modern salvage law? B. What is General Average, C. Explain with context to General Average, i. Entitlement; ii. Artificial; iii. Adjustment; iv. Contestation</t>
+        </is>
+      </c>
+      <c r="G112" s="26" t="inlineStr">
+        <is>
+          <t>Chain A and Chain B meeting in one question — how a salvage award enters the GA adjustment.</t>
+        </is>
+      </c>
+      <c r="H112" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I112" s="26" t="inlineStr">
+        <is>
+          <t>NEAR_REPEAT ×8 (February 2021 → July 2026)</t>
+        </is>
+      </c>
+      <c r="J112" s="26" t="inlineStr">
+        <is>
+          <t>Not on temporal watch</t>
+        </is>
+      </c>
+      <c r="K112" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L112" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="25" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C113" s="26" t="inlineStr">
+        <is>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+        </is>
+      </c>
+      <c r="D113" s="25" t="inlineStr">
+        <is>
+          <t>BUILD_NOTE</t>
+        </is>
+      </c>
+      <c r="E113" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F113" s="26" t="inlineStr"/>
+      <c r="G113" s="26" t="inlineStr">
+        <is>
+          <t>The salvage limb is what QP2406-Q8 tests and what a GA-only note misses.</t>
+        </is>
+      </c>
+      <c r="H113" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I113" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J113" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K113" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L113" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="25" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C114" s="26" t="inlineStr">
+        <is>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+        </is>
+      </c>
+      <c r="D114" s="25" t="inlineStr">
+        <is>
+          <t>BUILD_NOTE</t>
+        </is>
+      </c>
+      <c r="E114" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F114" s="26" t="inlineStr"/>
+      <c r="G114" s="26" t="inlineStr">
+        <is>
+          <t>Asked five times in writing and constantly orally.</t>
+        </is>
+      </c>
+      <c r="H114" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I114" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J114" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K114" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L114" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="25" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C115" s="26" t="inlineStr">
+        <is>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+        </is>
+      </c>
+      <c r="D115" s="25" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="E115" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F115" s="26" t="inlineStr"/>
+      <c r="G115" s="26" t="inlineStr">
+        <is>
+          <t>Pairs decay faster than singles; space them.</t>
+        </is>
+      </c>
+      <c r="H115" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I115" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J115" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K115" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L115" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="25" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C116" s="26" t="inlineStr">
+        <is>
+          <t>D02-S04 — Liability, limitation and pollution</t>
+        </is>
+      </c>
+      <c r="D116" s="25" t="inlineStr">
+        <is>
+          <t>CLOSED_BOOK_RECALL</t>
+        </is>
+      </c>
+      <c r="E116" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F116" s="26" t="inlineStr"/>
+      <c r="G116" s="26" t="inlineStr">
+        <is>
+          <t>Delayed recall from Session 3.</t>
+        </is>
+      </c>
+      <c r="H116" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I116" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J116" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K116" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L116" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="25" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C117" s="26" t="inlineStr">
+        <is>
+          <t>D02-S04 — Liability, limitation and pollution</t>
+        </is>
+      </c>
+      <c r="D117" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E117" s="25" t="inlineStr">
+        <is>
+          <t>QB1_A#q3</t>
+        </is>
+      </c>
+      <c r="F117" s="26" t="inlineStr">
+        <is>
+          <t>LLMC Convention — Who pays within and after the limits?</t>
+        </is>
+      </c>
+      <c r="G117" s="26" t="inlineStr">
+        <is>
+          <t>Branch 7 — the question that exposes whether you understand limitation at all.</t>
+        </is>
+      </c>
+      <c r="H117" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Simon</t>
+        </is>
+      </c>
+      <c r="I117" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J117" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K117" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L117" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="25" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C118" s="26" t="inlineStr">
+        <is>
+          <t>D02-S04 — Liability, limitation and pollution</t>
+        </is>
+      </c>
+      <c r="D118" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E118" s="25" t="inlineStr">
+        <is>
+          <t>QB1_A#q4</t>
+        </is>
+      </c>
+      <c r="F118" s="26" t="inlineStr">
+        <is>
+          <t>Bunker Convention 2001 — Explain in detail. Why was it required despite CLC?</t>
+        </is>
+      </c>
+      <c r="G118" s="26" t="inlineStr">
+        <is>
+          <t>The 3-occurrence written family, and the sharpest convention boundary in D02.</t>
+        </is>
+      </c>
+      <c r="H118" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Simon</t>
+        </is>
+      </c>
+      <c r="I118" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J118" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K118" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L118" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="25" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C119" s="26" t="inlineStr">
+        <is>
+          <t>D02-S04 — Liability, limitation and pollution</t>
+        </is>
+      </c>
+      <c r="D119" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E119" s="25" t="inlineStr">
+        <is>
+          <t>QB1_B#q10</t>
+        </is>
+      </c>
+      <c r="F119" s="26" t="inlineStr">
+        <is>
+          <t>Explain the CLC (Civil Liability Convention) — scope and application, including in the context of a bunker-spill incident</t>
+        </is>
+      </c>
+      <c r="G119" s="26" t="inlineStr">
+        <is>
+          <t>Chain C's gateway. Three examiners: Nair, Rajappan, Simon.</t>
+        </is>
+      </c>
+      <c r="H119" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Rajappan, Simon</t>
+        </is>
+      </c>
+      <c r="I119" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J119" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K119" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L119" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="25" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C120" s="26" t="inlineStr">
+        <is>
+          <t>D02-S04 — Liability, limitation and pollution</t>
+        </is>
+      </c>
+      <c r="D120" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E120" s="25" t="inlineStr">
+        <is>
+          <t>QP2506-Q5</t>
+        </is>
+      </c>
+      <c r="F120" s="26" t="inlineStr">
+        <is>
+          <t>a) What is LLMC and what is its purpose? Which are the two heads of claims for which limitation is stated in this Convention? Who can limit liability under this convention? b) Explain the terms: Plaintiff, Defendant, Pri</t>
+        </is>
+      </c>
+      <c r="G120" s="26" t="inlineStr">
+        <is>
+          <t>Purpose, heads of claim and the legal vocabulary the other limitation answers assume.</t>
+        </is>
+      </c>
+      <c r="H120" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I120" s="26" t="inlineStr">
+        <is>
+          <t>EXACT_REPEAT ×3 (January 2023 → June 2025)</t>
+        </is>
+      </c>
+      <c r="J120" s="26" t="inlineStr">
+        <is>
+          <t>Not on temporal watch</t>
+        </is>
+      </c>
+      <c r="K120" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L120" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="25" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C121" s="26" t="inlineStr">
+        <is>
+          <t>D02-S04 — Liability, limitation and pollution</t>
+        </is>
+      </c>
+      <c r="D121" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E121" s="25" t="inlineStr">
+        <is>
+          <t>QP2409-Q6</t>
+        </is>
+      </c>
+      <c r="F121" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Describe the background and relevance of the International Convention on Civil Liability for Bunker Oil Pollution Damage, 2001. Define the following under Bunker Convention and explain how they differ from other similar </t>
+        </is>
+      </c>
+      <c r="G121" s="26" t="inlineStr">
+        <is>
+          <t>The convention boundary examiners reach for immediately after CLC.</t>
+        </is>
+      </c>
+      <c r="H121" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I121" s="26" t="inlineStr">
+        <is>
+          <t>NEAR_REPEAT ×7 (January 2021 → September 2025)</t>
+        </is>
+      </c>
+      <c r="J121" s="26" t="inlineStr">
+        <is>
+          <t>Not on temporal watch</t>
+        </is>
+      </c>
+      <c r="K121" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L121" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="25" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C122" s="26" t="inlineStr">
+        <is>
+          <t>D02-S04 — Liability, limitation and pollution</t>
+        </is>
+      </c>
+      <c r="D122" s="25" t="inlineStr">
+        <is>
+          <t>BUILD_NOTE</t>
+        </is>
+      </c>
+      <c r="E122" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F122" s="26" t="inlineStr"/>
+      <c r="G122" s="26" t="inlineStr">
+        <is>
+          <t>Chain C is unanswerable without it, and QP2601-Q4 / QP2604-Q4 run the whole ladder in one question.</t>
+        </is>
+      </c>
+      <c r="H122" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I122" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J122" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K122" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L122" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="25" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C123" s="26" t="inlineStr">
+        <is>
+          <t>D02-S04 — Liability, limitation and pollution</t>
+        </is>
+      </c>
+      <c r="D123" s="25" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="E123" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F123" s="26" t="inlineStr"/>
+      <c r="G123" s="26" t="inlineStr">
+        <is>
+          <t>Sessions 1-4 read what exists; Session 5 writes what does not.</t>
+        </is>
+      </c>
+      <c r="H123" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I123" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J123" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K123" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L123" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="25" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C124" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D124" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E124" s="25" t="inlineStr">
+        <is>
+          <t>QB1_A#q8</t>
+        </is>
+      </c>
+      <c r="F124" s="26" t="inlineStr">
+        <is>
+          <t>Maritime Lien — Explain.</t>
+        </is>
+      </c>
+      <c r="G124" s="26" t="inlineStr">
+        <is>
+          <t>Branch 8, and the 5-occurrence lien family — the largest exact-title family in D02.</t>
+        </is>
+      </c>
+      <c r="H124" s="25" t="inlineStr">
+        <is>
+          <t>Nair</t>
+        </is>
+      </c>
+      <c r="I124" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J124" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K124" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L124" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="25" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C125" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D125" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E125" s="25" t="inlineStr">
+        <is>
+          <t>QB1_A#q7</t>
+        </is>
+      </c>
+      <c r="F125" s="26" t="inlineStr">
+        <is>
+          <t>Admiralty Law — Explain. How is the Chief Engineer related to the Admiralty Act?</t>
+        </is>
+      </c>
+      <c r="G125" s="26" t="inlineStr">
+        <is>
+          <t>Branch 8's Indian limb — the Admiralty Act 2017 and the CE's own exposure.</t>
+        </is>
+      </c>
+      <c r="H125" s="25" t="inlineStr">
+        <is>
+          <t>Nair</t>
+        </is>
+      </c>
+      <c r="I125" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J125" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K125" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L125" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="25" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C126" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D126" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E126" s="25" t="inlineStr">
+        <is>
+          <t>QB1_A#q27</t>
+        </is>
+      </c>
+      <c r="F126" s="26" t="inlineStr">
+        <is>
+          <t>Hague-Visby Rules — Explain.</t>
+        </is>
+      </c>
+      <c r="G126" s="26" t="inlineStr">
+        <is>
+          <t>The ONLY oral in the corpus on the cargo conventions.</t>
+        </is>
+      </c>
+      <c r="H126" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Simon</t>
+        </is>
+      </c>
+      <c r="I126" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J126" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K126" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L126" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="25" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C127" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D127" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E127" s="25" t="inlineStr">
+        <is>
+          <t>QP2512-Q9</t>
+        </is>
+      </c>
+      <c r="F127" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What is Maritime Lien? How does this lien travel with property? Explain the associated terms "In Rem" and "In personam". Which convention deals with maritime lien? Give the order of settlement of various debtor's claims </t>
+        </is>
+      </c>
+      <c r="G127" s="26" t="inlineStr">
+        <is>
+          <t>The most recent of the largest exact-title family — lien, in rem, in personam and priority.</t>
+        </is>
+      </c>
+      <c r="H127" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I127" s="26" t="inlineStr">
+        <is>
+          <t>EXACT_REPEAT ×6 (December 2022 → December 2025)</t>
+        </is>
+      </c>
+      <c r="J127" s="26" t="inlineStr">
+        <is>
+          <t>Not on temporal watch</t>
+        </is>
+      </c>
+      <c r="K127" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L127" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="25" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C128" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D128" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E128" s="25" t="inlineStr">
+        <is>
+          <t>QP2608-Q4</t>
+        </is>
+      </c>
+      <c r="F128" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G128" s="26" t="inlineStr">
+        <is>
+          <t>Adjudicated this session: the limb family and the whole-question family are nested, not duplicated. "Q4 is a five-time repeat" is true of 4 of its 16 marks.</t>
+        </is>
+      </c>
+      <c r="H128" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I128" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J128" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K128" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L128" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="25" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C129" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D129" s="25" t="inlineStr">
+        <is>
+          <t>BUILD_NOTE</t>
+        </is>
+      </c>
+      <c r="E129" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F129" s="26" t="inlineStr"/>
+      <c r="G129" s="26" t="inlineStr">
+        <is>
+          <t>Official item 11 says 1906; every paper that names an Act says 1963.</t>
+        </is>
+      </c>
+      <c r="H129" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I129" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J129" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K129" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L129" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="25" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C130" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D130" s="25" t="inlineStr">
+        <is>
+          <t>BUILD_NOTE</t>
+        </is>
+      </c>
+      <c r="E130" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F130" s="26" t="inlineStr"/>
+      <c r="G130" s="26" t="inlineStr">
+        <is>
+          <t>Ten written questions, ONE oral. Hamburg and Rotterdam appear in two written questions and no oral at all.</t>
+        </is>
+      </c>
+      <c r="H130" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I130" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J130" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K130" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L130" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="25" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C131" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D131" s="25" t="inlineStr">
+        <is>
+          <t>MOCK</t>
+        </is>
+      </c>
+      <c r="E131" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F131" s="26" t="inlineStr"/>
+      <c r="G131" s="26" t="inlineStr">
+        <is>
+          <t>Nearly every D02 follow-up is "and how is that different from...?".</t>
+        </is>
+      </c>
+      <c r="H131" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I131" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J131" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K131" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L131" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="25" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C132" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D132" s="25" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="E132" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F132" s="26" t="inlineStr"/>
+      <c r="G132" s="26" t="inlineStr">
+        <is>
+          <t>Progress is an input to the workbook, never an output.</t>
+        </is>
+      </c>
+      <c r="H132" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I132" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J132" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K132" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L132" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
         <is>
           <t>Generated from docs/study/study_sessions.json. Sessions for later topics appear here automatically as they are approved — this sheet has no hand-written rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L33"/>
+  <autoFilter ref="A1:L132"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId2"/>
@@ -3856,6 +9681,63 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId83"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4162,14 +10044,14 @@
           <t>WRITTEN ▸</t>
         </is>
       </c>
-      <c r="S3" s="27" t="inlineStr">
-        <is>
-          <t>NOT YET AVAILABLE</t>
-        </is>
-      </c>
-      <c r="T3" s="27" t="inlineStr">
-        <is>
-          <t>NOT YET AVAILABLE</t>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>PACK ▸</t>
+        </is>
+      </c>
+      <c r="T3" s="10" t="inlineStr">
+        <is>
+          <t>QUEUE ▸</t>
         </is>
       </c>
       <c r="U3" s="26" t="inlineStr">
@@ -4251,14 +10133,14 @@
           <t>WRITTEN ▸</t>
         </is>
       </c>
-      <c r="S4" s="27" t="inlineStr">
-        <is>
-          <t>NOT YET AVAILABLE</t>
-        </is>
-      </c>
-      <c r="T4" s="27" t="inlineStr">
-        <is>
-          <t>NOT YET AVAILABLE</t>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>PACK ▸</t>
+        </is>
+      </c>
+      <c r="T4" s="10" t="inlineStr">
+        <is>
+          <t>QUEUE ▸</t>
         </is>
       </c>
       <c r="U4" s="26" t="inlineStr">
@@ -4901,27 +10783,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId5"/>
     <hyperlink ref="R3" location="'WRITTEN BY TOPIC'!A168" display="WRITTEN ▸"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId6"/>
+    <hyperlink ref="T3" location="'STUDY QUEUE'!A34" display="QUEUE ▸"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId8"/>
     <hyperlink ref="R4" location="'WRITTEN BY TOPIC'!A98" display="WRITTEN ▸"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId9"/>
+    <hyperlink ref="T4" location="'STUDY QUEUE'!A84" display="QUEUE ▸"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId11"/>
     <hyperlink ref="R5" location="'WRITTEN BY TOPIC'!A237" display="WRITTEN ▸"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId13"/>
     <hyperlink ref="R6" location="'WRITTEN BY TOPIC'!A280" display="WRITTEN ▸"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId15"/>
     <hyperlink ref="R7" location="'WRITTEN BY TOPIC'!A349" display="WRITTEN ▸"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId17"/>
     <hyperlink ref="R8" location="'WRITTEN BY TOPIC'!A330" display="WRITTEN ▸"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5170,9 +11056,9 @@
           <t>WRITTEN ▸</t>
         </is>
       </c>
-      <c r="Q3" s="27" t="inlineStr">
-        <is>
-          <t>NOT YET AVAILABLE</t>
+      <c r="Q3" s="10" t="inlineStr">
+        <is>
+          <t>PACK ▸</t>
         </is>
       </c>
     </row>
@@ -5237,9 +11123,9 @@
           <t>WRITTEN ▸</t>
         </is>
       </c>
-      <c r="Q4" s="27" t="inlineStr">
-        <is>
-          <t>NOT YET AVAILABLE</t>
+      <c r="Q4" s="10" t="inlineStr">
+        <is>
+          <t>PACK ▸</t>
         </is>
       </c>
     </row>
@@ -5722,27 +11608,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId5"/>
     <hyperlink ref="P3" location="'WRITTEN BY TOPIC'!A168" display="WRITTEN ▸"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId8"/>
     <hyperlink ref="P4" location="'WRITTEN BY TOPIC'!A98" display="WRITTEN ▸"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId11"/>
     <hyperlink ref="P5" location="'WRITTEN BY TOPIC'!A237" display="WRITTEN ▸"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId13"/>
     <hyperlink ref="P6" location="'WRITTEN BY TOPIC'!A280" display="WRITTEN ▸"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId15"/>
     <hyperlink ref="P7" location="'WRITTEN BY TOPIC'!A349" display="WRITTEN ▸"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId17"/>
     <hyperlink ref="P8" location="'WRITTEN BY TOPIC'!A330" display="WRITTEN ▸"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
+++ b/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
@@ -636,7 +636,7 @@
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Study order #1 of 10, and study order is dependency-first, not priority-first. Prerequisites: —. It unlocks: D02, D03, D04, D05, D06, D07, D08, D09. Priority rank #2 (score 0.5897).</t>
+          <t>Study order #1 of 10, and study order is dependency-first, not priority-first. Prerequisites: —. It unlocks: D02, D03, D04, D05, D06, D07, D08, D09. Priority rank #2 (score 0.6035).</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
-          <t>9ef35a16ebc97d08</t>
+          <t>23495e145a2e1b0e</t>
         </is>
       </c>
     </row>
@@ -9907,10 +9907,10 @@
         </is>
       </c>
       <c r="F2" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="G2" s="21" t="n">
         <v>46</v>
-      </c>
-      <c r="G2" s="21" t="n">
-        <v>39</v>
       </c>
       <c r="H2" s="21" t="n">
         <v>96</v>
@@ -9933,7 +9933,7 @@
         <v>2</v>
       </c>
       <c r="N2" s="21" t="n">
-        <v>0.5897</v>
+        <v>0.6035</v>
       </c>
       <c r="O2" s="21" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="F3" s="25" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G3" s="25" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H3" s="25" t="n">
         <v>69</v>
@@ -10085,10 +10085,10 @@
         </is>
       </c>
       <c r="F4" s="25" t="n">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="H4" s="25" t="n">
         <v>70</v>
@@ -10111,7 +10111,7 @@
         <v>3</v>
       </c>
       <c r="N4" s="25" t="n">
-        <v>0.5782</v>
+        <v>0.5249</v>
       </c>
       <c r="O4" s="25" t="inlineStr">
         <is>
@@ -10174,10 +10174,10 @@
         </is>
       </c>
       <c r="F5" s="25" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>43</v>
@@ -10200,7 +10200,7 @@
         <v>5</v>
       </c>
       <c r="N5" s="25" t="n">
-        <v>0.3183</v>
+        <v>0.3302</v>
       </c>
       <c r="O5" s="25" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>4</v>
       </c>
       <c r="N6" s="25" t="n">
-        <v>0.3403</v>
+        <v>0.337</v>
       </c>
       <c r="O6" s="25" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>6</v>
       </c>
       <c r="N7" s="25" t="n">
-        <v>0.2856</v>
+        <v>0.2801</v>
       </c>
       <c r="O7" s="25" t="inlineStr">
         <is>
@@ -10441,10 +10441,10 @@
         </is>
       </c>
       <c r="F8" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="25" t="n">
         <v>19</v>
@@ -10467,7 +10467,7 @@
         <v>7</v>
       </c>
       <c r="N8" s="25" t="n">
-        <v>0.1067</v>
+        <v>0.109</v>
       </c>
       <c r="O8" s="25" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>8</v>
       </c>
       <c r="N9" s="25" t="n">
-        <v>0.0945</v>
+        <v>0.0934</v>
       </c>
       <c r="O9" s="25" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>9</v>
       </c>
       <c r="N10" s="25" t="n">
-        <v>0.074</v>
+        <v>0.0725</v>
       </c>
       <c r="O10" s="25" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="25" t="n">
-        <v>0.0589</v>
+        <v>0.0575</v>
       </c>
       <c r="O11" s="25" t="inlineStr">
         <is>
@@ -10940,13 +10940,13 @@
         </is>
       </c>
       <c r="C2" s="25" t="n">
+        <v>53</v>
+      </c>
+      <c r="D2" s="25" t="n">
         <v>46</v>
       </c>
-      <c r="D2" s="25" t="n">
-        <v>39</v>
-      </c>
       <c r="E2" s="25" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F2" s="25" t="n">
         <v>6</v>
@@ -10972,7 +10972,7 @@
         </is>
       </c>
       <c r="M2" s="25" t="n">
-        <v>0.5897</v>
+        <v>0.6035</v>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
@@ -11007,13 +11007,13 @@
         </is>
       </c>
       <c r="C3" s="25" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E3" s="25" t="n">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F3" s="25" t="n">
         <v>6</v>
@@ -11074,13 +11074,13 @@
         </is>
       </c>
       <c r="C4" s="25" t="n">
+        <v>114</v>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>108</v>
+      </c>
+      <c r="E4" s="25" t="n">
         <v>134</v>
-      </c>
-      <c r="D4" s="25" t="n">
-        <v>127</v>
-      </c>
-      <c r="E4" s="25" t="n">
-        <v>162</v>
       </c>
       <c r="F4" s="25" t="n">
         <v>6</v>
@@ -11106,7 +11106,7 @@
         </is>
       </c>
       <c r="M4" s="25" t="n">
-        <v>0.5782</v>
+        <v>0.5249</v>
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
@@ -11141,13 +11141,13 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>5</v>
@@ -11173,7 +11173,7 @@
         </is>
       </c>
       <c r="M5" s="25" t="n">
-        <v>0.3183</v>
+        <v>0.3302</v>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         </is>
       </c>
       <c r="M6" s="25" t="n">
-        <v>0.3403</v>
+        <v>0.337</v>
       </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="M7" s="25" t="n">
-        <v>0.2856</v>
+        <v>0.2801</v>
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
@@ -11342,16 +11342,16 @@
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="25" t="n">
         <v>19</v>
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="M8" s="25" t="n">
-        <v>0.1067</v>
+        <v>0.109</v>
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="M9" s="25" t="n">
-        <v>0.0945</v>
+        <v>0.0934</v>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         </is>
       </c>
       <c r="M10" s="25" t="n">
-        <v>0.074</v>
+        <v>0.0725</v>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="M11" s="25" t="n">
-        <v>0.0589</v>
+        <v>0.0575</v>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>

--- a/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
+++ b/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
@@ -29131,7 +29131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -29200,7 +29200,7 @@
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
-          <t>NOT_INTEGRATED</t>
+          <t>SOURCE_LAYER_ADOPTED_QUESTIONS_NOT_INGESTED</t>
         </is>
       </c>
     </row>
@@ -29301,7 +29301,7 @@
       <c r="A13" s="26" t="inlineStr"/>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>2006–2020</t>
+          <t>2006–2009</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
@@ -29312,36 +29312,36 @@
     </row>
     <row r="14">
       <c r="A14" s="26" t="inlineStr"/>
-      <c r="B14" s="26" t="inlineStr"/>
-      <c r="C14" s="26" t="inlineStr"/>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>2010–2020</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>source layer ADOPTED 2026-08-23 and questions NOT ingested; sitting dates are MONTH_YEAR_CLAIMED_BY_SECONDARY_SOURCE, so this window can never reach VALIDATED_RANGE on the present evidence</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>RESERVED FIELDS (populate themselves when the layer is validated)</t>
-        </is>
-      </c>
+      <c r="A15" s="26" t="inlineStr"/>
       <c r="B15" s="26" t="inlineStr"/>
       <c r="C15" s="26" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr"/>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>historical_written_papers</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>NOT YET INTEGRATED</t>
-        </is>
-      </c>
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>RESERVED FIELDS (populate themselves when the layer is validated)</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr"/>
+      <c r="C16" s="26" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="26" t="inlineStr"/>
       <c r="B17" s="26" t="inlineStr">
         <is>
-          <t>historical_written_questions</t>
+          <t>historical_written_papers</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -29354,7 +29354,7 @@
       <c r="A18" s="26" t="inlineStr"/>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>earliest_evidence</t>
+          <t>historical_written_questions</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -29367,7 +29367,7 @@
       <c r="A19" s="26" t="inlineStr"/>
       <c r="B19" s="26" t="inlineStr">
         <is>
-          <t>latest_evidence</t>
+          <t>earliest_evidence</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -29380,7 +29380,7 @@
       <c r="A20" s="26" t="inlineStr"/>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>long_term_recurrence</t>
+          <t>latest_evidence</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -29393,7 +29393,7 @@
       <c r="A21" s="26" t="inlineStr"/>
       <c r="B21" s="26" t="inlineStr">
         <is>
-          <t>recent_recurrence</t>
+          <t>long_term_recurrence</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -29406,7 +29406,7 @@
       <c r="A22" s="26" t="inlineStr"/>
       <c r="B22" s="26" t="inlineStr">
         <is>
-          <t>trend</t>
+          <t>recent_recurrence</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -29419,7 +29419,7 @@
       <c r="A23" s="26" t="inlineStr"/>
       <c r="B23" s="26" t="inlineStr">
         <is>
-          <t>currentness</t>
+          <t>trend</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -29432,7 +29432,7 @@
       <c r="A24" s="26" t="inlineStr"/>
       <c r="B24" s="26" t="inlineStr">
         <is>
-          <t>historical_qi_status</t>
+          <t>currentness</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -29443,26 +29443,39 @@
     </row>
     <row r="25">
       <c r="A25" s="26" t="inlineStr"/>
-      <c r="B25" s="26" t="inlineStr"/>
-      <c r="C25" s="26" t="inlineStr"/>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>historical_qi_status</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>NOT YET INTEGRATED</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="inlineStr">
-        <is>
-          <t>PUBLIC CLAIM (generated, never hand-written)</t>
-        </is>
-      </c>
+      <c r="A26" s="26" t="inlineStr"/>
       <c r="B26" s="26" t="inlineStr"/>
       <c r="C26" s="26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="26" t="inlineStr"/>
-      <c r="B27" s="26" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>PUBLIC CLAIM (generated, never hand-written)</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr"/>
+      <c r="C27" s="26" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr"/>
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>Based on MIW's currently mapped Oral corpus and 360 solved Written questions across 40 papers (2023-01 to 2026-08).</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr"/>
+      <c r="C28" s="26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
+++ b/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
@@ -636,7 +636,7 @@
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Study order #1 of 10, and study order is dependency-first, not priority-first. Prerequisites: —. It unlocks: D02, D03, D04, D05, D06, D07, D08, D09. Priority rank #2 (score 0.6035).</t>
+          <t>Study order #1 of 10, and study order is dependency-first, not priority-first. Prerequisites: —. It unlocks: D02, D03, D04, D05, D06, D07, D08, D09. Priority rank #2 (score 0.6554).</t>
         </is>
       </c>
     </row>
@@ -9907,10 +9907,10 @@
         </is>
       </c>
       <c r="F2" s="21" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="G2" s="21" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="H2" s="21" t="n">
         <v>96</v>
@@ -9933,7 +9933,7 @@
         <v>2</v>
       </c>
       <c r="N2" s="21" t="n">
-        <v>0.6035</v>
+        <v>0.6554</v>
       </c>
       <c r="O2" s="21" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="F3" s="25" t="n">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="G3" s="25" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="H3" s="25" t="n">
         <v>69</v>
@@ -10111,7 +10111,7 @@
         <v>3</v>
       </c>
       <c r="N4" s="25" t="n">
-        <v>0.5249</v>
+        <v>0.5389</v>
       </c>
       <c r="O4" s="25" t="inlineStr">
         <is>
@@ -10174,10 +10174,10 @@
         </is>
       </c>
       <c r="F5" s="25" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>43</v>
@@ -10200,7 +10200,7 @@
         <v>5</v>
       </c>
       <c r="N5" s="25" t="n">
-        <v>0.3302</v>
+        <v>0.3134</v>
       </c>
       <c r="O5" s="25" t="inlineStr">
         <is>
@@ -10263,10 +10263,10 @@
         </is>
       </c>
       <c r="F6" s="25" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H6" s="25" t="n">
         <v>50</v>
@@ -10289,7 +10289,7 @@
         <v>4</v>
       </c>
       <c r="N6" s="25" t="n">
-        <v>0.337</v>
+        <v>0.3466</v>
       </c>
       <c r="O6" s="25" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>6</v>
       </c>
       <c r="N7" s="25" t="n">
-        <v>0.2801</v>
+        <v>0.2922</v>
       </c>
       <c r="O7" s="25" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>7</v>
       </c>
       <c r="N8" s="25" t="n">
-        <v>0.109</v>
+        <v>0.1092</v>
       </c>
       <c r="O8" s="25" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>8</v>
       </c>
       <c r="N9" s="25" t="n">
-        <v>0.0934</v>
+        <v>0.0958</v>
       </c>
       <c r="O9" s="25" t="inlineStr">
         <is>
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="F10" s="25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G10" s="25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H10" s="25" t="n">
         <v>0</v>
@@ -10645,7 +10645,7 @@
         <v>9</v>
       </c>
       <c r="N10" s="25" t="n">
-        <v>0.0725</v>
+        <v>0.0781</v>
       </c>
       <c r="O10" s="25" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="25" t="n">
-        <v>0.0575</v>
+        <v>0.0606</v>
       </c>
       <c r="O11" s="25" t="inlineStr">
         <is>
@@ -10940,13 +10940,13 @@
         </is>
       </c>
       <c r="C2" s="25" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D2" s="25" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="F2" s="25" t="n">
         <v>6</v>
@@ -10972,7 +10972,7 @@
         </is>
       </c>
       <c r="M2" s="25" t="n">
-        <v>0.6035</v>
+        <v>0.6554</v>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
@@ -11007,13 +11007,13 @@
         </is>
       </c>
       <c r="C3" s="25" t="n">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E3" s="25" t="n">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F3" s="25" t="n">
         <v>6</v>
@@ -11106,7 +11106,7 @@
         </is>
       </c>
       <c r="M4" s="25" t="n">
-        <v>0.5249</v>
+        <v>0.5389</v>
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
@@ -11141,13 +11141,13 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>5</v>
@@ -11173,7 +11173,7 @@
         </is>
       </c>
       <c r="M5" s="25" t="n">
-        <v>0.3302</v>
+        <v>0.3134</v>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
@@ -11208,13 +11208,13 @@
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>6</v>
@@ -11240,7 +11240,7 @@
         </is>
       </c>
       <c r="M6" s="25" t="n">
-        <v>0.337</v>
+        <v>0.3466</v>
       </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="M7" s="25" t="n">
-        <v>0.2801</v>
+        <v>0.2922</v>
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="M8" s="25" t="n">
-        <v>0.109</v>
+        <v>0.1092</v>
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="M9" s="25" t="n">
-        <v>0.0934</v>
+        <v>0.0958</v>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
@@ -11476,16 +11476,16 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" s="25" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F10" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" s="25" t="n">
         <v>0</v>
@@ -11508,7 +11508,7 @@
         </is>
       </c>
       <c r="M10" s="25" t="n">
-        <v>0.0725</v>
+        <v>0.0781</v>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="M11" s="25" t="n">
-        <v>0.0575</v>
+        <v>0.0606</v>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>

--- a/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
+++ b/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
@@ -19,7 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ABOUT" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'STUDY QUEUE'!$A$1:$L$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'STUDY QUEUE'!$A$1:$L$140</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ROADMAP'!$A$1:$U$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TOPIC DETAIL'!$A$1:$Q$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'WRITTEN BY TOPIC'!$A$1:$H$361</definedName>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B27" s="26" t="inlineStr">
         <is>
-          <t>466, of which 0 could not be resolved</t>
+          <t>474, of which 0 could not be resolved</t>
         </is>
       </c>
       <c r="C27" s="26" t="n"/>
@@ -1898,7 +1898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L134"/>
+  <dimension ref="A1:L142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3589,37 +3589,37 @@
       </c>
       <c r="D29" s="25" t="inlineStr">
         <is>
-          <t>WRITTEN_STUDY</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E29" s="25" t="inlineStr">
         <is>
-          <t>QP2504-Q2</t>
+          <t>QB4_A#q10</t>
         </is>
       </c>
       <c r="F29" s="26" t="inlineStr">
         <is>
-          <t>a) Define "Clear Grounds" as per Port State Control procedures. Under what circumstances can an inspector establish clear grounds for a more detailed inspection onboard a vessel? (4) b) As a Chief Engineer, explain the i</t>
+          <t>What is the meaning of 'statutory' in the context of ship certificates? List the main statutory certificates carried on a container vessel.</t>
         </is>
       </c>
       <c r="G29" s="26" t="inlineStr">
         <is>
-          <t>A-priority orals 9, 10, 13, 14. Build N1 (certificate table) and N4 (PSC chain).</t>
+          <t>A-priority 12. The only question in the corpus that makes you assemble the certificate set; N1 is written from it.</t>
         </is>
       </c>
       <c r="H29" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Simon</t>
         </is>
       </c>
       <c r="I29" s="26" t="inlineStr">
         <is>
-          <t>UNIQUE ×1 (April 2025 → April 2025)</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J29" s="26" t="inlineStr">
         <is>
-          <t>Not on temporal watch</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K29" s="25" t="inlineStr">
@@ -3649,37 +3649,37 @@
       </c>
       <c r="D30" s="25" t="inlineStr">
         <is>
-          <t>WRITTEN_STUDY</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E30" s="25" t="inlineStr">
         <is>
-          <t>QP2606-Q2</t>
+          <t>QB1_A#q22</t>
         </is>
       </c>
       <c r="F30" s="26" t="inlineStr">
         <is>
-          <t>What provisions are made under Port State Control (PSC) towards (i) Certificates issued by non-party states to their ships (ii) Inspection of ships below convention size and (iii) No more favorable treatment. (16)</t>
+          <t>Port State, Coastal State, Flag State — duties in each maritime zone.</t>
         </is>
       </c>
       <c r="G30" s="26" t="inlineStr">
         <is>
-          <t>A-priority orals 9, 10, 13, 14. Build N1 (certificate table) and N4 (PSC chain).</t>
+          <t>A-priority 1. The flag/coastal/port State frame the rest of this session rests on.</t>
         </is>
       </c>
       <c r="H30" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Simon</t>
         </is>
       </c>
       <c r="I30" s="26" t="inlineStr">
         <is>
-          <t>NEAR_REPEAT ×4 (September 2023 → June 2026)</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J30" s="26" t="inlineStr">
         <is>
-          <t>TEMPORAL WATCH — law moved under this family</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K30" s="25" t="inlineStr">
@@ -3709,37 +3709,37 @@
       </c>
       <c r="D31" s="25" t="inlineStr">
         <is>
-          <t>WRITTEN_STUDY</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E31" s="25" t="inlineStr">
         <is>
-          <t>QP2401-Q9</t>
+          <t>QB4_A#q8</t>
         </is>
       </c>
       <c r="F31" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referring to the IMO Instruments Implementation Code. a) Briefly Discuss the objectives of the code and strategy recommended to flag state to achieve the objective. Which all IMO instruments covered in the code. b) What </t>
+          <t>What is the difference between a Flag State and a Recognised Organisation (RO)? What statutory authority does an RO carry?</t>
         </is>
       </c>
       <c r="G31" s="26" t="inlineStr">
         <is>
-          <t>A-priority orals 9, 10, 13, 14. Build N1 (certificate table) and N4 (PSC chain).</t>
+          <t>A-priority 2. What statutory authority an RO actually carries.</t>
         </is>
       </c>
       <c r="H31" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Srivastava</t>
         </is>
       </c>
       <c r="I31" s="26" t="inlineStr">
         <is>
-          <t>EXACT_REPEAT ×6 (February 2023 → October 2025)</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J31" s="26" t="inlineStr">
         <is>
-          <t>TEMPORAL WATCH — law moved under this family</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K31" s="25" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="C32" s="26" t="inlineStr">
         <is>
-          <t>D01-S05 — Follow-ups &amp; closed-book mock</t>
+          <t>D01-S04 — Certificates, flag &amp; PSC</t>
         </is>
       </c>
       <c r="D32" s="25" t="inlineStr">
@@ -3774,22 +3774,22 @@
       </c>
       <c r="E32" s="25" t="inlineStr">
         <is>
-          <t>QB1_F#q13</t>
+          <t>QB4_A#q5</t>
         </is>
       </c>
       <c r="F32" s="26" t="inlineStr">
         <is>
-          <t>audit, survey,inspection,statutory suvery definitions and differences</t>
+          <t>Describe how a PSC inspection is conducted — how do officers board, what are the types and levels of inspection, and how are deficiency codes used?</t>
         </is>
       </c>
       <c r="G32" s="26" t="inlineStr">
         <is>
-          <t>Build N3. Then closed-book: 8 questions in 30 minutes, aloud, no notes.</t>
+          <t>A-priority 17. First half of the N4 PSC chain.</t>
         </is>
       </c>
       <c r="H32" s="25" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Nair</t>
         </is>
       </c>
       <c r="I32" s="26" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>D01-S05 — Follow-ups &amp; closed-book mock</t>
+          <t>D01-S04 — Certificates, flag &amp; PSC</t>
         </is>
       </c>
       <c r="D33" s="25" t="inlineStr">
@@ -3834,22 +3834,22 @@
       </c>
       <c r="E33" s="25" t="inlineStr">
         <is>
-          <t>QB1_F#q15</t>
+          <t>QB4_A#q6</t>
         </is>
       </c>
       <c r="F33" s="26" t="inlineStr">
         <is>
-          <t>What all items cannot be credited by chief engineer in a CSM survey</t>
+          <t>Your vessel is detained by PSC. What are the grounds for detention, what actions do you take, and what is the appeal procedure?</t>
         </is>
       </c>
       <c r="G33" s="26" t="inlineStr">
         <is>
-          <t>Build N3. Then closed-book: 8 questions in 30 minutes, aloud, no notes.</t>
+          <t>A-priority 18. Second half of the N4 PSC chain.</t>
         </is>
       </c>
       <c r="H33" s="25" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Nair, Srivastava</t>
         </is>
       </c>
       <c r="I33" s="26" t="inlineStr">
@@ -3879,28 +3879,32 @@
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="C34" s="26" t="inlineStr">
         <is>
-          <t>D03-S01 — Foundation — the ISM architecture</t>
+          <t>D01-S04 — Certificates, flag &amp; PSC</t>
         </is>
       </c>
       <c r="D34" s="25" t="inlineStr">
         <is>
-          <t>READ_SKELETON</t>
+          <t>WRITTEN_STUDY</t>
         </is>
       </c>
       <c r="E34" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="26" t="inlineStr"/>
+          <t>QP2504-Q2</t>
+        </is>
+      </c>
+      <c r="F34" s="26" t="inlineStr">
+        <is>
+          <t>a) Define "Clear Grounds" as per Port State Control procedures. Under what circumstances can an inspector establish clear grounds for a more detailed inspection onboard a vessel? (4) b) As a Chief Engineer, explain the i</t>
+        </is>
+      </c>
       <c r="G34" s="26" t="inlineStr">
         <is>
-          <t>Branches 1-3 carry the examiner chain; you cannot rank the 210 orals without them.</t>
+          <t>Five A-priority orals and three written. Build N1 (certificate table) and N4 (PSC chain). The orals were added 2026-08-23: this session promised certificates, flag and PSC and carried no oral on any of them, because D01 owned no settled oral on those branches until the file-title contradictions were adjudicated.</t>
         </is>
       </c>
       <c r="H34" s="25" t="inlineStr">
@@ -3910,12 +3914,12 @@
       </c>
       <c r="I34" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNIQUE ×1 (April 2025 → April 2025)</t>
         </is>
       </c>
       <c r="J34" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Not on temporal watch</t>
         </is>
       </c>
       <c r="K34" s="25" t="inlineStr">
@@ -3923,9 +3927,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -3935,47 +3939,47 @@
       </c>
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="C35" s="26" t="inlineStr">
         <is>
-          <t>D03-S01 — Foundation — the ISM architecture</t>
+          <t>D01-S04 — Certificates, flag &amp; PSC</t>
         </is>
       </c>
       <c r="D35" s="25" t="inlineStr">
         <is>
-          <t>ORAL_COLD_ATTEMPT</t>
+          <t>WRITTEN_STUDY</t>
         </is>
       </c>
       <c r="E35" s="25" t="inlineStr">
         <is>
-          <t>QB4_A#q1</t>
+          <t>QP2606-Q2</t>
         </is>
       </c>
       <c r="F35" s="26" t="inlineStr">
         <is>
-          <t>State the objective and functional requirements of the ISM Code. What must a Safety Management System contain?</t>
+          <t>What provisions are made under Port State Control (PSC) towards (i) Certificates issued by non-party states to their ships (ii) Inspection of ships below convention size and (iii) No more favorable treatment. (16)</t>
         </is>
       </c>
       <c r="G35" s="26" t="inlineStr">
         <is>
-          <t>The ISM frame every other D03 answer hangs on. Examiners: Nair, Srivastava.</t>
+          <t>Five A-priority orals and three written. Build N1 (certificate table) and N4 (PSC chain). The orals were added 2026-08-23: this session promised certificates, flag and PSC and carried no oral on any of them, because D01 owned no settled oral on those branches until the file-title contradictions were adjudicated.</t>
         </is>
       </c>
       <c r="H35" s="25" t="inlineStr">
         <is>
-          <t>Nair, Srivastava</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I35" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>NEAR_REPEAT ×4 (September 2023 → June 2026)</t>
         </is>
       </c>
       <c r="J35" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>TEMPORAL WATCH — law moved under this family</t>
         </is>
       </c>
       <c r="K35" s="25" t="inlineStr">
@@ -3995,47 +3999,47 @@
       </c>
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="C36" s="26" t="inlineStr">
         <is>
-          <t>D03-S01 — Foundation — the ISM architecture</t>
+          <t>D01-S04 — Certificates, flag &amp; PSC</t>
         </is>
       </c>
       <c r="D36" s="25" t="inlineStr">
         <is>
-          <t>ORAL_COLD_ATTEMPT</t>
+          <t>WRITTEN_STUDY</t>
         </is>
       </c>
       <c r="E36" s="25" t="inlineStr">
         <is>
-          <t>QB4_E#q5</t>
+          <t>QP2401-Q9</t>
         </is>
       </c>
       <c r="F36" s="26" t="inlineStr">
         <is>
-          <t>ISM Code elements — list all 12 elements and explain the key ones.</t>
+          <t xml:space="preserve">Referring to the IMO Instruments Implementation Code. a) Briefly Discuss the objectives of the code and strategy recommended to flag state to achieve the objective. Which all IMO instruments covered in the code. b) What </t>
         </is>
       </c>
       <c r="G36" s="26" t="inlineStr">
         <is>
-          <t>The twelve elements. Three examiners: Nair, Simon, Srivastava.</t>
+          <t>Five A-priority orals and three written. Build N1 (certificate table) and N4 (PSC chain). The orals were added 2026-08-23: this session promised certificates, flag and PSC and carried no oral on any of them, because D01 owned no settled oral on those branches until the file-title contradictions were adjudicated.</t>
         </is>
       </c>
       <c r="H36" s="25" t="inlineStr">
         <is>
-          <t>Nair, Simon, Srivastava</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I36" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>EXACT_REPEAT ×6 (February 2023 → October 2025)</t>
         </is>
       </c>
       <c r="J36" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>TEMPORAL WATCH — law moved under this family</t>
         </is>
       </c>
       <c r="K36" s="25" t="inlineStr">
@@ -4055,37 +4059,37 @@
       </c>
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="C37" s="26" t="inlineStr">
         <is>
-          <t>D03-S01 — Foundation — the ISM architecture</t>
+          <t>D01-S05 — A-set completion, follow-ups &amp; closed-book mock</t>
         </is>
       </c>
       <c r="D37" s="25" t="inlineStr">
         <is>
-          <t>ORAL_COLD_ATTEMPT</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E37" s="25" t="inlineStr">
         <is>
-          <t>QB4_C#q16</t>
+          <t>QB1_I#q5</t>
         </is>
       </c>
       <c r="F37" s="26" t="inlineStr">
         <is>
-          <t>Master's authority under ISM?</t>
+          <t>Explain any renewal survey in detail as Chief Engineer.</t>
         </is>
       </c>
       <c r="G37" s="26" t="inlineStr">
         <is>
-          <t>Broadest examiner evidence in the whole topic — Nair, Rajappan, Simon, Srivastava.</t>
+          <t>A-priority 11, the integrating question. It has no examiner evidence and is in A for that reason alone.</t>
         </is>
       </c>
       <c r="H37" s="25" t="inlineStr">
         <is>
-          <t>Nair, Rajappan, Simon, Srivastava</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I37" s="26" t="inlineStr">
@@ -4115,12 +4119,12 @@
       </c>
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="C38" s="26" t="inlineStr">
         <is>
-          <t>D03-S01 — Foundation — the ISM architecture</t>
+          <t>D01-S05 — A-set completion, follow-ups &amp; closed-book mock</t>
         </is>
       </c>
       <c r="D38" s="25" t="inlineStr">
@@ -4130,22 +4134,22 @@
       </c>
       <c r="E38" s="25" t="inlineStr">
         <is>
-          <t>QB4_A#q1</t>
+          <t>QB4_A#q9</t>
         </is>
       </c>
       <c r="F38" s="26" t="inlineStr">
         <is>
-          <t>State the objective and functional requirements of the ISM Code. What must a Safety Management System contain?</t>
+          <t>Explain Condition of Class — what triggers it, types, and what is Suspension of Class? What is the CE's obligation?</t>
         </is>
       </c>
       <c r="G38" s="26" t="inlineStr">
         <is>
-          <t>Branch 1, first half.</t>
+          <t>A-priority 4. Extends the Session 1 Condition-of-Class answer to suspension and the CE's duty.</t>
         </is>
       </c>
       <c r="H38" s="25" t="inlineStr">
         <is>
-          <t>Nair, Srivastava</t>
+          <t>Nair</t>
         </is>
       </c>
       <c r="I38" s="26" t="inlineStr">
@@ -4175,12 +4179,12 @@
       </c>
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="C39" s="26" t="inlineStr">
         <is>
-          <t>D03-S01 — Foundation — the ISM architecture</t>
+          <t>D01-S05 — A-set completion, follow-ups &amp; closed-book mock</t>
         </is>
       </c>
       <c r="D39" s="25" t="inlineStr">
@@ -4190,22 +4194,22 @@
       </c>
       <c r="E39" s="25" t="inlineStr">
         <is>
-          <t>QB4_E#q5</t>
+          <t>QB3_A#q4</t>
         </is>
       </c>
       <c r="F39" s="26" t="inlineStr">
         <is>
-          <t>ISM Code elements — list all 12 elements and explain the key ones.</t>
+          <t>Explain class notations using your last vessel as an example.</t>
         </is>
       </c>
       <c r="G39" s="26" t="inlineStr">
         <is>
-          <t>Branch 1, the element list.</t>
+          <t>A-priority 6. A personal-ship opener; it must be fluent, not recalled.</t>
         </is>
       </c>
       <c r="H39" s="25" t="inlineStr">
         <is>
-          <t>Nair, Simon, Srivastava</t>
+          <t>Nair, Srivastava</t>
         </is>
       </c>
       <c r="I39" s="26" t="inlineStr">
@@ -4235,12 +4239,12 @@
       </c>
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="C40" s="26" t="inlineStr">
         <is>
-          <t>D03-S01 — Foundation — the ISM architecture</t>
+          <t>D01-S05 — A-set completion, follow-ups &amp; closed-book mock</t>
         </is>
       </c>
       <c r="D40" s="25" t="inlineStr">
@@ -4250,22 +4254,22 @@
       </c>
       <c r="E40" s="25" t="inlineStr">
         <is>
-          <t>QB4_C#q16</t>
+          <t>QB1_F#q13</t>
         </is>
       </c>
       <c r="F40" s="26" t="inlineStr">
         <is>
-          <t>Master's authority under ISM?</t>
+          <t>audit, survey,inspection,statutory suvery definitions and differences</t>
         </is>
       </c>
       <c r="G40" s="26" t="inlineStr">
         <is>
-          <t>Branch 1, the Master's overriding authority.</t>
+          <t>Review bucket, first in study order. Mapping is REVIEW_PENDING but the subject is not in doubt.</t>
         </is>
       </c>
       <c r="H40" s="25" t="inlineStr">
         <is>
-          <t>Nair, Rajappan, Simon, Srivastava</t>
+          <t>Simon</t>
         </is>
       </c>
       <c r="I40" s="26" t="inlineStr">
@@ -4295,47 +4299,47 @@
       </c>
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="C41" s="26" t="inlineStr">
         <is>
-          <t>D03-S01 — Foundation — the ISM architecture</t>
+          <t>D01-S05 — A-set completion, follow-ups &amp; closed-book mock</t>
         </is>
       </c>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>WRITTEN_STUDY</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E41" s="25" t="inlineStr">
         <is>
-          <t>QP2406-Q5</t>
+          <t>QB1_F#q15</t>
         </is>
       </c>
       <c r="F41" s="26" t="inlineStr">
         <is>
-          <t>A) What are the functional requirements of ISM Code. (4) B) What are the objectives of an ISM internal Audit of a ship? How an internal Audit helps in External Audit of a vessel? Name the salient issues addressed in Inte</t>
+          <t>What all items cannot be credited by chief engineer in a CSM survey</t>
         </is>
       </c>
       <c r="G41" s="26" t="inlineStr">
         <is>
-          <t>Functional requirements, internal audit and non-conformities — branches 1 to 3 in one answer.</t>
+          <t>Review bucket. Completion-test item 6 depends on it.</t>
         </is>
       </c>
       <c r="H41" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Simon</t>
         </is>
       </c>
       <c r="I41" s="26" t="inlineStr">
         <is>
-          <t>UNIQUE ×1 (June 2024 → June 2024)</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J41" s="26" t="inlineStr">
         <is>
-          <t>Not on temporal watch</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K41" s="25" t="inlineStr">
@@ -4365,7 +4369,7 @@
       </c>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>CLOSED_BOOK_RECALL</t>
+          <t>READ_SKELETON</t>
         </is>
       </c>
       <c r="E42" s="25" t="inlineStr">
@@ -4376,7 +4380,7 @@
       <c r="F42" s="26" t="inlineStr"/>
       <c r="G42" s="26" t="inlineStr">
         <is>
-          <t>Delayed recall is the point of the session, not the reading.</t>
+          <t>Branches 1-3 carry the examiner chain; you cannot rank the 210 orals without them.</t>
         </is>
       </c>
       <c r="H42" s="25" t="inlineStr">
@@ -4421,33 +4425,37 @@
       </c>
       <c r="D43" s="25" t="inlineStr">
         <is>
-          <t>CLOSED_BOOK_RECALL</t>
+          <t>ORAL_COLD_ATTEMPT</t>
         </is>
       </c>
       <c r="E43" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="26" t="inlineStr"/>
+          <t>QB4_A#q1</t>
+        </is>
+      </c>
+      <c r="F43" s="26" t="inlineStr">
+        <is>
+          <t>State the objective and functional requirements of the ISM Code. What must a Safety Management System contain?</t>
+        </is>
+      </c>
       <c r="G43" s="26" t="inlineStr">
         <is>
-          <t>The list is the index to every ISM follow-up.</t>
+          <t>The ISM frame every other D03 answer hangs on. Examiners: Nair, Srivastava.</t>
         </is>
       </c>
       <c r="H43" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Srivastava</t>
         </is>
       </c>
       <c r="I43" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J43" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K43" s="25" t="inlineStr">
@@ -4455,9 +4463,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L43" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -4477,33 +4485,37 @@
       </c>
       <c r="D44" s="25" t="inlineStr">
         <is>
-          <t>CLOSED_BOOK_RECALL</t>
+          <t>ORAL_COLD_ATTEMPT</t>
         </is>
       </c>
       <c r="E44" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F44" s="26" t="inlineStr"/>
+          <t>QB4_E#q5</t>
+        </is>
+      </c>
+      <c r="F44" s="26" t="inlineStr">
+        <is>
+          <t>ISM Code elements — list all 12 elements and explain the key ones.</t>
+        </is>
+      </c>
       <c r="G44" s="26" t="inlineStr">
         <is>
-          <t>The most examiner-broad question in D03.</t>
+          <t>The twelve elements. Three examiners: Nair, Simon, Srivastava.</t>
         </is>
       </c>
       <c r="H44" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Simon, Srivastava</t>
         </is>
       </c>
       <c r="I44" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J44" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K44" s="25" t="inlineStr">
@@ -4511,9 +4523,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L44" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -4533,33 +4545,37 @@
       </c>
       <c r="D45" s="25" t="inlineStr">
         <is>
-          <t>CLOSED_BOOK_RECALL</t>
+          <t>ORAL_COLD_ATTEMPT</t>
         </is>
       </c>
       <c r="E45" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F45" s="26" t="inlineStr"/>
+          <t>QB4_C#q16</t>
+        </is>
+      </c>
+      <c r="F45" s="26" t="inlineStr">
+        <is>
+          <t>Master's authority under ISM?</t>
+        </is>
+      </c>
       <c r="G45" s="26" t="inlineStr">
         <is>
-          <t>Session 2 opens by re-answering this cold.</t>
+          <t>Broadest examiner evidence in the whole topic — Nair, Rajappan, Simon, Srivastava.</t>
         </is>
       </c>
       <c r="H45" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Rajappan, Simon, Srivastava</t>
         </is>
       </c>
       <c r="I45" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J45" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K45" s="25" t="inlineStr">
@@ -4567,9 +4583,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L45" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -4589,33 +4605,37 @@
       </c>
       <c r="D46" s="25" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E46" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F46" s="26" t="inlineStr"/>
+          <t>QB4_A#q1</t>
+        </is>
+      </c>
+      <c r="F46" s="26" t="inlineStr">
+        <is>
+          <t>State the objective and functional requirements of the ISM Code. What must a Safety Management System contain?</t>
+        </is>
+      </c>
       <c r="G46" s="26" t="inlineStr">
         <is>
-          <t>Spacing, not volume, is what moves a 60-second answer into recall.</t>
+          <t>Branch 1, first half.</t>
         </is>
       </c>
       <c r="H46" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Srivastava</t>
         </is>
       </c>
       <c r="I46" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J46" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K46" s="25" t="inlineStr">
@@ -4623,9 +4643,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L46" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -4640,38 +4660,42 @@
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>D03-S02 — Oral core — the ISM audit chain</t>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
         </is>
       </c>
       <c r="D47" s="25" t="inlineStr">
         <is>
-          <t>CLOSED_BOOK_RECALL</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E47" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F47" s="26" t="inlineStr"/>
+          <t>QB4_E#q5</t>
+        </is>
+      </c>
+      <c r="F47" s="26" t="inlineStr">
+        <is>
+          <t>ISM Code elements — list all 12 elements and explain the key ones.</t>
+        </is>
+      </c>
       <c r="G47" s="26" t="inlineStr">
         <is>
-          <t>Delayed recall from Session 1 step 12.</t>
+          <t>Branch 1, the element list.</t>
         </is>
       </c>
       <c r="H47" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Simon, Srivastava</t>
         </is>
       </c>
       <c r="I47" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J47" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K47" s="25" t="inlineStr">
@@ -4679,9 +4703,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L47" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L47" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4720,7 @@
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t>D03-S02 — Oral core — the ISM audit chain</t>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
         </is>
       </c>
       <c r="D48" s="25" t="inlineStr">
@@ -4706,22 +4730,22 @@
       </c>
       <c r="E48" s="25" t="inlineStr">
         <is>
-          <t>QB4_J#q7</t>
+          <t>QB4_C#q16</t>
         </is>
       </c>
       <c r="F48" s="26" t="inlineStr">
         <is>
-          <t>Difference between ISM survey and ISM audit.</t>
+          <t>Master's authority under ISM?</t>
         </is>
       </c>
       <c r="G48" s="26" t="inlineStr">
         <is>
-          <t>Chain A step 2 — the D01/D03 hinge in one question.</t>
+          <t>Branch 1, the Master's overriding authority.</t>
         </is>
       </c>
       <c r="H48" s="25" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Nair, Rajappan, Simon, Srivastava</t>
         </is>
       </c>
       <c r="I48" s="26" t="inlineStr">
@@ -4756,42 +4780,42 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>D03-S02 — Oral core — the ISM audit chain</t>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
         </is>
       </c>
       <c r="D49" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>WRITTEN_STUDY</t>
         </is>
       </c>
       <c r="E49" s="25" t="inlineStr">
         <is>
-          <t>QB4_A#q4</t>
+          <t>QP2406-Q5</t>
         </is>
       </c>
       <c r="F49" s="26" t="inlineStr">
         <is>
-          <t>Describe the internal audit procedure under the ISM Code. Who conducts it, what is checked, and what is the outcome?</t>
+          <t>A) What are the functional requirements of ISM Code. (4) B) What are the objectives of an ISM internal Audit of a ship? How an internal Audit helps in External Audit of a vessel? Name the salient issues addressed in Inte</t>
         </is>
       </c>
       <c r="G49" s="26" t="inlineStr">
         <is>
-          <t>Chain A step 3. Node 02 names internal auditing explicitly.</t>
+          <t>Functional requirements, internal audit and non-conformities — branches 1 to 3 in one answer.</t>
         </is>
       </c>
       <c r="H49" s="25" t="inlineStr">
         <is>
-          <t>Nair</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I49" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>UNIQUE ×1 (June 2024 → June 2024)</t>
         </is>
       </c>
       <c r="J49" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>Not on temporal watch</t>
         </is>
       </c>
       <c r="K49" s="25" t="inlineStr">
@@ -4816,42 +4840,38 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>D03-S02 — Oral core — the ISM audit chain</t>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
         </is>
       </c>
       <c r="D50" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>CLOSED_BOOK_RECALL</t>
         </is>
       </c>
       <c r="E50" s="25" t="inlineStr">
         <is>
-          <t>QB4_C#q10</t>
-        </is>
-      </c>
-      <c r="F50" s="26" t="inlineStr">
-        <is>
-          <t>NC vs MNC?</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="26" t="inlineStr"/>
       <c r="G50" s="26" t="inlineStr">
         <is>
-          <t>Chain A step 4. Short question, high failure rate.</t>
+          <t>Delayed recall is the point of the session, not the reading.</t>
         </is>
       </c>
       <c r="H50" s="25" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I50" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J50" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K50" s="25" t="inlineStr">
@@ -4859,9 +4879,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L50" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4876,42 +4896,38 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>D03-S02 — Oral core — the ISM audit chain</t>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
         </is>
       </c>
       <c r="D51" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>CLOSED_BOOK_RECALL</t>
         </is>
       </c>
       <c r="E51" s="25" t="inlineStr">
         <is>
-          <t>QB4_A#q3</t>
-        </is>
-      </c>
-      <c r="F51" s="26" t="inlineStr">
-        <is>
-          <t>An ISM non-conformity or deficiency is raised during an audit. What are the timescales for corrective action and how does the process work?</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="26" t="inlineStr"/>
       <c r="G51" s="26" t="inlineStr">
         <is>
-          <t>Chain A step 5 — corrective action WITH the timescales.</t>
+          <t>The list is the index to every ISM follow-up.</t>
         </is>
       </c>
       <c r="H51" s="25" t="inlineStr">
         <is>
-          <t>Nair, Srivastava</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I51" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J51" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K51" s="25" t="inlineStr">
@@ -4919,9 +4935,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L51" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4936,42 +4952,38 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>D03-S02 — Oral core — the ISM audit chain</t>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
         </is>
       </c>
       <c r="D52" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>CLOSED_BOOK_RECALL</t>
         </is>
       </c>
       <c r="E52" s="25" t="inlineStr">
         <is>
-          <t>QB4_E#q6</t>
-        </is>
-      </c>
-      <c r="F52" s="26" t="inlineStr">
-        <is>
-          <t>Master's review and authority under ISM Code — overriding authority?</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="26" t="inlineStr"/>
       <c r="G52" s="26" t="inlineStr">
         <is>
-          <t>Chain A step 6 — master's review. Three examiners.</t>
+          <t>The most examiner-broad question in D03.</t>
         </is>
       </c>
       <c r="H52" s="25" t="inlineStr">
         <is>
-          <t>Nair, Simon, Srivastava</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I52" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J52" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K52" s="25" t="inlineStr">
@@ -4979,9 +4991,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L52" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4996,42 +5008,38 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>D03-S02 — Oral core — the ISM audit chain</t>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
         </is>
       </c>
       <c r="D53" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>CLOSED_BOOK_RECALL</t>
         </is>
       </c>
       <c r="E53" s="25" t="inlineStr">
         <is>
-          <t>QB4_E#q7</t>
-        </is>
-      </c>
-      <c r="F53" s="26" t="inlineStr">
-        <is>
-          <t>How is continuous improvement achieved under the ISM Code?</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="26" t="inlineStr"/>
       <c r="G53" s="26" t="inlineStr">
         <is>
-          <t>Chain A terminus — the answer examiners wait for.</t>
+          <t>Session 2 opens by re-answering this cold.</t>
         </is>
       </c>
       <c r="H53" s="25" t="inlineStr">
         <is>
-          <t>Nair, Simon, Srivastava</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I53" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J53" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K53" s="25" t="inlineStr">
@@ -5039,9 +5047,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L53" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5056,42 +5064,38 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>D03-S02 — Oral core — the ISM audit chain</t>
+          <t>D03-S01 — Foundation — the ISM architecture</t>
         </is>
       </c>
       <c r="D54" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>STOP</t>
         </is>
       </c>
       <c r="E54" s="25" t="inlineStr">
         <is>
-          <t>QB4_C#q7</t>
-        </is>
-      </c>
-      <c r="F54" s="26" t="inlineStr">
-        <is>
-          <t>DOC cancellation — grounds?</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="26" t="inlineStr"/>
       <c r="G54" s="26" t="inlineStr">
         <is>
-          <t>Chain A consequence limb — what makes a DOC withdrawable.</t>
+          <t>Spacing, not volume, is what moves a 60-second answer into recall.</t>
         </is>
       </c>
       <c r="H54" s="25" t="inlineStr">
         <is>
-          <t>Srivastava</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I54" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J54" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K54" s="25" t="inlineStr">
@@ -5099,9 +5103,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L54" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L54" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5121,22 +5125,18 @@
       </c>
       <c r="D55" s="25" t="inlineStr">
         <is>
-          <t>WRITTEN_STUDY</t>
+          <t>CLOSED_BOOK_RECALL</t>
         </is>
       </c>
       <c r="E55" s="25" t="inlineStr">
         <is>
-          <t>QP2309-Q7</t>
-        </is>
-      </c>
-      <c r="F55" s="26" t="inlineStr">
-        <is>
-          <t>(a) State the difference between an audit and survey. (4) (b) State the action taken by a recognized organization carrying out ISM certification on behalf of the Administration towards handling of an ISM certificate in c</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="26" t="inlineStr"/>
       <c r="G55" s="26" t="inlineStr">
         <is>
-          <t>Audit versus survey, and RO action on ISM certificates — the written form of Chain A.</t>
+          <t>Delayed recall from Session 1 step 12.</t>
         </is>
       </c>
       <c r="H55" s="25" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="I55" s="26" t="inlineStr">
         <is>
-          <t>NEAR_REPEAT ×2 (September 2023 → April 2024)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J55" s="26" t="inlineStr">
         <is>
-          <t>TEMPORAL WATCH — law moved under this family</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K55" s="25" t="inlineStr">
@@ -5159,9 +5159,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L55" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5181,33 +5181,37 @@
       </c>
       <c r="D56" s="25" t="inlineStr">
         <is>
-          <t>BUILD_NOTE</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E56" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F56" s="26" t="inlineStr"/>
+          <t>QB4_J#q7</t>
+        </is>
+      </c>
+      <c r="F56" s="26" t="inlineStr">
+        <is>
+          <t>Difference between ISM survey and ISM audit.</t>
+        </is>
+      </c>
       <c r="G56" s="26" t="inlineStr">
         <is>
-          <t>Nothing in the corpus assembles the chain in one place, and every branch 1-3 answer leans on it.</t>
+          <t>Chain A step 2 — the D01/D03 hinge in one question.</t>
         </is>
       </c>
       <c r="H56" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Simon</t>
         </is>
       </c>
       <c r="I56" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J56" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K56" s="25" t="inlineStr">
@@ -5215,9 +5219,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L56" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L56" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -5237,33 +5241,37 @@
       </c>
       <c r="D57" s="25" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E57" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F57" s="26" t="inlineStr"/>
+          <t>QB4_A#q4</t>
+        </is>
+      </c>
+      <c r="F57" s="26" t="inlineStr">
+        <is>
+          <t>Describe the internal audit procedure under the ISM Code. Who conducts it, what is checked, and what is the outcome?</t>
+        </is>
+      </c>
       <c r="G57" s="26" t="inlineStr">
         <is>
-          <t>The chain is the unit of recall, not the individual questions.</t>
+          <t>Chain A step 3. Node 02 names internal auditing explicitly.</t>
         </is>
       </c>
       <c r="H57" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair</t>
         </is>
       </c>
       <c r="I57" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J57" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K57" s="25" t="inlineStr">
@@ -5271,9 +5279,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L57" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L57" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -5288,38 +5296,42 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>D03-S03 — Written core — fatigue and MLC</t>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
         </is>
       </c>
       <c r="D58" s="25" t="inlineStr">
         <is>
-          <t>CLOSED_BOOK_RECALL</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E58" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F58" s="26" t="inlineStr"/>
+          <t>QB4_C#q10</t>
+        </is>
+      </c>
+      <c r="F58" s="26" t="inlineStr">
+        <is>
+          <t>NC vs MNC?</t>
+        </is>
+      </c>
       <c r="G58" s="26" t="inlineStr">
         <is>
-          <t>Delayed recall from Session 2.</t>
+          <t>Chain A step 4. Short question, high failure rate.</t>
         </is>
       </c>
       <c r="H58" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Simon</t>
         </is>
       </c>
       <c r="I58" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J58" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K58" s="25" t="inlineStr">
@@ -5327,9 +5339,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L58" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L58" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5356,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>D03-S03 — Written core — fatigue and MLC</t>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
         </is>
       </c>
       <c r="D59" s="25" t="inlineStr">
@@ -5354,17 +5366,17 @@
       </c>
       <c r="E59" s="25" t="inlineStr">
         <is>
-          <t>QB4_B#q5</t>
+          <t>QB4_A#q3</t>
         </is>
       </c>
       <c r="F59" s="26" t="inlineStr">
         <is>
-          <t>What is the human element in shipping? Explain its key dimensions — navigation, safety, fatigue, communication, and organisational factors.</t>
+          <t>An ISM non-conformity or deficiency is raised during an audit. What are the timescales for corrective action and how does the process work?</t>
         </is>
       </c>
       <c r="G59" s="26" t="inlineStr">
         <is>
-          <t>Branch 4's opening answer.</t>
+          <t>Chain A step 5 — corrective action WITH the timescales.</t>
         </is>
       </c>
       <c r="H59" s="25" t="inlineStr">
@@ -5404,7 +5416,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>D03-S03 — Written core — fatigue and MLC</t>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
         </is>
       </c>
       <c r="D60" s="25" t="inlineStr">
@@ -5414,22 +5426,22 @@
       </c>
       <c r="E60" s="25" t="inlineStr">
         <is>
-          <t>QB4_A#q17</t>
+          <t>QB4_E#q6</t>
         </is>
       </c>
       <c r="F60" s="26" t="inlineStr">
         <is>
-          <t>Explain STCW Chapter VIII — Fitness for Duty, watch composition, and fatigue management.</t>
+          <t>Master's review and authority under ISM Code — overriding authority?</t>
         </is>
       </c>
       <c r="G60" s="26" t="inlineStr">
         <is>
-          <t>Directly under the 11-question written cluster. Examiner: Rajappan.</t>
+          <t>Chain A step 6 — master's review. Three examiners.</t>
         </is>
       </c>
       <c r="H60" s="25" t="inlineStr">
         <is>
-          <t>Rajappan</t>
+          <t>Nair, Simon, Srivastava</t>
         </is>
       </c>
       <c r="I60" s="26" t="inlineStr">
@@ -5464,7 +5476,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>D03-S03 — Written core — fatigue and MLC</t>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
         </is>
       </c>
       <c r="D61" s="25" t="inlineStr">
@@ -5474,22 +5486,22 @@
       </c>
       <c r="E61" s="25" t="inlineStr">
         <is>
-          <t>QB4_A#q15</t>
+          <t>QB4_E#q7</t>
         </is>
       </c>
       <c r="F61" s="26" t="inlineStr">
         <is>
-          <t>What are the hours of work and rest limits under MLC 2006 and STCW, and how is rest splitting governed?</t>
+          <t>How is continuous improvement achieved under the ISM Code?</t>
         </is>
       </c>
       <c r="G61" s="26" t="inlineStr">
         <is>
-          <t>The numbers examiners test.</t>
+          <t>Chain A terminus — the answer examiners wait for.</t>
         </is>
       </c>
       <c r="H61" s="25" t="inlineStr">
         <is>
-          <t>Nair, Srivastava</t>
+          <t>Nair, Simon, Srivastava</t>
         </is>
       </c>
       <c r="I61" s="26" t="inlineStr">
@@ -5524,7 +5536,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>D03-S03 — Written core — fatigue and MLC</t>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
         </is>
       </c>
       <c r="D62" s="25" t="inlineStr">
@@ -5534,22 +5546,22 @@
       </c>
       <c r="E62" s="25" t="inlineStr">
         <is>
-          <t>QB4_A#q14</t>
+          <t>QB4_C#q7</t>
         </is>
       </c>
       <c r="F62" s="26" t="inlineStr">
         <is>
-          <t>Explain DMLC Part I and Part II under MLC 2006 — who issues each and what do they contain?</t>
+          <t>DOC cancellation — grounds?</t>
         </is>
       </c>
       <c r="G62" s="26" t="inlineStr">
         <is>
-          <t>The most-confused point in the MLC cluster.</t>
+          <t>Chain A consequence limb — what makes a DOC withdrawable.</t>
         </is>
       </c>
       <c r="H62" s="25" t="inlineStr">
         <is>
-          <t>Nair, Srivastava</t>
+          <t>Srivastava</t>
         </is>
       </c>
       <c r="I62" s="26" t="inlineStr">
@@ -5584,7 +5596,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>D03-S03 — Written core — fatigue and MLC</t>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
         </is>
       </c>
       <c r="D63" s="25" t="inlineStr">
@@ -5594,17 +5606,17 @@
       </c>
       <c r="E63" s="25" t="inlineStr">
         <is>
-          <t>QP2601-Q9</t>
+          <t>QP2309-Q7</t>
         </is>
       </c>
       <c r="F63" s="26" t="inlineStr">
         <is>
-          <t>A). How is Human Element issue addressed in STCW code. B). Discuss the IMO guidance on fatigue mitigation and management on board ships</t>
+          <t>(a) State the difference between an audit and survey. (4) (b) State the action taken by a recognized organization carrying out ISM certification on behalf of the Administration towards handling of an ISM certificate in c</t>
         </is>
       </c>
       <c r="G63" s="26" t="inlineStr">
         <is>
-          <t>Most recent occurrence of the largest family in D03 — the current wording.</t>
+          <t>Audit versus survey, and RO action on ISM certificates — the written form of Chain A.</t>
         </is>
       </c>
       <c r="H63" s="25" t="inlineStr">
@@ -5614,7 +5626,7 @@
       </c>
       <c r="I63" s="26" t="inlineStr">
         <is>
-          <t>NEAR_REPEAT ×8 (January 2023 → April 2026)</t>
+          <t>NEAR_REPEAT ×2 (September 2023 → April 2024)</t>
         </is>
       </c>
       <c r="J63" s="26" t="inlineStr">
@@ -5644,27 +5656,23 @@
       </c>
       <c r="C64" s="26" t="inlineStr">
         <is>
-          <t>D03-S03 — Written core — fatigue and MLC</t>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
         </is>
       </c>
       <c r="D64" s="25" t="inlineStr">
         <is>
-          <t>WRITTEN_STUDY</t>
+          <t>BUILD_NOTE</t>
         </is>
       </c>
       <c r="E64" s="25" t="inlineStr">
         <is>
-          <t>QP2301-Q8</t>
-        </is>
-      </c>
-      <c r="F64" s="26" t="inlineStr">
-        <is>
-          <t>A). How is Human Element issue addressed in STCW code. B). Discuss the IMO guidance on fatigue mitigation and management on board ships</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="26" t="inlineStr"/>
       <c r="G64" s="26" t="inlineStr">
         <is>
-          <t>Read against QP2601-Q9 to see what the family does and does not change.</t>
+          <t>Nothing in the corpus assembles the chain in one place, and every branch 1-3 answer leans on it.</t>
         </is>
       </c>
       <c r="H64" s="25" t="inlineStr">
@@ -5674,12 +5682,12 @@
       </c>
       <c r="I64" s="26" t="inlineStr">
         <is>
-          <t>NEAR_REPEAT ×8 (January 2023 → April 2026)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J64" s="26" t="inlineStr">
         <is>
-          <t>TEMPORAL WATCH — law moved under this family</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K64" s="25" t="inlineStr">
@@ -5687,9 +5695,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L64" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5704,27 +5712,23 @@
       </c>
       <c r="C65" s="26" t="inlineStr">
         <is>
-          <t>D03-S03 — Written core — fatigue and MLC</t>
+          <t>D03-S02 — Oral core — the ISM audit chain</t>
         </is>
       </c>
       <c r="D65" s="25" t="inlineStr">
         <is>
-          <t>WRITTEN_STUDY</t>
+          <t>STOP</t>
         </is>
       </c>
       <c r="E65" s="25" t="inlineStr">
         <is>
-          <t>QP2302-Q8</t>
-        </is>
-      </c>
-      <c r="F65" s="26" t="inlineStr">
-        <is>
-          <t>Referring to the Maritime Labour Convention (MLC) 2006, discuss: a) Flag State &amp; Port State responsibilities. b) On-board &amp; On-shore Compliant Procedures. c) Detainable deficiencies. d) Grievance Redressal Mechanisms for</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="26" t="inlineStr"/>
       <c r="G65" s="26" t="inlineStr">
         <is>
-          <t>The widest MLC answer held — flag and port State duties, complaint procedure, detainable deficiencies, Indian grievance redressal.</t>
+          <t>The chain is the unit of recall, not the individual questions.</t>
         </is>
       </c>
       <c r="H65" s="25" t="inlineStr">
@@ -5734,12 +5738,12 @@
       </c>
       <c r="I65" s="26" t="inlineStr">
         <is>
-          <t>NEAR_REPEAT ×4 (November 2022 → July 2024)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J65" s="26" t="inlineStr">
         <is>
-          <t>Not on temporal watch</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K65" s="25" t="inlineStr">
@@ -5747,9 +5751,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L65" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5773,7 @@
       </c>
       <c r="D66" s="25" t="inlineStr">
         <is>
-          <t>BUILD_NOTE</t>
+          <t>CLOSED_BOOK_RECALL</t>
         </is>
       </c>
       <c r="E66" s="25" t="inlineStr">
@@ -5780,7 +5784,7 @@
       <c r="F66" s="26" t="inlineStr"/>
       <c r="G66" s="26" t="inlineStr">
         <is>
-          <t>Asked eleven times in writing. The numbers must be exact.</t>
+          <t>Delayed recall from Session 2.</t>
         </is>
       </c>
       <c r="H66" s="25" t="inlineStr">
@@ -5825,33 +5829,37 @@
       </c>
       <c r="D67" s="25" t="inlineStr">
         <is>
-          <t>BUILD_NOTE</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E67" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F67" s="26" t="inlineStr"/>
+          <t>QB4_B#q5</t>
+        </is>
+      </c>
+      <c r="F67" s="26" t="inlineStr">
+        <is>
+          <t>What is the human element in shipping? Explain its key dimensions — navigation, safety, fatigue, communication, and organisational factors.</t>
+        </is>
+      </c>
       <c r="G67" s="26" t="inlineStr">
         <is>
-          <t>The single most confused point in the MLC cluster.</t>
+          <t>Branch 4's opening answer.</t>
         </is>
       </c>
       <c r="H67" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Srivastava</t>
         </is>
       </c>
       <c r="I67" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J67" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K67" s="25" t="inlineStr">
@@ -5859,9 +5867,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L67" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L67" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -5881,33 +5889,37 @@
       </c>
       <c r="D68" s="25" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E68" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="26" t="inlineStr"/>
+          <t>QB4_A#q17</t>
+        </is>
+      </c>
+      <c r="F68" s="26" t="inlineStr">
+        <is>
+          <t>Explain STCW Chapter VIII — Fitness for Duty, watch composition, and fatigue management.</t>
+        </is>
+      </c>
       <c r="G68" s="26" t="inlineStr">
         <is>
-          <t>Numbers decay fastest; space them.</t>
+          <t>Directly under the 11-question written cluster. Examiner: Rajappan.</t>
         </is>
       </c>
       <c r="H68" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajappan</t>
         </is>
       </c>
       <c r="I68" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J68" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K68" s="25" t="inlineStr">
@@ -5915,9 +5927,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L68" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L68" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -5932,38 +5944,42 @@
       </c>
       <c r="C69" s="26" t="inlineStr">
         <is>
-          <t>D03-S04 — Human element, communication and risk</t>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
         </is>
       </c>
       <c r="D69" s="25" t="inlineStr">
         <is>
-          <t>CLOSED_BOOK_RECALL</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E69" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="26" t="inlineStr"/>
+          <t>QB4_A#q15</t>
+        </is>
+      </c>
+      <c r="F69" s="26" t="inlineStr">
+        <is>
+          <t>What are the hours of work and rest limits under MLC 2006 and STCW, and how is rest splitting governed?</t>
+        </is>
+      </c>
       <c r="G69" s="26" t="inlineStr">
         <is>
-          <t>Delayed recall from Session 3.</t>
+          <t>The numbers examiners test.</t>
         </is>
       </c>
       <c r="H69" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Srivastava</t>
         </is>
       </c>
       <c r="I69" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J69" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K69" s="25" t="inlineStr">
@@ -5971,9 +5987,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L69" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L69" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -5988,7 +6004,7 @@
       </c>
       <c r="C70" s="26" t="inlineStr">
         <is>
-          <t>D03-S04 — Human element, communication and risk</t>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
         </is>
       </c>
       <c r="D70" s="25" t="inlineStr">
@@ -5998,17 +6014,17 @@
       </c>
       <c r="E70" s="25" t="inlineStr">
         <is>
-          <t>QB4_B#q9</t>
+          <t>QB4_A#q14</t>
         </is>
       </c>
       <c r="F70" s="26" t="inlineStr">
         <is>
-          <t>Explain Maslow's Hierarchy of Needs and how it applies to crew motivation onboard.</t>
+          <t>Explain DMLC Part I and Part II under MLC 2006 — who issues each and what do they contain?</t>
         </is>
       </c>
       <c r="G70" s="26" t="inlineStr">
         <is>
-          <t>Branch 8, and the answer donor behind QP2512-Q4.</t>
+          <t>The most-confused point in the MLC cluster.</t>
         </is>
       </c>
       <c r="H70" s="25" t="inlineStr">
@@ -6048,42 +6064,42 @@
       </c>
       <c r="C71" s="26" t="inlineStr">
         <is>
-          <t>D03-S04 — Human element, communication and risk</t>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
         </is>
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>WRITTEN_STUDY</t>
         </is>
       </c>
       <c r="E71" s="25" t="inlineStr">
         <is>
-          <t>QB5_E#q2</t>
+          <t>QP2601-Q9</t>
         </is>
       </c>
       <c r="F71" s="26" t="inlineStr">
         <is>
-          <t>Hazard vs risk — what is the difference? Give examples from shipboard context.</t>
+          <t>A). How is Human Element issue addressed in STCW code. B). Discuss the IMO guidance on fatigue mitigation and management on board ships</t>
         </is>
       </c>
       <c r="G71" s="26" t="inlineStr">
         <is>
-          <t>Branch 10's gateway. Three examiners: Paul, Senthil, Simon.</t>
+          <t>Most recent occurrence of the largest family in D03 — the current wording.</t>
         </is>
       </c>
       <c r="H71" s="25" t="inlineStr">
         <is>
-          <t>Paul, Senthil, Simon</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>NEAR_REPEAT ×8 (January 2023 → April 2026)</t>
         </is>
       </c>
       <c r="J71" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>TEMPORAL WATCH — law moved under this family</t>
         </is>
       </c>
       <c r="K71" s="25" t="inlineStr">
@@ -6108,7 +6124,7 @@
       </c>
       <c r="C72" s="26" t="inlineStr">
         <is>
-          <t>D03-S04 — Human element, communication and risk</t>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
         </is>
       </c>
       <c r="D72" s="25" t="inlineStr">
@@ -6118,17 +6134,17 @@
       </c>
       <c r="E72" s="25" t="inlineStr">
         <is>
-          <t>QP2608-Q8</t>
+          <t>QP2301-Q8</t>
         </is>
       </c>
       <c r="F72" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A). How is Human Element issue addressed in STCW code. B). Discuss the IMO guidance on fatigue mitigation and management on board ships</t>
         </is>
       </c>
       <c r="G72" s="26" t="inlineStr">
         <is>
-          <t>Adjudicated this session: the question belongs to two families because its limbs do. "Q8 is a repeat" is false for the larger limb.</t>
+          <t>Read against QP2601-Q9 to see what the family does and does not change.</t>
         </is>
       </c>
       <c r="H72" s="25" t="inlineStr">
@@ -6138,12 +6154,12 @@
       </c>
       <c r="I72" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NEAR_REPEAT ×8 (January 2023 → April 2026)</t>
         </is>
       </c>
       <c r="J72" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TEMPORAL WATCH — law moved under this family</t>
         </is>
       </c>
       <c r="K72" s="25" t="inlineStr">
@@ -6168,7 +6184,7 @@
       </c>
       <c r="C73" s="26" t="inlineStr">
         <is>
-          <t>D03-S04 — Human element, communication and risk</t>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
         </is>
       </c>
       <c r="D73" s="25" t="inlineStr">
@@ -6178,17 +6194,17 @@
       </c>
       <c r="E73" s="25" t="inlineStr">
         <is>
-          <t>QP2606-Q5</t>
+          <t>QP2302-Q8</t>
         </is>
       </c>
       <c r="F73" s="26" t="inlineStr">
         <is>
-          <t>a) Examine the role of the Safety Management System (SMS) in the implementation of the ISM Code, highlighting its components and significance of continuous improvement. (8) b) Examine the evolution of the ISM Code in res</t>
+          <t>Referring to the Maritime Labour Convention (MLC) 2006, discuss: a) Flag State &amp; Port State responsibilities. b) On-board &amp; On-shore Compliant Procedures. c) Detainable deficiencies. d) Grievance Redressal Mechanisms for</t>
         </is>
       </c>
       <c r="G73" s="26" t="inlineStr">
         <is>
-          <t>The Code evolution including MSC.428(98) cyber risk — the currentness limb of branch 1.</t>
+          <t>The widest MLC answer held — flag and port State duties, complaint procedure, detainable deficiencies, Indian grievance redressal.</t>
         </is>
       </c>
       <c r="H73" s="25" t="inlineStr">
@@ -6198,7 +6214,7 @@
       </c>
       <c r="I73" s="26" t="inlineStr">
         <is>
-          <t>EXACT_REPEAT ×3 (December 2023 → June 2026)</t>
+          <t>NEAR_REPEAT ×4 (November 2022 → July 2024)</t>
         </is>
       </c>
       <c r="J73" s="26" t="inlineStr">
@@ -6228,7 +6244,7 @@
       </c>
       <c r="C74" s="26" t="inlineStr">
         <is>
-          <t>D03-S04 — Human element, communication and risk</t>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
         </is>
       </c>
       <c r="D74" s="25" t="inlineStr">
@@ -6244,7 +6260,7 @@
       <c r="F74" s="26" t="inlineStr"/>
       <c r="G74" s="26" t="inlineStr">
         <is>
-          <t>Two written questions test the distinctions directly.</t>
+          <t>Asked eleven times in writing. The numbers must be exact.</t>
         </is>
       </c>
       <c r="H74" s="25" t="inlineStr">
@@ -6284,7 +6300,7 @@
       </c>
       <c r="C75" s="26" t="inlineStr">
         <is>
-          <t>D03-S04 — Human element, communication and risk</t>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
         </is>
       </c>
       <c r="D75" s="25" t="inlineStr">
@@ -6300,7 +6316,7 @@
       <c r="F75" s="26" t="inlineStr"/>
       <c r="G75" s="26" t="inlineStr">
         <is>
-          <t>ALARP appears in four written questions and the tools are asked by name.</t>
+          <t>The single most confused point in the MLC cluster.</t>
         </is>
       </c>
       <c r="H75" s="25" t="inlineStr">
@@ -6340,7 +6356,7 @@
       </c>
       <c r="C76" s="26" t="inlineStr">
         <is>
-          <t>D03-S04 — Human element, communication and risk</t>
+          <t>D03-S03 — Written core — fatigue and MLC</t>
         </is>
       </c>
       <c r="D76" s="25" t="inlineStr">
@@ -6356,7 +6372,7 @@
       <c r="F76" s="26" t="inlineStr"/>
       <c r="G76" s="26" t="inlineStr">
         <is>
-          <t>Sessions 1-4 read what exists; Session 5 writes what does not.</t>
+          <t>Numbers decay fastest; space them.</t>
         </is>
       </c>
       <c r="H76" s="25" t="inlineStr">
@@ -6396,42 +6412,38 @@
       </c>
       <c r="C77" s="26" t="inlineStr">
         <is>
-          <t>D03-S05 — Gaps and closed-book mock</t>
+          <t>D03-S04 — Human element, communication and risk</t>
         </is>
       </c>
       <c r="D77" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>CLOSED_BOOK_RECALL</t>
         </is>
       </c>
       <c r="E77" s="25" t="inlineStr">
         <is>
-          <t>QB4_E#q8</t>
-        </is>
-      </c>
-      <c r="F77" s="26" t="inlineStr">
-        <is>
-          <t>PSC — appeal process, codes involved, and process after detention?</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="26" t="inlineStr"/>
       <c r="G77" s="26" t="inlineStr">
         <is>
-          <t>B-priority, three examiners — PSC appeal and post-detention process.</t>
+          <t>Delayed recall from Session 3.</t>
         </is>
       </c>
       <c r="H77" s="25" t="inlineStr">
         <is>
-          <t>Nair, Simon, Srivastava</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I77" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J77" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K77" s="25" t="inlineStr">
@@ -6439,9 +6451,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L77" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6468,7 @@
       </c>
       <c r="C78" s="26" t="inlineStr">
         <is>
-          <t>D03-S05 — Gaps and closed-book mock</t>
+          <t>D03-S04 — Human element, communication and risk</t>
         </is>
       </c>
       <c r="D78" s="25" t="inlineStr">
@@ -6466,22 +6478,22 @@
       </c>
       <c r="E78" s="25" t="inlineStr">
         <is>
-          <t>QB4_C#q6</t>
+          <t>QB4_B#q9</t>
         </is>
       </c>
       <c r="F78" s="26" t="inlineStr">
         <is>
-          <t>MLC 2006 — 5 Titles and flag/port state duties?</t>
+          <t>Explain Maslow's Hierarchy of Needs and how it applies to crew motivation onboard.</t>
         </is>
       </c>
       <c r="G78" s="26" t="inlineStr">
         <is>
-          <t>The five MLC Titles — the frame for the whole MLC cluster.</t>
+          <t>Branch 8, and the answer donor behind QP2512-Q4.</t>
         </is>
       </c>
       <c r="H78" s="25" t="inlineStr">
         <is>
-          <t>Rajappan</t>
+          <t>Nair, Srivastava</t>
         </is>
       </c>
       <c r="I78" s="26" t="inlineStr">
@@ -6516,7 +6528,7 @@
       </c>
       <c r="C79" s="26" t="inlineStr">
         <is>
-          <t>D03-S05 — Gaps and closed-book mock</t>
+          <t>D03-S04 — Human element, communication and risk</t>
         </is>
       </c>
       <c r="D79" s="25" t="inlineStr">
@@ -6526,22 +6538,22 @@
       </c>
       <c r="E79" s="25" t="inlineStr">
         <is>
-          <t>QB5_A#q11</t>
+          <t>QB5_E#q2</t>
         </is>
       </c>
       <c r="F79" s="26" t="inlineStr">
         <is>
-          <t>Risk Assessment — How to Carry Out. How to Decide Risk Category.</t>
+          <t>Hazard vs risk — what is the difference? Give examples from shipboard context.</t>
         </is>
       </c>
       <c r="G79" s="26" t="inlineStr">
         <is>
-          <t>How to actually carry out a risk assessment and decide a risk category.</t>
+          <t>Branch 10's gateway. Three examiners: Paul, Senthil, Simon.</t>
         </is>
       </c>
       <c r="H79" s="25" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Paul, Senthil, Simon</t>
         </is>
       </c>
       <c r="I79" s="26" t="inlineStr">
@@ -6576,23 +6588,27 @@
       </c>
       <c r="C80" s="26" t="inlineStr">
         <is>
-          <t>D03-S05 — Gaps and closed-book mock</t>
+          <t>D03-S04 — Human element, communication and risk</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>BUILD_NOTE</t>
+          <t>WRITTEN_STUDY</t>
         </is>
       </c>
       <c r="E80" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="26" t="inlineStr"/>
+          <t>QP2608-Q8</t>
+        </is>
+      </c>
+      <c r="F80" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G80" s="26" t="inlineStr">
         <is>
-          <t>Corpus coverage is 0 orals, 0 examiners. "Standing orders" and "night order book" return ZERO hits anywhere in the corpus — the clearest content gap in D03.</t>
+          <t>Adjudicated this session: the question belongs to two families because its limbs do. "Q8 is a repeat" is false for the larger limb.</t>
         </is>
       </c>
       <c r="H80" s="25" t="inlineStr">
@@ -6615,9 +6631,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L80" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L80" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -6632,23 +6648,27 @@
       </c>
       <c r="C81" s="26" t="inlineStr">
         <is>
-          <t>D03-S05 — Gaps and closed-book mock</t>
+          <t>D03-S04 — Human element, communication and risk</t>
         </is>
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>BUILD_NOTE</t>
+          <t>WRITTEN_STUDY</t>
         </is>
       </c>
       <c r="E81" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="26" t="inlineStr"/>
+          <t>QP2606-Q5</t>
+        </is>
+      </c>
+      <c r="F81" s="26" t="inlineStr">
+        <is>
+          <t>a) Examine the role of the Safety Management System (SMS) in the implementation of the ISM Code, highlighting its components and significance of continuous improvement. (8) b) Examine the evolution of the ISM Code in res</t>
+        </is>
+      </c>
       <c r="G81" s="26" t="inlineStr">
         <is>
-          <t>One oral, one examiner. "Low BN" returns zero hits despite being named in the official item.</t>
+          <t>The Code evolution including MSC.428(98) cyber risk — the currentness limb of branch 1.</t>
         </is>
       </c>
       <c r="H81" s="25" t="inlineStr">
@@ -6658,12 +6678,12 @@
       </c>
       <c r="I81" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>EXACT_REPEAT ×3 (December 2023 → June 2026)</t>
         </is>
       </c>
       <c r="J81" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Not on temporal watch</t>
         </is>
       </c>
       <c r="K81" s="25" t="inlineStr">
@@ -6671,9 +6691,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L81" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L81" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6708,12 @@
       </c>
       <c r="C82" s="26" t="inlineStr">
         <is>
-          <t>D03-S05 — Gaps and closed-book mock</t>
+          <t>D03-S04 — Human element, communication and risk</t>
         </is>
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>MOCK</t>
+          <t>BUILD_NOTE</t>
         </is>
       </c>
       <c r="E82" s="25" t="inlineStr">
@@ -6704,7 +6724,7 @@
       <c r="F82" s="26" t="inlineStr"/>
       <c r="G82" s="26" t="inlineStr">
         <is>
-          <t>The completion test is the exit condition for the topic, not a warm-up.</t>
+          <t>Two written questions test the distinctions directly.</t>
         </is>
       </c>
       <c r="H82" s="25" t="inlineStr">
@@ -6744,12 +6764,12 @@
       </c>
       <c r="C83" s="26" t="inlineStr">
         <is>
-          <t>D03-S05 — Gaps and closed-book mock</t>
+          <t>D03-S04 — Human element, communication and risk</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>BUILD_NOTE</t>
         </is>
       </c>
       <c r="E83" s="25" t="inlineStr">
@@ -6760,7 +6780,7 @@
       <c r="F83" s="26" t="inlineStr"/>
       <c r="G83" s="26" t="inlineStr">
         <is>
-          <t>Progress is an input to the workbook, never an output.</t>
+          <t>ALARP appears in four written questions and the tools are asked by name.</t>
         </is>
       </c>
       <c r="H83" s="25" t="inlineStr">
@@ -6795,17 +6815,17 @@
       </c>
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="C84" s="26" t="inlineStr">
         <is>
-          <t>D02-S01 — Foundation — principles and types of loss</t>
+          <t>D03-S04 — Human element, communication and risk</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>READ_SKELETON</t>
+          <t>STOP</t>
         </is>
       </c>
       <c r="E84" s="25" t="inlineStr">
@@ -6816,7 +6836,7 @@
       <c r="F84" s="26" t="inlineStr"/>
       <c r="G84" s="26" t="inlineStr">
         <is>
-          <t>Almost every D02 question is a relationship between two concepts; the skeleton is the pair list.</t>
+          <t>Sessions 1-4 read what exists; Session 5 writes what does not.</t>
         </is>
       </c>
       <c r="H84" s="25" t="inlineStr">
@@ -6851,37 +6871,37 @@
       </c>
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="C85" s="26" t="inlineStr">
         <is>
-          <t>D02-S01 — Foundation — principles and types of loss</t>
+          <t>D03-S05 — Gaps and closed-book mock</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>ORAL_COLD_ATTEMPT</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E85" s="25" t="inlineStr">
         <is>
-          <t>QB9_C#q5</t>
+          <t>QB4_E#q8</t>
         </is>
       </c>
       <c r="F85" s="26" t="inlineStr">
         <is>
-          <t>Insurance principles — list all principles of marine insurance and explain each.</t>
+          <t>PSC — appeal process, codes involved, and process after detention?</t>
         </is>
       </c>
       <c r="G85" s="26" t="inlineStr">
         <is>
-          <t>Branch 1 entire. Three examiners: Nair, Rajappan, Simon.</t>
+          <t>B-priority, three examiners — PSC appeal and post-detention process.</t>
         </is>
       </c>
       <c r="H85" s="25" t="inlineStr">
         <is>
-          <t>Nair, Rajappan, Simon</t>
+          <t>Nair, Simon, Srivastava</t>
         </is>
       </c>
       <c r="I85" s="26" t="inlineStr">
@@ -6911,37 +6931,37 @@
       </c>
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="C86" s="26" t="inlineStr">
         <is>
-          <t>D02-S01 — Foundation — principles and types of loss</t>
+          <t>D03-S05 — Gaps and closed-book mock</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>ORAL_COLD_ATTEMPT</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E86" s="25" t="inlineStr">
         <is>
-          <t>QB1_B#q20</t>
+          <t>QB4_C#q6</t>
         </is>
       </c>
       <c r="F86" s="26" t="inlineStr">
         <is>
-          <t>What is subrogation in the context of marine insurance/P&amp;I claims?</t>
+          <t>MLC 2006 — 5 Titles and flag/port state duties?</t>
         </is>
       </c>
       <c r="G86" s="26" t="inlineStr">
         <is>
-          <t>Branch 1's most-missed principle. Three examiners.</t>
+          <t>The five MLC Titles — the frame for the whole MLC cluster.</t>
         </is>
       </c>
       <c r="H86" s="25" t="inlineStr">
         <is>
-          <t>Nair, Rajappan, Simon</t>
+          <t>Rajappan</t>
         </is>
       </c>
       <c r="I86" s="26" t="inlineStr">
@@ -6971,37 +6991,37 @@
       </c>
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="C87" s="26" t="inlineStr">
         <is>
-          <t>D02-S01 — Foundation — principles and types of loss</t>
+          <t>D03-S05 — Gaps and closed-book mock</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>ORAL_COLD_ATTEMPT</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E87" s="25" t="inlineStr">
         <is>
-          <t>QB9_C#q1</t>
+          <t>QB5_A#q11</t>
         </is>
       </c>
       <c r="F87" s="26" t="inlineStr">
         <is>
-          <t>Constructive total loss — define and explain the criteria for declaring CTL in marine insurance.</t>
+          <t>Risk Assessment — How to Carry Out. How to Decide Risk Category.</t>
         </is>
       </c>
       <c r="G87" s="26" t="inlineStr">
         <is>
-          <t>Branch 3 — the CTL test, with the numbers.</t>
+          <t>How to actually carry out a risk assessment and decide a risk category.</t>
         </is>
       </c>
       <c r="H87" s="25" t="inlineStr">
         <is>
-          <t>Srivastava</t>
+          <t>Simon</t>
         </is>
       </c>
       <c r="I87" s="26" t="inlineStr">
@@ -7031,47 +7051,43 @@
       </c>
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="C88" s="26" t="inlineStr">
         <is>
-          <t>D02-S01 — Foundation — principles and types of loss</t>
+          <t>D03-S05 — Gaps and closed-book mock</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>BUILD_NOTE</t>
         </is>
       </c>
       <c r="E88" s="25" t="inlineStr">
         <is>
-          <t>QB9_C#q5</t>
-        </is>
-      </c>
-      <c r="F88" s="26" t="inlineStr">
-        <is>
-          <t>Insurance principles — list all principles of marine insurance and explain each.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" s="26" t="inlineStr"/>
       <c r="G88" s="26" t="inlineStr">
         <is>
-          <t>Branch 1.</t>
+          <t>Corpus coverage is 0 orals, 0 examiners. "Standing orders" and "night order book" return ZERO hits anywhere in the corpus — the clearest content gap in D03.</t>
         </is>
       </c>
       <c r="H88" s="25" t="inlineStr">
         <is>
-          <t>Nair, Rajappan, Simon</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I88" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J88" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K88" s="25" t="inlineStr">
@@ -7079,9 +7095,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L88" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L88" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7091,47 +7107,43 @@
       </c>
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="C89" s="26" t="inlineStr">
         <is>
-          <t>D02-S01 — Foundation — principles and types of loss</t>
+          <t>D03-S05 — Gaps and closed-book mock</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>BUILD_NOTE</t>
         </is>
       </c>
       <c r="E89" s="25" t="inlineStr">
         <is>
-          <t>QB1_B#q20</t>
-        </is>
-      </c>
-      <c r="F89" s="26" t="inlineStr">
-        <is>
-          <t>What is subrogation in the context of marine insurance/P&amp;I claims?</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F89" s="26" t="inlineStr"/>
       <c r="G89" s="26" t="inlineStr">
         <is>
-          <t>Subrogation vs contribution is a standard follow-up pair.</t>
+          <t>One oral, one examiner. "Low BN" returns zero hits despite being named in the official item.</t>
         </is>
       </c>
       <c r="H89" s="25" t="inlineStr">
         <is>
-          <t>Nair, Rajappan, Simon</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I89" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J89" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K89" s="25" t="inlineStr">
@@ -7139,9 +7151,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L89" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L89" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7151,47 +7163,43 @@
       </c>
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="C90" s="26" t="inlineStr">
         <is>
-          <t>D02-S01 — Foundation — principles and types of loss</t>
+          <t>D03-S05 — Gaps and closed-book mock</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>MOCK</t>
         </is>
       </c>
       <c r="E90" s="25" t="inlineStr">
         <is>
-          <t>QB9_C#q1</t>
-        </is>
-      </c>
-      <c r="F90" s="26" t="inlineStr">
-        <is>
-          <t>Constructive total loss — define and explain the criteria for declaring CTL in marine insurance.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F90" s="26" t="inlineStr"/>
       <c r="G90" s="26" t="inlineStr">
         <is>
-          <t>CTL is the gateway to the whole loss-classification tree.</t>
+          <t>The completion test is the exit condition for the topic, not a warm-up.</t>
         </is>
       </c>
       <c r="H90" s="25" t="inlineStr">
         <is>
-          <t>Srivastava</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I90" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J90" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K90" s="25" t="inlineStr">
@@ -7199,9 +7207,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L90" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L90" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7211,32 +7219,28 @@
       </c>
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="C91" s="26" t="inlineStr">
         <is>
-          <t>D02-S01 — Foundation — principles and types of loss</t>
+          <t>D03-S05 — Gaps and closed-book mock</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>WRITTEN_STUDY</t>
+          <t>STOP</t>
         </is>
       </c>
       <c r="E91" s="25" t="inlineStr">
         <is>
-          <t>QP2512-Q3</t>
-        </is>
-      </c>
-      <c r="F91" s="26" t="inlineStr">
-        <is>
-          <t>Discuss the principles of Marine Insurance. Explain each of the principle with suitable examples.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" s="26" t="inlineStr"/>
       <c r="G91" s="26" t="inlineStr">
         <is>
-          <t>Branch 1 in a single answer.</t>
+          <t>Progress is an input to the workbook, never an output.</t>
         </is>
       </c>
       <c r="H91" s="25" t="inlineStr">
@@ -7246,12 +7250,12 @@
       </c>
       <c r="I91" s="26" t="inlineStr">
         <is>
-          <t>EXACT_REPEAT ×2 (March 2021 → December 2025)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J91" s="26" t="inlineStr">
         <is>
-          <t>Not on temporal watch</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K91" s="25" t="inlineStr">
@@ -7259,9 +7263,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L91" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L91" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7285,7 @@
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>CLOSED_BOOK_RECALL</t>
+          <t>READ_SKELETON</t>
         </is>
       </c>
       <c r="E92" s="25" t="inlineStr">
@@ -7292,7 +7296,7 @@
       <c r="F92" s="26" t="inlineStr"/>
       <c r="G92" s="26" t="inlineStr">
         <is>
-          <t>Everything else in D02 is built on these.</t>
+          <t>Almost every D02 question is a relationship between two concepts; the skeleton is the pair list.</t>
         </is>
       </c>
       <c r="H92" s="25" t="inlineStr">
@@ -7337,33 +7341,37 @@
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>CLOSED_BOOK_RECALL</t>
+          <t>ORAL_COLD_ATTEMPT</t>
         </is>
       </c>
       <c r="E93" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F93" s="26" t="inlineStr"/>
+          <t>QB9_C#q5</t>
+        </is>
+      </c>
+      <c r="F93" s="26" t="inlineStr">
+        <is>
+          <t>Insurance principles — list all principles of marine insurance and explain each.</t>
+        </is>
+      </c>
       <c r="G93" s="26" t="inlineStr">
         <is>
-          <t>The timing point separates a memorised list from an understood one.</t>
+          <t>Branch 1 entire. Three examiners: Nair, Rajappan, Simon.</t>
         </is>
       </c>
       <c r="H93" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Rajappan, Simon</t>
         </is>
       </c>
       <c r="I93" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J93" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K93" s="25" t="inlineStr">
@@ -7371,9 +7379,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L93" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L93" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -7393,33 +7401,37 @@
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>CLOSED_BOOK_RECALL</t>
+          <t>ORAL_COLD_ATTEMPT</t>
         </is>
       </c>
       <c r="E94" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F94" s="26" t="inlineStr"/>
+          <t>QB1_B#q20</t>
+        </is>
+      </c>
+      <c r="F94" s="26" t="inlineStr">
+        <is>
+          <t>What is subrogation in the context of marine insurance/P&amp;I claims?</t>
+        </is>
+      </c>
       <c r="G94" s="26" t="inlineStr">
         <is>
-          <t>Session 2 opens by re-answering this cold.</t>
+          <t>Branch 1's most-missed principle. Three examiners.</t>
         </is>
       </c>
       <c r="H94" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Rajappan, Simon</t>
         </is>
       </c>
       <c r="I94" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J94" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K94" s="25" t="inlineStr">
@@ -7427,9 +7439,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L94" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L94" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -7449,33 +7461,37 @@
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>CLOSED_BOOK_RECALL</t>
+          <t>ORAL_COLD_ATTEMPT</t>
         </is>
       </c>
       <c r="E95" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F95" s="26" t="inlineStr"/>
+          <t>QB9_C#q1</t>
+        </is>
+      </c>
+      <c r="F95" s="26" t="inlineStr">
+        <is>
+          <t>Constructive total loss — define and explain the criteria for declaring CTL in marine insurance.</t>
+        </is>
+      </c>
       <c r="G95" s="26" t="inlineStr">
         <is>
-          <t>A boundary question, which is how D02 is examined.</t>
+          <t>Branch 3 — the CTL test, with the numbers.</t>
         </is>
       </c>
       <c r="H95" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Srivastava</t>
         </is>
       </c>
       <c r="I95" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J95" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K95" s="25" t="inlineStr">
@@ -7483,9 +7499,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L95" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L95" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -7505,33 +7521,37 @@
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E96" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F96" s="26" t="inlineStr"/>
+          <t>QB9_C#q5</t>
+        </is>
+      </c>
+      <c r="F96" s="26" t="inlineStr">
+        <is>
+          <t>Insurance principles — list all principles of marine insurance and explain each.</t>
+        </is>
+      </c>
       <c r="G96" s="26" t="inlineStr">
         <is>
-          <t>Spacing, not volume.</t>
+          <t>Branch 1.</t>
         </is>
       </c>
       <c r="H96" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Rajappan, Simon</t>
         </is>
       </c>
       <c r="I96" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J96" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K96" s="25" t="inlineStr">
@@ -7539,9 +7559,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L96" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L96" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -7556,38 +7576,42 @@
       </c>
       <c r="C97" s="26" t="inlineStr">
         <is>
-          <t>D02-S02 — General Average</t>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>CLOSED_BOOK_RECALL</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E97" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F97" s="26" t="inlineStr"/>
+          <t>QB1_B#q20</t>
+        </is>
+      </c>
+      <c r="F97" s="26" t="inlineStr">
+        <is>
+          <t>What is subrogation in the context of marine insurance/P&amp;I claims?</t>
+        </is>
+      </c>
       <c r="G97" s="26" t="inlineStr">
         <is>
-          <t>Delayed recall from Session 1 step 11.</t>
+          <t>Subrogation vs contribution is a standard follow-up pair.</t>
         </is>
       </c>
       <c r="H97" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Rajappan, Simon</t>
         </is>
       </c>
       <c r="I97" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J97" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K97" s="25" t="inlineStr">
@@ -7595,9 +7619,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L97" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L97" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7636,7 @@
       </c>
       <c r="C98" s="26" t="inlineStr">
         <is>
-          <t>D02-S02 — General Average</t>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
@@ -7622,22 +7646,22 @@
       </c>
       <c r="E98" s="25" t="inlineStr">
         <is>
-          <t>QB1_B#q14</t>
+          <t>QB9_C#q1</t>
         </is>
       </c>
       <c r="F98" s="26" t="inlineStr">
         <is>
-          <t>What is General Average, and what is the procedure followed onboard when GA is declared?</t>
+          <t>Constructive total loss — define and explain the criteria for declaring CTL in marine insurance.</t>
         </is>
       </c>
       <c r="G98" s="26" t="inlineStr">
         <is>
-          <t>Branch 4, and the procedural limb the CE actually owns. Three examiners.</t>
+          <t>CTL is the gateway to the whole loss-classification tree.</t>
         </is>
       </c>
       <c r="H98" s="25" t="inlineStr">
         <is>
-          <t>Nair, Rajappan, Simon</t>
+          <t>Srivastava</t>
         </is>
       </c>
       <c r="I98" s="26" t="inlineStr">
@@ -7672,42 +7696,42 @@
       </c>
       <c r="C99" s="26" t="inlineStr">
         <is>
-          <t>D02-S02 — General Average</t>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>WRITTEN_STUDY</t>
         </is>
       </c>
       <c r="E99" s="25" t="inlineStr">
         <is>
-          <t>QB1_A#q9</t>
+          <t>QP2512-Q3</t>
         </is>
       </c>
       <c r="F99" s="26" t="inlineStr">
         <is>
-          <t>General Average — Explain including act and procedure followed.</t>
+          <t>Discuss the principles of Marine Insurance. Explain each of the principle with suitable examples.</t>
         </is>
       </c>
       <c r="G99" s="26" t="inlineStr">
         <is>
-          <t>The same ask from a second file — read the two together.</t>
+          <t>Branch 1 in a single answer.</t>
         </is>
       </c>
       <c r="H99" s="25" t="inlineStr">
         <is>
-          <t>Nair, Simon</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I99" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>EXACT_REPEAT ×2 (March 2021 → December 2025)</t>
         </is>
       </c>
       <c r="J99" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>Not on temporal watch</t>
         </is>
       </c>
       <c r="K99" s="25" t="inlineStr">
@@ -7732,42 +7756,38 @@
       </c>
       <c r="C100" s="26" t="inlineStr">
         <is>
-          <t>D02-S02 — General Average</t>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>CLOSED_BOOK_RECALL</t>
         </is>
       </c>
       <c r="E100" s="25" t="inlineStr">
         <is>
-          <t>QB9_G#q7</t>
-        </is>
-      </c>
-      <c r="F100" s="26" t="inlineStr">
-        <is>
-          <t>What is the difference between General Average and Particular Average?</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="26" t="inlineStr"/>
       <c r="G100" s="26" t="inlineStr">
         <is>
-          <t>The boundary the follow-up always reaches for.</t>
+          <t>Everything else in D02 is built on these.</t>
         </is>
       </c>
       <c r="H100" s="25" t="inlineStr">
         <is>
-          <t>Nair</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I100" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J100" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K100" s="25" t="inlineStr">
@@ -7775,9 +7795,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L100" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L100" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7792,27 +7812,23 @@
       </c>
       <c r="C101" s="26" t="inlineStr">
         <is>
-          <t>D02-S02 — General Average</t>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>WRITTEN_STUDY</t>
+          <t>CLOSED_BOOK_RECALL</t>
         </is>
       </c>
       <c r="E101" s="25" t="inlineStr">
         <is>
-          <t>QP2602-Q6</t>
-        </is>
-      </c>
-      <c r="F101" s="26" t="inlineStr">
-        <is>
-          <t>a)" General average is based on certain essential features" -Discuss the statement. b) A large vessel ran aground. Main engine was used in ahead and astern directions to shake the vessel loose from the ground. Due to exc</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" s="26" t="inlineStr"/>
       <c r="G101" s="26" t="inlineStr">
         <is>
-          <t>The most recent full GA-and-refloating answer — the current wording of the cluster.</t>
+          <t>The timing point separates a memorised list from an understood one.</t>
         </is>
       </c>
       <c r="H101" s="25" t="inlineStr">
@@ -7822,12 +7838,12 @@
       </c>
       <c r="I101" s="26" t="inlineStr">
         <is>
-          <t>NEAR_REPEAT ×6 (January 2023 → February 2026)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J101" s="26" t="inlineStr">
         <is>
-          <t>Not on temporal watch</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K101" s="25" t="inlineStr">
@@ -7835,9 +7851,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L101" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L101" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7852,27 +7868,23 @@
       </c>
       <c r="C102" s="26" t="inlineStr">
         <is>
-          <t>D02-S02 — General Average</t>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>WRITTEN_STUDY</t>
+          <t>CLOSED_BOOK_RECALL</t>
         </is>
       </c>
       <c r="E102" s="25" t="inlineStr">
         <is>
-          <t>QP2304-Q3</t>
-        </is>
-      </c>
-      <c r="F102" s="26" t="inlineStr">
-        <is>
-          <t>A. What are the principles of modern salvage law? B. What is General Average, C. Explain with context to General Average, i. Entitlement; ii. Artificial; iii. Adjustment; iv. Contestation</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F102" s="26" t="inlineStr"/>
       <c r="G102" s="26" t="inlineStr">
         <is>
-          <t>Particular vs general average and the adjuster — the boundary, which is what the follow-up asks.</t>
+          <t>Session 2 opens by re-answering this cold.</t>
         </is>
       </c>
       <c r="H102" s="25" t="inlineStr">
@@ -7882,12 +7894,12 @@
       </c>
       <c r="I102" s="26" t="inlineStr">
         <is>
-          <t>NEAR_REPEAT ×8 (February 2021 → July 2026)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J102" s="26" t="inlineStr">
         <is>
-          <t>Not on temporal watch</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K102" s="25" t="inlineStr">
@@ -7895,9 +7907,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L102" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L102" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7912,12 +7924,12 @@
       </c>
       <c r="C103" s="26" t="inlineStr">
         <is>
-          <t>D02-S02 — General Average</t>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>BUILD_NOTE</t>
+          <t>CLOSED_BOOK_RECALL</t>
         </is>
       </c>
       <c r="E103" s="25" t="inlineStr">
@@ -7928,7 +7940,7 @@
       <c r="F103" s="26" t="inlineStr"/>
       <c r="G103" s="26" t="inlineStr">
         <is>
-          <t>Branches 3 to 5 all hang off it. Highest-value note in the topic.</t>
+          <t>A boundary question, which is how D02 is examined.</t>
         </is>
       </c>
       <c r="H103" s="25" t="inlineStr">
@@ -7968,12 +7980,12 @@
       </c>
       <c r="C104" s="26" t="inlineStr">
         <is>
-          <t>D02-S02 — General Average</t>
+          <t>D02-S01 — Foundation — principles and types of loss</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>BUILD_NOTE</t>
+          <t>STOP</t>
         </is>
       </c>
       <c r="E104" s="25" t="inlineStr">
@@ -7984,7 +7996,7 @@
       <c r="F104" s="26" t="inlineStr"/>
       <c r="G104" s="26" t="inlineStr">
         <is>
-          <t>Nineteen written questions reward one well-built skeleton.</t>
+          <t>Spacing, not volume.</t>
         </is>
       </c>
       <c r="H104" s="25" t="inlineStr">
@@ -8029,7 +8041,7 @@
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>CLOSED_BOOK_RECALL</t>
         </is>
       </c>
       <c r="E105" s="25" t="inlineStr">
@@ -8040,7 +8052,7 @@
       <c r="F105" s="26" t="inlineStr"/>
       <c r="G105" s="26" t="inlineStr">
         <is>
-          <t>The tree is the unit of recall.</t>
+          <t>Delayed recall from Session 1 step 11.</t>
         </is>
       </c>
       <c r="H105" s="25" t="inlineStr">
@@ -8080,38 +8092,42 @@
       </c>
       <c r="C106" s="26" t="inlineStr">
         <is>
-          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+          <t>D02-S02 — General Average</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>CLOSED_BOOK_RECALL</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E106" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F106" s="26" t="inlineStr"/>
+          <t>QB1_B#q14</t>
+        </is>
+      </c>
+      <c r="F106" s="26" t="inlineStr">
+        <is>
+          <t>What is General Average, and what is the procedure followed onboard when GA is declared?</t>
+        </is>
+      </c>
       <c r="G106" s="26" t="inlineStr">
         <is>
-          <t>Delayed recall from Session 2.</t>
+          <t>Branch 4, and the procedural limb the CE actually owns. Three examiners.</t>
         </is>
       </c>
       <c r="H106" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Rajappan, Simon</t>
         </is>
       </c>
       <c r="I106" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J106" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K106" s="25" t="inlineStr">
@@ -8119,9 +8135,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L106" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L106" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8152,7 @@
       </c>
       <c r="C107" s="26" t="inlineStr">
         <is>
-          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+          <t>D02-S02 — General Average</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
@@ -8146,22 +8162,22 @@
       </c>
       <c r="E107" s="25" t="inlineStr">
         <is>
-          <t>QB1_A#q1</t>
+          <t>QB1_A#q9</t>
         </is>
       </c>
       <c r="F107" s="26" t="inlineStr">
         <is>
-          <t>P&amp;I Club — What is Protection &amp; Indemnity? How does it differ from other marine insurance?</t>
+          <t>General Average — Explain including act and procedure followed.</t>
         </is>
       </c>
       <c r="G107" s="26" t="inlineStr">
         <is>
-          <t>Branch 5 opening — the most-asked insurance question in the corpus.</t>
+          <t>The same ask from a second file — read the two together.</t>
         </is>
       </c>
       <c r="H107" s="25" t="inlineStr">
         <is>
-          <t>Nair, Rajappan</t>
+          <t>Nair, Simon</t>
         </is>
       </c>
       <c r="I107" s="26" t="inlineStr">
@@ -8196,7 +8212,7 @@
       </c>
       <c r="C108" s="26" t="inlineStr">
         <is>
-          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+          <t>D02-S02 — General Average</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
@@ -8206,22 +8222,22 @@
       </c>
       <c r="E108" s="25" t="inlineStr">
         <is>
-          <t>QB1_A#q10</t>
+          <t>QB9_G#q7</t>
         </is>
       </c>
       <c r="F108" s="26" t="inlineStr">
         <is>
-          <t>Sue and Labour Clause — Explain.</t>
+          <t>What is the difference between General Average and Particular Average?</t>
         </is>
       </c>
       <c r="G108" s="26" t="inlineStr">
         <is>
-          <t>Branches 2 and 3 — small, precise, frequently asked.</t>
+          <t>The boundary the follow-up always reaches for.</t>
         </is>
       </c>
       <c r="H108" s="25" t="inlineStr">
         <is>
-          <t>Nair, Rajappan</t>
+          <t>Nair</t>
         </is>
       </c>
       <c r="I108" s="26" t="inlineStr">
@@ -8256,42 +8272,42 @@
       </c>
       <c r="C109" s="26" t="inlineStr">
         <is>
-          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+          <t>D02-S02 — General Average</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>WRITTEN_STUDY</t>
         </is>
       </c>
       <c r="E109" s="25" t="inlineStr">
         <is>
-          <t>QB1_A#q11</t>
+          <t>QP2602-Q6</t>
         </is>
       </c>
       <c r="F109" s="26" t="inlineStr">
         <is>
-          <t>Salvage and SCOPIC — Different types of salvage. What is SCOPIC?</t>
+          <t>a)" General average is based on certain essential features" -Discuss the statement. b) A large vessel ran aground. Main engine was used in ahead and astern directions to shake the vessel loose from the ground. Due to exc</t>
         </is>
       </c>
       <c r="G109" s="26" t="inlineStr">
         <is>
-          <t>Branch 6. Three examiners: Nair, Rajappan, Simon.</t>
+          <t>The most recent full GA-and-refloating answer — the current wording of the cluster.</t>
         </is>
       </c>
       <c r="H109" s="25" t="inlineStr">
         <is>
-          <t>Nair, Rajappan, Simon</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I109" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>NEAR_REPEAT ×6 (January 2023 → February 2026)</t>
         </is>
       </c>
       <c r="J109" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>Not on temporal watch</t>
         </is>
       </c>
       <c r="K109" s="25" t="inlineStr">
@@ -8316,42 +8332,42 @@
       </c>
       <c r="C110" s="26" t="inlineStr">
         <is>
-          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+          <t>D02-S02 — General Average</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>WRITTEN_STUDY</t>
         </is>
       </c>
       <c r="E110" s="25" t="inlineStr">
         <is>
-          <t>QB1_B#q11</t>
+          <t>QP2304-Q3</t>
         </is>
       </c>
       <c r="F110" s="26" t="inlineStr">
         <is>
-          <t>What is Salvage, and explain SCOPIC (Special Compensation P&amp;I Clause)</t>
+          <t>A. What are the principles of modern salvage law? B. What is General Average, C. Explain with context to General Average, i. Entitlement; ii. Artificial; iii. Adjustment; iv. Contestation</t>
         </is>
       </c>
       <c r="G110" s="26" t="inlineStr">
         <is>
-          <t>The same ask from a second file — confirms the examiners really do ask it.</t>
+          <t>Particular vs general average and the adjuster — the boundary, which is what the follow-up asks.</t>
         </is>
       </c>
       <c r="H110" s="25" t="inlineStr">
         <is>
-          <t>Nair, Rajappan, Simon</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I110" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>NEAR_REPEAT ×8 (February 2021 → July 2026)</t>
         </is>
       </c>
       <c r="J110" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>Not on temporal watch</t>
         </is>
       </c>
       <c r="K110" s="25" t="inlineStr">
@@ -8376,27 +8392,23 @@
       </c>
       <c r="C111" s="26" t="inlineStr">
         <is>
-          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+          <t>D02-S02 — General Average</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>WRITTEN_STUDY</t>
+          <t>BUILD_NOTE</t>
         </is>
       </c>
       <c r="E111" s="25" t="inlineStr">
         <is>
-          <t>QP2411-Q6</t>
-        </is>
-      </c>
-      <c r="F111" s="26" t="inlineStr">
-        <is>
-          <t>a) Define P&amp;I insurance and H&amp;M insurance, outlining the main differences between them in terms of coverage and purpose within the maritime industry. Why are both types of insurance essential for shipowners? (8) b) Discu</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F111" s="26" t="inlineStr"/>
       <c r="G111" s="26" t="inlineStr">
         <is>
-          <t>The comparison in one answer, including the 3/4ths collision split.</t>
+          <t>Branches 3 to 5 all hang off it. Highest-value note in the topic.</t>
         </is>
       </c>
       <c r="H111" s="25" t="inlineStr">
@@ -8406,12 +8418,12 @@
       </c>
       <c r="I111" s="26" t="inlineStr">
         <is>
-          <t>UNIQUE ×1 (November 2024 → November 2024)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J111" s="26" t="inlineStr">
         <is>
-          <t>Not on temporal watch</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K111" s="25" t="inlineStr">
@@ -8419,9 +8431,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L111" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L111" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8436,27 +8448,23 @@
       </c>
       <c r="C112" s="26" t="inlineStr">
         <is>
-          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+          <t>D02-S02 — General Average</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>WRITTEN_STUDY</t>
+          <t>BUILD_NOTE</t>
         </is>
       </c>
       <c r="E112" s="25" t="inlineStr">
         <is>
-          <t>QP2406-Q8</t>
-        </is>
-      </c>
-      <c r="F112" s="26" t="inlineStr">
-        <is>
-          <t>A. What are the principles of modern salvage law? B. What is General Average, C. Explain with context to General Average, i. Entitlement; ii. Artificial; iii. Adjustment; iv. Contestation</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F112" s="26" t="inlineStr"/>
       <c r="G112" s="26" t="inlineStr">
         <is>
-          <t>Chain A and Chain B meeting in one question — how a salvage award enters the GA adjustment.</t>
+          <t>Nineteen written questions reward one well-built skeleton.</t>
         </is>
       </c>
       <c r="H112" s="25" t="inlineStr">
@@ -8466,12 +8474,12 @@
       </c>
       <c r="I112" s="26" t="inlineStr">
         <is>
-          <t>NEAR_REPEAT ×8 (February 2021 → July 2026)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J112" s="26" t="inlineStr">
         <is>
-          <t>Not on temporal watch</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K112" s="25" t="inlineStr">
@@ -8479,9 +8487,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L112" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L112" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8504,12 @@
       </c>
       <c r="C113" s="26" t="inlineStr">
         <is>
-          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
+          <t>D02-S02 — General Average</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>BUILD_NOTE</t>
+          <t>STOP</t>
         </is>
       </c>
       <c r="E113" s="25" t="inlineStr">
@@ -8512,7 +8520,7 @@
       <c r="F113" s="26" t="inlineStr"/>
       <c r="G113" s="26" t="inlineStr">
         <is>
-          <t>The salvage limb is what QP2406-Q8 tests and what a GA-only note misses.</t>
+          <t>The tree is the unit of recall.</t>
         </is>
       </c>
       <c r="H113" s="25" t="inlineStr">
@@ -8557,7 +8565,7 @@
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>BUILD_NOTE</t>
+          <t>CLOSED_BOOK_RECALL</t>
         </is>
       </c>
       <c r="E114" s="25" t="inlineStr">
@@ -8568,7 +8576,7 @@
       <c r="F114" s="26" t="inlineStr"/>
       <c r="G114" s="26" t="inlineStr">
         <is>
-          <t>Asked five times in writing and constantly orally.</t>
+          <t>Delayed recall from Session 2.</t>
         </is>
       </c>
       <c r="H114" s="25" t="inlineStr">
@@ -8613,33 +8621,37 @@
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E115" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F115" s="26" t="inlineStr"/>
+          <t>QB1_A#q1</t>
+        </is>
+      </c>
+      <c r="F115" s="26" t="inlineStr">
+        <is>
+          <t>P&amp;I Club — What is Protection &amp; Indemnity? How does it differ from other marine insurance?</t>
+        </is>
+      </c>
       <c r="G115" s="26" t="inlineStr">
         <is>
-          <t>Pairs decay faster than singles; space them.</t>
+          <t>Branch 5 opening — the most-asked insurance question in the corpus.</t>
         </is>
       </c>
       <c r="H115" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Rajappan</t>
         </is>
       </c>
       <c r="I115" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J115" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K115" s="25" t="inlineStr">
@@ -8647,9 +8659,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L115" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L115" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -8664,38 +8676,42 @@
       </c>
       <c r="C116" s="26" t="inlineStr">
         <is>
-          <t>D02-S04 — Liability, limitation and pollution</t>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>CLOSED_BOOK_RECALL</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E116" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F116" s="26" t="inlineStr"/>
+          <t>QB1_A#q10</t>
+        </is>
+      </c>
+      <c r="F116" s="26" t="inlineStr">
+        <is>
+          <t>Sue and Labour Clause — Explain.</t>
+        </is>
+      </c>
       <c r="G116" s="26" t="inlineStr">
         <is>
-          <t>Delayed recall from Session 3.</t>
+          <t>Branches 2 and 3 — small, precise, frequently asked.</t>
         </is>
       </c>
       <c r="H116" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Rajappan</t>
         </is>
       </c>
       <c r="I116" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J116" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K116" s="25" t="inlineStr">
@@ -8703,9 +8719,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L116" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L116" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8736,7 @@
       </c>
       <c r="C117" s="26" t="inlineStr">
         <is>
-          <t>D02-S04 — Liability, limitation and pollution</t>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
@@ -8730,22 +8746,22 @@
       </c>
       <c r="E117" s="25" t="inlineStr">
         <is>
-          <t>QB1_A#q3</t>
+          <t>QB1_A#q11</t>
         </is>
       </c>
       <c r="F117" s="26" t="inlineStr">
         <is>
-          <t>LLMC Convention — Who pays within and after the limits?</t>
+          <t>Salvage and SCOPIC — Different types of salvage. What is SCOPIC?</t>
         </is>
       </c>
       <c r="G117" s="26" t="inlineStr">
         <is>
-          <t>Branch 7 — the question that exposes whether you understand limitation at all.</t>
+          <t>Branch 6. Three examiners: Nair, Rajappan, Simon.</t>
         </is>
       </c>
       <c r="H117" s="25" t="inlineStr">
         <is>
-          <t>Nair, Simon</t>
+          <t>Nair, Rajappan, Simon</t>
         </is>
       </c>
       <c r="I117" s="26" t="inlineStr">
@@ -8780,7 +8796,7 @@
       </c>
       <c r="C118" s="26" t="inlineStr">
         <is>
-          <t>D02-S04 — Liability, limitation and pollution</t>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
@@ -8790,22 +8806,22 @@
       </c>
       <c r="E118" s="25" t="inlineStr">
         <is>
-          <t>QB1_A#q4</t>
+          <t>QB1_B#q11</t>
         </is>
       </c>
       <c r="F118" s="26" t="inlineStr">
         <is>
-          <t>Bunker Convention 2001 — Explain in detail. Why was it required despite CLC?</t>
+          <t>What is Salvage, and explain SCOPIC (Special Compensation P&amp;I Clause)</t>
         </is>
       </c>
       <c r="G118" s="26" t="inlineStr">
         <is>
-          <t>The 3-occurrence written family, and the sharpest convention boundary in D02.</t>
+          <t>The same ask from a second file — confirms the examiners really do ask it.</t>
         </is>
       </c>
       <c r="H118" s="25" t="inlineStr">
         <is>
-          <t>Nair, Simon</t>
+          <t>Nair, Rajappan, Simon</t>
         </is>
       </c>
       <c r="I118" s="26" t="inlineStr">
@@ -8840,42 +8856,42 @@
       </c>
       <c r="C119" s="26" t="inlineStr">
         <is>
-          <t>D02-S04 — Liability, limitation and pollution</t>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>WRITTEN_STUDY</t>
         </is>
       </c>
       <c r="E119" s="25" t="inlineStr">
         <is>
-          <t>QB1_B#q10</t>
+          <t>QP2411-Q6</t>
         </is>
       </c>
       <c r="F119" s="26" t="inlineStr">
         <is>
-          <t>Explain the CLC (Civil Liability Convention) — scope and application, including in the context of a bunker-spill incident</t>
+          <t>a) Define P&amp;I insurance and H&amp;M insurance, outlining the main differences between them in terms of coverage and purpose within the maritime industry. Why are both types of insurance essential for shipowners? (8) b) Discu</t>
         </is>
       </c>
       <c r="G119" s="26" t="inlineStr">
         <is>
-          <t>Chain C's gateway. Three examiners: Nair, Rajappan, Simon.</t>
+          <t>The comparison in one answer, including the 3/4ths collision split.</t>
         </is>
       </c>
       <c r="H119" s="25" t="inlineStr">
         <is>
-          <t>Nair, Rajappan, Simon</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I119" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>UNIQUE ×1 (November 2024 → November 2024)</t>
         </is>
       </c>
       <c r="J119" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>Not on temporal watch</t>
         </is>
       </c>
       <c r="K119" s="25" t="inlineStr">
@@ -8900,7 +8916,7 @@
       </c>
       <c r="C120" s="26" t="inlineStr">
         <is>
-          <t>D02-S04 — Liability, limitation and pollution</t>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
@@ -8910,17 +8926,17 @@
       </c>
       <c r="E120" s="25" t="inlineStr">
         <is>
-          <t>QP2506-Q5</t>
+          <t>QP2406-Q8</t>
         </is>
       </c>
       <c r="F120" s="26" t="inlineStr">
         <is>
-          <t>a) What is LLMC and what is its purpose? Which are the two heads of claims for which limitation is stated in this Convention? Who can limit liability under this convention? b) Explain the terms: Plaintiff, Defendant, Pri</t>
+          <t>A. What are the principles of modern salvage law? B. What is General Average, C. Explain with context to General Average, i. Entitlement; ii. Artificial; iii. Adjustment; iv. Contestation</t>
         </is>
       </c>
       <c r="G120" s="26" t="inlineStr">
         <is>
-          <t>Purpose, heads of claim and the legal vocabulary the other limitation answers assume.</t>
+          <t>Chain A and Chain B meeting in one question — how a salvage award enters the GA adjustment.</t>
         </is>
       </c>
       <c r="H120" s="25" t="inlineStr">
@@ -8930,7 +8946,7 @@
       </c>
       <c r="I120" s="26" t="inlineStr">
         <is>
-          <t>EXACT_REPEAT ×3 (January 2023 → June 2025)</t>
+          <t>NEAR_REPEAT ×8 (February 2021 → July 2026)</t>
         </is>
       </c>
       <c r="J120" s="26" t="inlineStr">
@@ -8960,27 +8976,23 @@
       </c>
       <c r="C121" s="26" t="inlineStr">
         <is>
-          <t>D02-S04 — Liability, limitation and pollution</t>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>WRITTEN_STUDY</t>
+          <t>BUILD_NOTE</t>
         </is>
       </c>
       <c r="E121" s="25" t="inlineStr">
         <is>
-          <t>QP2409-Q6</t>
-        </is>
-      </c>
-      <c r="F121" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Describe the background and relevance of the International Convention on Civil Liability for Bunker Oil Pollution Damage, 2001. Define the following under Bunker Convention and explain how they differ from other similar </t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F121" s="26" t="inlineStr"/>
       <c r="G121" s="26" t="inlineStr">
         <is>
-          <t>The convention boundary examiners reach for immediately after CLC.</t>
+          <t>The salvage limb is what QP2406-Q8 tests and what a GA-only note misses.</t>
         </is>
       </c>
       <c r="H121" s="25" t="inlineStr">
@@ -8990,12 +9002,12 @@
       </c>
       <c r="I121" s="26" t="inlineStr">
         <is>
-          <t>NEAR_REPEAT ×7 (January 2021 → September 2025)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J121" s="26" t="inlineStr">
         <is>
-          <t>Not on temporal watch</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K121" s="25" t="inlineStr">
@@ -9003,9 +9015,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L121" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L121" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9020,7 +9032,7 @@
       </c>
       <c r="C122" s="26" t="inlineStr">
         <is>
-          <t>D02-S04 — Liability, limitation and pollution</t>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
@@ -9036,7 +9048,7 @@
       <c r="F122" s="26" t="inlineStr"/>
       <c r="G122" s="26" t="inlineStr">
         <is>
-          <t>Chain C is unanswerable without it, and QP2601-Q4 / QP2604-Q4 run the whole ladder in one question.</t>
+          <t>Asked five times in writing and constantly orally.</t>
         </is>
       </c>
       <c r="H122" s="25" t="inlineStr">
@@ -9076,7 +9088,7 @@
       </c>
       <c r="C123" s="26" t="inlineStr">
         <is>
-          <t>D02-S04 — Liability, limitation and pollution</t>
+          <t>D02-S03 — The insurance market — P&amp;I, H&amp;M and salvage</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
@@ -9092,7 +9104,7 @@
       <c r="F123" s="26" t="inlineStr"/>
       <c r="G123" s="26" t="inlineStr">
         <is>
-          <t>Sessions 1-4 read what exists; Session 5 writes what does not.</t>
+          <t>Pairs decay faster than singles; space them.</t>
         </is>
       </c>
       <c r="H123" s="25" t="inlineStr">
@@ -9132,42 +9144,38 @@
       </c>
       <c r="C124" s="26" t="inlineStr">
         <is>
-          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+          <t>D02-S04 — Liability, limitation and pollution</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>ORAL_STUDY</t>
+          <t>CLOSED_BOOK_RECALL</t>
         </is>
       </c>
       <c r="E124" s="25" t="inlineStr">
         <is>
-          <t>QB1_A#q8</t>
-        </is>
-      </c>
-      <c r="F124" s="26" t="inlineStr">
-        <is>
-          <t>Maritime Lien — Explain.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F124" s="26" t="inlineStr"/>
       <c r="G124" s="26" t="inlineStr">
         <is>
-          <t>Branch 8, and the 5-occurrence lien family — the largest exact-title family in D02.</t>
+          <t>Delayed recall from Session 3.</t>
         </is>
       </c>
       <c r="H124" s="25" t="inlineStr">
         <is>
-          <t>Nair</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I124" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J124" s="26" t="inlineStr">
         <is>
-          <t>n/a (oral)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K124" s="25" t="inlineStr">
@@ -9175,9 +9183,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L124" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="L124" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9200,7 @@
       </c>
       <c r="C125" s="26" t="inlineStr">
         <is>
-          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+          <t>D02-S04 — Liability, limitation and pollution</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
@@ -9202,22 +9210,22 @@
       </c>
       <c r="E125" s="25" t="inlineStr">
         <is>
-          <t>QB1_A#q7</t>
+          <t>QB1_A#q3</t>
         </is>
       </c>
       <c r="F125" s="26" t="inlineStr">
         <is>
-          <t>Admiralty Law — Explain. How is the Chief Engineer related to the Admiralty Act?</t>
+          <t>LLMC Convention — Who pays within and after the limits?</t>
         </is>
       </c>
       <c r="G125" s="26" t="inlineStr">
         <is>
-          <t>Branch 8's Indian limb — the Admiralty Act 2017 and the CE's own exposure.</t>
+          <t>Branch 7 — the question that exposes whether you understand limitation at all.</t>
         </is>
       </c>
       <c r="H125" s="25" t="inlineStr">
         <is>
-          <t>Nair</t>
+          <t>Nair, Simon</t>
         </is>
       </c>
       <c r="I125" s="26" t="inlineStr">
@@ -9252,7 +9260,7 @@
       </c>
       <c r="C126" s="26" t="inlineStr">
         <is>
-          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+          <t>D02-S04 — Liability, limitation and pollution</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
@@ -9262,17 +9270,17 @@
       </c>
       <c r="E126" s="25" t="inlineStr">
         <is>
-          <t>QB1_A#q27</t>
+          <t>QB1_A#q4</t>
         </is>
       </c>
       <c r="F126" s="26" t="inlineStr">
         <is>
-          <t>Hague-Visby Rules — Explain.</t>
+          <t>Bunker Convention 2001 — Explain in detail. Why was it required despite CLC?</t>
         </is>
       </c>
       <c r="G126" s="26" t="inlineStr">
         <is>
-          <t>The ONLY oral in the corpus on the cargo conventions.</t>
+          <t>The 3-occurrence written family, and the sharpest convention boundary in D02.</t>
         </is>
       </c>
       <c r="H126" s="25" t="inlineStr">
@@ -9312,42 +9320,42 @@
       </c>
       <c r="C127" s="26" t="inlineStr">
         <is>
-          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+          <t>D02-S04 — Liability, limitation and pollution</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>WRITTEN_STUDY</t>
+          <t>ORAL_STUDY</t>
         </is>
       </c>
       <c r="E127" s="25" t="inlineStr">
         <is>
-          <t>QP2512-Q9</t>
+          <t>QB1_B#q10</t>
         </is>
       </c>
       <c r="F127" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is Maritime Lien? How does this lien travel with property? Explain the associated terms "In Rem" and "In personam". Which convention deals with maritime lien? Give the order of settlement of various debtor's claims </t>
+          <t>Explain the CLC (Civil Liability Convention) — scope and application, including in the context of a bunker-spill incident</t>
         </is>
       </c>
       <c r="G127" s="26" t="inlineStr">
         <is>
-          <t>The most recent of the largest exact-title family — lien, in rem, in personam and priority.</t>
+          <t>Chain C's gateway. Three examiners: Nair, Rajappan, Simon.</t>
         </is>
       </c>
       <c r="H127" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nair, Rajappan, Simon</t>
         </is>
       </c>
       <c r="I127" s="26" t="inlineStr">
         <is>
-          <t>EXACT_REPEAT ×6 (December 2022 → December 2025)</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="J127" s="26" t="inlineStr">
         <is>
-          <t>Not on temporal watch</t>
+          <t>n/a (oral)</t>
         </is>
       </c>
       <c r="K127" s="25" t="inlineStr">
@@ -9372,7 +9380,7 @@
       </c>
       <c r="C128" s="26" t="inlineStr">
         <is>
-          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+          <t>D02-S04 — Liability, limitation and pollution</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
@@ -9382,17 +9390,17 @@
       </c>
       <c r="E128" s="25" t="inlineStr">
         <is>
-          <t>QP2608-Q4</t>
+          <t>QP2506-Q5</t>
         </is>
       </c>
       <c r="F128" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>a) What is LLMC and what is its purpose? Which are the two heads of claims for which limitation is stated in this Convention? Who can limit liability under this convention? b) Explain the terms: Plaintiff, Defendant, Pri</t>
         </is>
       </c>
       <c r="G128" s="26" t="inlineStr">
         <is>
-          <t>Adjudicated this session: the limb family and the whole-question family are nested, not duplicated. "Q4 is a five-time repeat" is true of 4 of its 16 marks.</t>
+          <t>Purpose, heads of claim and the legal vocabulary the other limitation answers assume.</t>
         </is>
       </c>
       <c r="H128" s="25" t="inlineStr">
@@ -9402,12 +9410,12 @@
       </c>
       <c r="I128" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>EXACT_REPEAT ×3 (January 2023 → June 2025)</t>
         </is>
       </c>
       <c r="J128" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Not on temporal watch</t>
         </is>
       </c>
       <c r="K128" s="25" t="inlineStr">
@@ -9432,23 +9440,27 @@
       </c>
       <c r="C129" s="26" t="inlineStr">
         <is>
-          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+          <t>D02-S04 — Liability, limitation and pollution</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>BUILD_NOTE</t>
+          <t>WRITTEN_STUDY</t>
         </is>
       </c>
       <c r="E129" s="25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F129" s="26" t="inlineStr"/>
+          <t>QP2409-Q6</t>
+        </is>
+      </c>
+      <c r="F129" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Describe the background and relevance of the International Convention on Civil Liability for Bunker Oil Pollution Damage, 2001. Define the following under Bunker Convention and explain how they differ from other similar </t>
+        </is>
+      </c>
       <c r="G129" s="26" t="inlineStr">
         <is>
-          <t>Official item 11 says 1906; every paper that names an Act says 1963.</t>
+          <t>The convention boundary examiners reach for immediately after CLC.</t>
         </is>
       </c>
       <c r="H129" s="25" t="inlineStr">
@@ -9458,12 +9470,12 @@
       </c>
       <c r="I129" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NEAR_REPEAT ×7 (January 2021 → September 2025)</t>
         </is>
       </c>
       <c r="J129" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Not on temporal watch</t>
         </is>
       </c>
       <c r="K129" s="25" t="inlineStr">
@@ -9471,9 +9483,9 @@
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L129" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="L129" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -9488,7 +9500,7 @@
       </c>
       <c r="C130" s="26" t="inlineStr">
         <is>
-          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+          <t>D02-S04 — Liability, limitation and pollution</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
@@ -9504,7 +9516,7 @@
       <c r="F130" s="26" t="inlineStr"/>
       <c r="G130" s="26" t="inlineStr">
         <is>
-          <t>Ten written questions, ONE oral. Hamburg and Rotterdam appear in two written questions and no oral at all.</t>
+          <t>Chain C is unanswerable without it, and QP2601-Q4 / QP2604-Q4 run the whole ladder in one question.</t>
         </is>
       </c>
       <c r="H130" s="25" t="inlineStr">
@@ -9544,12 +9556,12 @@
       </c>
       <c r="C131" s="26" t="inlineStr">
         <is>
-          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+          <t>D02-S04 — Liability, limitation and pollution</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>MOCK</t>
+          <t>STOP</t>
         </is>
       </c>
       <c r="E131" s="25" t="inlineStr">
@@ -9560,7 +9572,7 @@
       <c r="F131" s="26" t="inlineStr"/>
       <c r="G131" s="26" t="inlineStr">
         <is>
-          <t>Nearly every D02 follow-up is "and how is that different from...?".</t>
+          <t>Sessions 1-4 read what exists; Session 5 writes what does not.</t>
         </is>
       </c>
       <c r="H131" s="25" t="inlineStr">
@@ -9605,55 +9617,523 @@
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E132" s="25" t="inlineStr">
+        <is>
+          <t>QB1_A#q8</t>
+        </is>
+      </c>
+      <c r="F132" s="26" t="inlineStr">
+        <is>
+          <t>Maritime Lien — Explain.</t>
+        </is>
+      </c>
+      <c r="G132" s="26" t="inlineStr">
+        <is>
+          <t>Branch 8, and the 5-occurrence lien family — the largest exact-title family in D02.</t>
+        </is>
+      </c>
+      <c r="H132" s="25" t="inlineStr">
+        <is>
+          <t>Nair</t>
+        </is>
+      </c>
+      <c r="I132" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J132" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K132" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L132" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="25" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C133" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D133" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E133" s="25" t="inlineStr">
+        <is>
+          <t>QB1_A#q7</t>
+        </is>
+      </c>
+      <c r="F133" s="26" t="inlineStr">
+        <is>
+          <t>Admiralty Law — Explain. How is the Chief Engineer related to the Admiralty Act?</t>
+        </is>
+      </c>
+      <c r="G133" s="26" t="inlineStr">
+        <is>
+          <t>Branch 8's Indian limb — the Admiralty Act 2017 and the CE's own exposure.</t>
+        </is>
+      </c>
+      <c r="H133" s="25" t="inlineStr">
+        <is>
+          <t>Nair</t>
+        </is>
+      </c>
+      <c r="I133" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J133" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K133" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L133" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="25" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C134" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D134" s="25" t="inlineStr">
+        <is>
+          <t>ORAL_STUDY</t>
+        </is>
+      </c>
+      <c r="E134" s="25" t="inlineStr">
+        <is>
+          <t>QB1_A#q27</t>
+        </is>
+      </c>
+      <c r="F134" s="26" t="inlineStr">
+        <is>
+          <t>Hague-Visby Rules — Explain.</t>
+        </is>
+      </c>
+      <c r="G134" s="26" t="inlineStr">
+        <is>
+          <t>The ONLY oral in the corpus on the cargo conventions.</t>
+        </is>
+      </c>
+      <c r="H134" s="25" t="inlineStr">
+        <is>
+          <t>Nair, Simon</t>
+        </is>
+      </c>
+      <c r="I134" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="J134" s="26" t="inlineStr">
+        <is>
+          <t>n/a (oral)</t>
+        </is>
+      </c>
+      <c r="K134" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L134" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="25" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C135" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D135" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E135" s="25" t="inlineStr">
+        <is>
+          <t>QP2512-Q9</t>
+        </is>
+      </c>
+      <c r="F135" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What is Maritime Lien? How does this lien travel with property? Explain the associated terms "In Rem" and "In personam". Which convention deals with maritime lien? Give the order of settlement of various debtor's claims </t>
+        </is>
+      </c>
+      <c r="G135" s="26" t="inlineStr">
+        <is>
+          <t>The most recent of the largest exact-title family — lien, in rem, in personam and priority.</t>
+        </is>
+      </c>
+      <c r="H135" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I135" s="26" t="inlineStr">
+        <is>
+          <t>EXACT_REPEAT ×6 (December 2022 → December 2025)</t>
+        </is>
+      </c>
+      <c r="J135" s="26" t="inlineStr">
+        <is>
+          <t>Not on temporal watch</t>
+        </is>
+      </c>
+      <c r="K135" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L135" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="25" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C136" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D136" s="25" t="inlineStr">
+        <is>
+          <t>WRITTEN_STUDY</t>
+        </is>
+      </c>
+      <c r="E136" s="25" t="inlineStr">
+        <is>
+          <t>QP2608-Q4</t>
+        </is>
+      </c>
+      <c r="F136" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G136" s="26" t="inlineStr">
+        <is>
+          <t>Adjudicated this session: the limb family and the whole-question family are nested, not duplicated. "Q4 is a five-time repeat" is true of 4 of its 16 marks.</t>
+        </is>
+      </c>
+      <c r="H136" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I136" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J136" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K136" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L136" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="25" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C137" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D137" s="25" t="inlineStr">
+        <is>
+          <t>BUILD_NOTE</t>
+        </is>
+      </c>
+      <c r="E137" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F137" s="26" t="inlineStr"/>
+      <c r="G137" s="26" t="inlineStr">
+        <is>
+          <t>Official item 11 says 1906; every paper that names an Act says 1963.</t>
+        </is>
+      </c>
+      <c r="H137" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I137" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J137" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K137" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L137" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="25" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C138" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D138" s="25" t="inlineStr">
+        <is>
+          <t>BUILD_NOTE</t>
+        </is>
+      </c>
+      <c r="E138" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F138" s="26" t="inlineStr"/>
+      <c r="G138" s="26" t="inlineStr">
+        <is>
+          <t>Ten written questions, ONE oral. Hamburg and Rotterdam appear in two written questions and no oral at all.</t>
+        </is>
+      </c>
+      <c r="H138" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I138" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J138" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K138" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L138" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="25" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C139" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D139" s="25" t="inlineStr">
+        <is>
+          <t>MOCK</t>
+        </is>
+      </c>
+      <c r="E139" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F139" s="26" t="inlineStr"/>
+      <c r="G139" s="26" t="inlineStr">
+        <is>
+          <t>Nearly every D02 follow-up is "and how is that different from...?".</t>
+        </is>
+      </c>
+      <c r="H139" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I139" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J139" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K139" s="25" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+      <c r="L139" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="25" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="25" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C140" s="26" t="inlineStr">
+        <is>
+          <t>D02-S05 — Admiralty, carriage and closed-book mock</t>
+        </is>
+      </c>
+      <c r="D140" s="25" t="inlineStr">
+        <is>
           <t>STOP</t>
         </is>
       </c>
-      <c r="E132" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F132" s="26" t="inlineStr"/>
-      <c r="G132" s="26" t="inlineStr">
+      <c r="E140" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F140" s="26" t="inlineStr"/>
+      <c r="G140" s="26" t="inlineStr">
         <is>
           <t>Progress is an input to the workbook, never an output.</t>
         </is>
       </c>
-      <c r="H132" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I132" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J132" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K132" s="25" t="inlineStr">
+      <c r="H140" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I140" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J140" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K140" s="25" t="inlineStr">
         <is>
           <t>QUEUED</t>
         </is>
       </c>
-      <c r="L132" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="9" t="inlineStr">
+      <c r="L140" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
         <is>
           <t>Generated from docs/study/study_sessions.json. Sessions for later topics appear here automatically as they are approved — this sheet has no hand-written rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L132"/>
+  <autoFilter ref="A1:L140"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId2"/>
@@ -9681,63 +10161,71 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId91"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10784,12 +11272,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId5"/>
     <hyperlink ref="R3" location="'WRITTEN BY TOPIC'!A168" display="WRITTEN ▸"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId6"/>
-    <hyperlink ref="T3" location="'STUDY QUEUE'!A34" display="QUEUE ▸"/>
+    <hyperlink ref="T3" location="'STUDY QUEUE'!A42" display="QUEUE ▸"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId8"/>
     <hyperlink ref="R4" location="'WRITTEN BY TOPIC'!A98" display="WRITTEN ▸"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId9"/>
-    <hyperlink ref="T4" location="'STUDY QUEUE'!A84" display="QUEUE ▸"/>
+    <hyperlink ref="T4" location="'STUDY QUEUE'!A92" display="QUEUE ▸"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId11"/>
     <hyperlink ref="R5" location="'WRITTEN BY TOPIC'!A237" display="WRITTEN ▸"/>

--- a/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
+++ b/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
@@ -636,7 +636,7 @@
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Study order #1 of 10, and study order is dependency-first, not priority-first. Prerequisites: —. It unlocks: D02, D03, D04, D05, D06, D07, D08, D09. Priority rank #2 (score 0.6554).</t>
+          <t>Study order #1 of 10, and study order is dependency-first, not priority-first. Prerequisites: —. It unlocks: D02, D03, D04, D05, D06, D07, D08, D09. Priority rank #2 (score 0.6831).</t>
         </is>
       </c>
     </row>
@@ -6886,22 +6886,22 @@
       </c>
       <c r="E85" s="25" t="inlineStr">
         <is>
-          <t>QB4_E#q8</t>
+          <t>QB4_J#q6</t>
         </is>
       </c>
       <c r="F85" s="26" t="inlineStr">
         <is>
-          <t>PSC — appeal process, codes involved, and process after detention?</t>
+          <t>What are the ISM manuals? Describe the SMS documentation structure.</t>
         </is>
       </c>
       <c r="G85" s="26" t="inlineStr">
         <is>
-          <t>B-priority, three examiners — PSC appeal and post-detention process.</t>
+          <t>B-priority, and the documentation frame N6 is built on — the ISM manuals and SMS documentation structure. Replaces QB4_E#q8, which was reassigned to D01 on 2026-08-23 and is therefore covered before D03 begins.</t>
         </is>
       </c>
       <c r="H85" s="25" t="inlineStr">
         <is>
-          <t>Nair, Simon, Srivastava</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="I85" s="26" t="inlineStr">
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="F2" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="G2" s="21" t="n">
         <v>72</v>
-      </c>
-      <c r="G2" s="21" t="n">
-        <v>64</v>
       </c>
       <c r="H2" s="21" t="n">
         <v>96</v>
@@ -10421,7 +10421,7 @@
         <v>2</v>
       </c>
       <c r="N2" s="21" t="n">
-        <v>0.6554</v>
+        <v>0.6831</v>
       </c>
       <c r="O2" s="21" t="inlineStr">
         <is>
@@ -10484,10 +10484,10 @@
         </is>
       </c>
       <c r="F3" s="25" t="n">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G3" s="25" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="H3" s="25" t="n">
         <v>69</v>
@@ -10599,7 +10599,7 @@
         <v>3</v>
       </c>
       <c r="N4" s="25" t="n">
-        <v>0.5389</v>
+        <v>0.5506</v>
       </c>
       <c r="O4" s="25" t="inlineStr">
         <is>
@@ -10662,10 +10662,10 @@
         </is>
       </c>
       <c r="F5" s="25" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>43</v>
@@ -10688,7 +10688,7 @@
         <v>5</v>
       </c>
       <c r="N5" s="25" t="n">
-        <v>0.3134</v>
+        <v>0.3229</v>
       </c>
       <c r="O5" s="25" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>4</v>
       </c>
       <c r="N6" s="25" t="n">
-        <v>0.3466</v>
+        <v>0.3528</v>
       </c>
       <c r="O6" s="25" t="inlineStr">
         <is>
@@ -10840,10 +10840,10 @@
         </is>
       </c>
       <c r="F7" s="25" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H7" s="25" t="n">
         <v>13</v>
@@ -10866,7 +10866,7 @@
         <v>6</v>
       </c>
       <c r="N7" s="25" t="n">
-        <v>0.2922</v>
+        <v>0.2946</v>
       </c>
       <c r="O7" s="25" t="inlineStr">
         <is>
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="F8" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="25" t="n">
         <v>19</v>
@@ -10955,7 +10955,7 @@
         <v>7</v>
       </c>
       <c r="N8" s="25" t="n">
-        <v>0.1092</v>
+        <v>0.1119</v>
       </c>
       <c r="O8" s="25" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         </is>
       </c>
       <c r="F9" s="25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G9" s="25" t="n">
         <v>17</v>
@@ -11044,7 +11044,7 @@
         <v>8</v>
       </c>
       <c r="N9" s="25" t="n">
-        <v>0.0958</v>
+        <v>0.0964</v>
       </c>
       <c r="O9" s="25" t="inlineStr">
         <is>
@@ -11107,10 +11107,10 @@
         </is>
       </c>
       <c r="F10" s="25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G10" s="25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10" s="25" t="n">
         <v>0</v>
@@ -11133,7 +11133,7 @@
         <v>9</v>
       </c>
       <c r="N10" s="25" t="n">
-        <v>0.0781</v>
+        <v>0.0832</v>
       </c>
       <c r="O10" s="25" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="25" t="n">
-        <v>0.0606</v>
+        <v>0.0631</v>
       </c>
       <c r="O11" s="25" t="inlineStr">
         <is>
@@ -11428,13 +11428,13 @@
         </is>
       </c>
       <c r="C2" s="25" t="n">
+        <v>80</v>
+      </c>
+      <c r="D2" s="25" t="n">
         <v>72</v>
       </c>
-      <c r="D2" s="25" t="n">
-        <v>64</v>
-      </c>
       <c r="E2" s="25" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="F2" s="25" t="n">
         <v>6</v>
@@ -11460,7 +11460,7 @@
         </is>
       </c>
       <c r="M2" s="25" t="n">
-        <v>0.6554</v>
+        <v>0.6831</v>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
@@ -11495,13 +11495,13 @@
         </is>
       </c>
       <c r="C3" s="25" t="n">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E3" s="25" t="n">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="F3" s="25" t="n">
         <v>6</v>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="M4" s="25" t="n">
-        <v>0.5389</v>
+        <v>0.5506</v>
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
@@ -11629,13 +11629,13 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>5</v>
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="M5" s="25" t="n">
-        <v>0.3134</v>
+        <v>0.3229</v>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="M6" s="25" t="n">
-        <v>0.3466</v>
+        <v>0.3528</v>
       </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="F7" s="25" t="n">
         <v>6</v>
@@ -11795,7 +11795,7 @@
         </is>
       </c>
       <c r="M7" s="25" t="n">
-        <v>0.2922</v>
+        <v>0.2946</v>
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
@@ -11830,16 +11830,16 @@
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="25" t="n">
         <v>19</v>
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="M8" s="25" t="n">
-        <v>0.1092</v>
+        <v>0.1119</v>
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" s="25" t="n">
         <v>17</v>
@@ -11929,7 +11929,7 @@
         </is>
       </c>
       <c r="M9" s="25" t="n">
-        <v>0.0958</v>
+        <v>0.0964</v>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10" s="25" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F10" s="25" t="n">
         <v>5</v>
@@ -11996,7 +11996,7 @@
         </is>
       </c>
       <c r="M10" s="25" t="n">
-        <v>0.0781</v>
+        <v>0.0832</v>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         </is>
       </c>
       <c r="M11" s="25" t="n">
-        <v>0.0606</v>
+        <v>0.0631</v>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>

--- a/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
+++ b/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
@@ -636,7 +636,7 @@
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Study order #1 of 10, and study order is dependency-first, not priority-first. Prerequisites: —. It unlocks: D02, D03, D04, D05, D06, D07, D08, D09. Priority rank #2 (score 0.6831).</t>
+          <t>Study order #1 of 10, and study order is dependency-first, not priority-first. Prerequisites: —. It unlocks: D02, D03, D04, D05, D06, D07, D08, D09. Priority rank #2 (score 0.6568).</t>
         </is>
       </c>
     </row>
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="F2" s="21" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G2" s="21" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H2" s="21" t="n">
         <v>96</v>
@@ -10421,7 +10421,7 @@
         <v>2</v>
       </c>
       <c r="N2" s="21" t="n">
-        <v>0.6831</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="O2" s="21" t="inlineStr">
         <is>
@@ -10484,10 +10484,10 @@
         </is>
       </c>
       <c r="F3" s="25" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G3" s="25" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H3" s="25" t="n">
         <v>69</v>
@@ -10599,7 +10599,7 @@
         <v>3</v>
       </c>
       <c r="N4" s="25" t="n">
-        <v>0.5506</v>
+        <v>0.5476</v>
       </c>
       <c r="O4" s="25" t="inlineStr">
         <is>
@@ -10662,10 +10662,10 @@
         </is>
       </c>
       <c r="F5" s="25" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>43</v>
@@ -10688,7 +10688,7 @@
         <v>5</v>
       </c>
       <c r="N5" s="25" t="n">
-        <v>0.3229</v>
+        <v>0.3265</v>
       </c>
       <c r="O5" s="25" t="inlineStr">
         <is>
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="F6" s="25" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H6" s="25" t="n">
         <v>50</v>
@@ -10777,7 +10777,7 @@
         <v>4</v>
       </c>
       <c r="N6" s="25" t="n">
-        <v>0.3528</v>
+        <v>0.3538</v>
       </c>
       <c r="O6" s="25" t="inlineStr">
         <is>
@@ -10840,10 +10840,10 @@
         </is>
       </c>
       <c r="F7" s="25" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H7" s="25" t="n">
         <v>13</v>
@@ -10866,7 +10866,7 @@
         <v>6</v>
       </c>
       <c r="N7" s="25" t="n">
-        <v>0.2946</v>
+        <v>0.2947</v>
       </c>
       <c r="O7" s="25" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         </is>
       </c>
       <c r="F8" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" s="25" t="n">
         <v>2</v>
@@ -10955,7 +10955,7 @@
         <v>7</v>
       </c>
       <c r="N8" s="25" t="n">
-        <v>0.1119</v>
+        <v>0.1131</v>
       </c>
       <c r="O8" s="25" t="inlineStr">
         <is>
@@ -11018,10 +11018,10 @@
         </is>
       </c>
       <c r="F9" s="25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H9" s="25" t="n">
         <v>0</v>
@@ -11044,7 +11044,7 @@
         <v>8</v>
       </c>
       <c r="N9" s="25" t="n">
-        <v>0.0964</v>
+        <v>0.0985</v>
       </c>
       <c r="O9" s="25" t="inlineStr">
         <is>
@@ -11107,10 +11107,10 @@
         </is>
       </c>
       <c r="F10" s="25" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G10" s="25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H10" s="25" t="n">
         <v>0</v>
@@ -11133,7 +11133,7 @@
         <v>9</v>
       </c>
       <c r="N10" s="25" t="n">
-        <v>0.0832</v>
+        <v>0.0877</v>
       </c>
       <c r="O10" s="25" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="25" t="n">
-        <v>0.0631</v>
+        <v>0.0625</v>
       </c>
       <c r="O11" s="25" t="inlineStr">
         <is>
@@ -11428,13 +11428,13 @@
         </is>
       </c>
       <c r="C2" s="25" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D2" s="25" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F2" s="25" t="n">
         <v>6</v>
@@ -11460,7 +11460,7 @@
         </is>
       </c>
       <c r="M2" s="25" t="n">
-        <v>0.6831</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
@@ -11495,13 +11495,13 @@
         </is>
       </c>
       <c r="C3" s="25" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E3" s="25" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F3" s="25" t="n">
         <v>6</v>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="M4" s="25" t="n">
-        <v>0.5506</v>
+        <v>0.5476</v>
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
@@ -11629,13 +11629,13 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>5</v>
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="M5" s="25" t="n">
-        <v>0.3229</v>
+        <v>0.3265</v>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>6</v>
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="M6" s="25" t="n">
-        <v>0.3528</v>
+        <v>0.3538</v>
       </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F7" s="25" t="n">
         <v>6</v>
@@ -11795,7 +11795,7 @@
         </is>
       </c>
       <c r="M7" s="25" t="n">
-        <v>0.2946</v>
+        <v>0.2947</v>
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>2</v>
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="M8" s="25" t="n">
-        <v>0.1119</v>
+        <v>0.1131</v>
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
@@ -11897,13 +11897,13 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E9" s="25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" s="25" t="n">
         <v>3</v>
@@ -11929,7 +11929,7 @@
         </is>
       </c>
       <c r="M9" s="25" t="n">
-        <v>0.0964</v>
+        <v>0.0985</v>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" s="25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F10" s="25" t="n">
         <v>5</v>
@@ -11996,7 +11996,7 @@
         </is>
       </c>
       <c r="M10" s="25" t="n">
-        <v>0.0832</v>
+        <v>0.0877</v>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         </is>
       </c>
       <c r="M11" s="25" t="n">
-        <v>0.0631</v>
+        <v>0.0625</v>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>

--- a/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
+++ b/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
@@ -636,7 +636,7 @@
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Study order #1 of 10, and study order is dependency-first, not priority-first. Prerequisites: —. It unlocks: D02, D03, D04, D05, D06, D07, D08, D09. Priority rank #2 (score 0.6568).</t>
+          <t>Study order #1 of 10, and study order is dependency-first, not priority-first. Prerequisites: —. It unlocks: D02, D03, D04, D05, D06, D07, D08, D09. Priority rank #2 (score 0.675).</t>
         </is>
       </c>
     </row>
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="F2" s="21" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G2" s="21" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H2" s="21" t="n">
         <v>96</v>
@@ -10421,7 +10421,7 @@
         <v>2</v>
       </c>
       <c r="N2" s="21" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.675</v>
       </c>
       <c r="O2" s="21" t="inlineStr">
         <is>
@@ -10484,10 +10484,10 @@
         </is>
       </c>
       <c r="F3" s="25" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G3" s="25" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H3" s="25" t="n">
         <v>69</v>
@@ -10573,10 +10573,10 @@
         </is>
       </c>
       <c r="F4" s="25" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H4" s="25" t="n">
         <v>70</v>
@@ -10599,7 +10599,7 @@
         <v>3</v>
       </c>
       <c r="N4" s="25" t="n">
-        <v>0.5476</v>
+        <v>0.5419</v>
       </c>
       <c r="O4" s="25" t="inlineStr">
         <is>
@@ -10662,10 +10662,10 @@
         </is>
       </c>
       <c r="F5" s="25" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>43</v>
@@ -10688,7 +10688,7 @@
         <v>5</v>
       </c>
       <c r="N5" s="25" t="n">
-        <v>0.3265</v>
+        <v>0.3248</v>
       </c>
       <c r="O5" s="25" t="inlineStr">
         <is>
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="F6" s="25" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H6" s="25" t="n">
         <v>50</v>
@@ -10777,7 +10777,7 @@
         <v>4</v>
       </c>
       <c r="N6" s="25" t="n">
-        <v>0.3538</v>
+        <v>0.3588</v>
       </c>
       <c r="O6" s="25" t="inlineStr">
         <is>
@@ -10840,10 +10840,10 @@
         </is>
       </c>
       <c r="F7" s="25" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H7" s="25" t="n">
         <v>13</v>
@@ -10866,7 +10866,7 @@
         <v>6</v>
       </c>
       <c r="N7" s="25" t="n">
-        <v>0.2947</v>
+        <v>0.3037</v>
       </c>
       <c r="O7" s="25" t="inlineStr">
         <is>
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="F8" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="25" t="n">
         <v>3</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>2</v>
       </c>
       <c r="H8" s="25" t="n">
         <v>19</v>
@@ -10955,7 +10955,7 @@
         <v>7</v>
       </c>
       <c r="N8" s="25" t="n">
-        <v>0.1131</v>
+        <v>0.1157</v>
       </c>
       <c r="O8" s="25" t="inlineStr">
         <is>
@@ -11018,10 +11018,10 @@
         </is>
       </c>
       <c r="F9" s="25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H9" s="25" t="n">
         <v>0</v>
@@ -11044,7 +11044,7 @@
         <v>8</v>
       </c>
       <c r="N9" s="25" t="n">
-        <v>0.0985</v>
+        <v>0.1019</v>
       </c>
       <c r="O9" s="25" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>9</v>
       </c>
       <c r="N10" s="25" t="n">
-        <v>0.0877</v>
+        <v>0.0888</v>
       </c>
       <c r="O10" s="25" t="inlineStr">
         <is>
@@ -11196,10 +11196,10 @@
         </is>
       </c>
       <c r="F11" s="25" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H11" s="25" t="n">
         <v>0</v>
@@ -11222,7 +11222,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="25" t="n">
-        <v>0.0625</v>
+        <v>0.0571</v>
       </c>
       <c r="O11" s="25" t="inlineStr">
         <is>
@@ -11428,13 +11428,13 @@
         </is>
       </c>
       <c r="C2" s="25" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D2" s="25" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F2" s="25" t="n">
         <v>6</v>
@@ -11460,7 +11460,7 @@
         </is>
       </c>
       <c r="M2" s="25" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.675</v>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
@@ -11495,13 +11495,13 @@
         </is>
       </c>
       <c r="C3" s="25" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E3" s="25" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F3" s="25" t="n">
         <v>6</v>
@@ -11562,13 +11562,13 @@
         </is>
       </c>
       <c r="C4" s="25" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E4" s="25" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F4" s="25" t="n">
         <v>6</v>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="M4" s="25" t="n">
-        <v>0.5476</v>
+        <v>0.5419</v>
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
@@ -11629,13 +11629,13 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>5</v>
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="M5" s="25" t="n">
-        <v>0.3265</v>
+        <v>0.3248</v>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>6</v>
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="M6" s="25" t="n">
-        <v>0.3538</v>
+        <v>0.3588</v>
       </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F7" s="25" t="n">
         <v>6</v>
@@ -11795,7 +11795,7 @@
         </is>
       </c>
       <c r="M7" s="25" t="n">
-        <v>0.2947</v>
+        <v>0.3037</v>
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
@@ -11830,13 +11830,13 @@
         </is>
       </c>
       <c r="C8" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="25" t="n">
-        <v>2</v>
-      </c>
       <c r="E8" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="25" t="n">
         <v>2</v>
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="M8" s="25" t="n">
-        <v>0.1131</v>
+        <v>0.1157</v>
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
@@ -11897,16 +11897,16 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" s="25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F9" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="25" t="n">
         <v>0</v>
@@ -11929,7 +11929,7 @@
         </is>
       </c>
       <c r="M9" s="25" t="n">
-        <v>0.0985</v>
+        <v>0.1019</v>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         </is>
       </c>
       <c r="M10" s="25" t="n">
-        <v>0.0877</v>
+        <v>0.0888</v>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
@@ -12031,13 +12031,13 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>19</v>
+      </c>
+      <c r="E11" s="25" t="n">
         <v>27</v>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>22</v>
-      </c>
-      <c r="E11" s="25" t="n">
-        <v>30</v>
       </c>
       <c r="F11" s="25" t="n">
         <v>3</v>
@@ -12063,7 +12063,7 @@
         </is>
       </c>
       <c r="M11" s="25" t="n">
-        <v>0.0625</v>
+        <v>0.0571</v>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>

--- a/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
+++ b/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
@@ -636,7 +636,7 @@
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Study order #1 of 10, and study order is dependency-first, not priority-first. Prerequisites: —. It unlocks: D02, D03, D04, D05, D06, D07, D08, D09. Priority rank #2 (score 0.675).</t>
+          <t>Study order #1 of 10, and study order is dependency-first, not priority-first. Prerequisites: —. It unlocks: D02, D03, D04, D05, D06, D07, D08, D09. Priority rank #2 (score 0.6757).</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
         <v>75</v>
       </c>
       <c r="G2" s="21" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H2" s="21" t="n">
         <v>96</v>
@@ -10421,7 +10421,7 @@
         <v>2</v>
       </c>
       <c r="N2" s="21" t="n">
-        <v>0.675</v>
+        <v>0.6757</v>
       </c>
       <c r="O2" s="21" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>195</v>
       </c>
       <c r="G3" s="25" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H3" s="25" t="n">
         <v>69</v>
@@ -10599,7 +10599,7 @@
         <v>3</v>
       </c>
       <c r="N4" s="25" t="n">
-        <v>0.5419</v>
+        <v>0.5412</v>
       </c>
       <c r="O4" s="25" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>59</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>43</v>
@@ -10688,7 +10688,7 @@
         <v>5</v>
       </c>
       <c r="N5" s="25" t="n">
-        <v>0.3248</v>
+        <v>0.327</v>
       </c>
       <c r="O5" s="25" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>63</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H6" s="25" t="n">
         <v>50</v>
@@ -10777,7 +10777,7 @@
         <v>4</v>
       </c>
       <c r="N6" s="25" t="n">
-        <v>0.3588</v>
+        <v>0.3596</v>
       </c>
       <c r="O6" s="25" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>6</v>
       </c>
       <c r="N7" s="25" t="n">
-        <v>0.3037</v>
+        <v>0.303</v>
       </c>
       <c r="O7" s="25" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>8</v>
       </c>
       <c r="N9" s="25" t="n">
-        <v>0.1019</v>
+        <v>0.1017</v>
       </c>
       <c r="O9" s="25" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>9</v>
       </c>
       <c r="N10" s="25" t="n">
-        <v>0.0888</v>
+        <v>0.0887</v>
       </c>
       <c r="O10" s="25" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>25</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H11" s="25" t="n">
         <v>0</v>
@@ -11222,7 +11222,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="25" t="n">
-        <v>0.0571</v>
+        <v>0.0582</v>
       </c>
       <c r="O11" s="25" t="inlineStr">
         <is>
@@ -11431,10 +11431,10 @@
         <v>75</v>
       </c>
       <c r="D2" s="25" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F2" s="25" t="n">
         <v>6</v>
@@ -11460,7 +11460,7 @@
         </is>
       </c>
       <c r="M2" s="25" t="n">
-        <v>0.675</v>
+        <v>0.6757</v>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
@@ -11498,10 +11498,10 @@
         <v>195</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E3" s="25" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F3" s="25" t="n">
         <v>6</v>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="M4" s="25" t="n">
-        <v>0.5419</v>
+        <v>0.5412</v>
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
@@ -11632,10 +11632,10 @@
         <v>59</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>5</v>
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="M5" s="25" t="n">
-        <v>0.3248</v>
+        <v>0.327</v>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
@@ -11699,10 +11699,10 @@
         <v>63</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>6</v>
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="M6" s="25" t="n">
-        <v>0.3588</v>
+        <v>0.3596</v>
       </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         </is>
       </c>
       <c r="M7" s="25" t="n">
-        <v>0.3037</v>
+        <v>0.303</v>
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         </is>
       </c>
       <c r="M9" s="25" t="n">
-        <v>0.1019</v>
+        <v>0.1017</v>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         </is>
       </c>
       <c r="M10" s="25" t="n">
-        <v>0.0888</v>
+        <v>0.0887</v>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
@@ -12034,10 +12034,10 @@
         <v>25</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" s="25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11" s="25" t="n">
         <v>3</v>
@@ -12063,7 +12063,7 @@
         </is>
       </c>
       <c r="M11" s="25" t="n">
-        <v>0.0571</v>
+        <v>0.0582</v>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>

--- a/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
+++ b/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
@@ -10665,7 +10665,7 @@
         <v>59</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>43</v>
@@ -10688,7 +10688,7 @@
         <v>5</v>
       </c>
       <c r="N5" s="25" t="n">
-        <v>0.327</v>
+        <v>0.3183</v>
       </c>
       <c r="O5" s="25" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>22</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H9" s="25" t="n">
         <v>0</v>
@@ -11044,7 +11044,7 @@
         <v>8</v>
       </c>
       <c r="N9" s="25" t="n">
-        <v>0.1017</v>
+        <v>0.1005</v>
       </c>
       <c r="O9" s="25" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>31</v>
       </c>
       <c r="G10" s="25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H10" s="25" t="n">
         <v>0</v>
@@ -11133,7 +11133,7 @@
         <v>9</v>
       </c>
       <c r="N10" s="25" t="n">
-        <v>0.0887</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="O10" s="25" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>25</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="25" t="n">
         <v>0</v>
@@ -11222,7 +11222,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="25" t="n">
-        <v>0.0582</v>
+        <v>0.0594</v>
       </c>
       <c r="O11" s="25" t="inlineStr">
         <is>
@@ -11632,10 +11632,10 @@
         <v>59</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>5</v>
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="M5" s="25" t="n">
-        <v>0.327</v>
+        <v>0.3183</v>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
@@ -11900,10 +11900,10 @@
         <v>22</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" s="25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" s="25" t="n">
         <v>4</v>
@@ -11929,7 +11929,7 @@
         </is>
       </c>
       <c r="M9" s="25" t="n">
-        <v>0.1017</v>
+        <v>0.1005</v>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
@@ -11967,10 +11967,10 @@
         <v>31</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" s="25" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" s="25" t="n">
         <v>5</v>
@@ -11996,7 +11996,7 @@
         </is>
       </c>
       <c r="M10" s="25" t="n">
-        <v>0.0887</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
@@ -12034,13 +12034,13 @@
         <v>25</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" s="25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" s="25" t="n">
         <v>0</v>
@@ -12063,7 +12063,7 @@
         </is>
       </c>
       <c r="M11" s="25" t="n">
-        <v>0.0582</v>
+        <v>0.0594</v>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>

--- a/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
+++ b/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
@@ -19530,7 +19530,7 @@
       </c>
       <c r="P83" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q83" s="25" t="inlineStr">
@@ -20509,7 +20509,7 @@
       </c>
       <c r="P94" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q94" s="25" t="inlineStr">
@@ -31547,7 +31547,7 @@
       </c>
       <c r="P218" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q218" s="25" t="inlineStr">
@@ -32170,7 +32170,7 @@
       </c>
       <c r="P225" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q225" s="25" t="inlineStr">
@@ -32348,7 +32348,7 @@
       </c>
       <c r="P227" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q227" s="25" t="inlineStr">
@@ -35997,7 +35997,7 @@
       </c>
       <c r="P268" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q268" s="25" t="inlineStr">
@@ -36531,7 +36531,7 @@
       </c>
       <c r="P274" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q274" s="25" t="inlineStr">
@@ -40715,7 +40715,7 @@
       </c>
       <c r="P321" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q321" s="25" t="inlineStr">
@@ -42940,7 +42940,7 @@
       </c>
       <c r="P346" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q346" s="25" t="inlineStr">

--- a/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
+++ b/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
@@ -20,8 +20,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'STUDY QUEUE'!$A$1:$L$140</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ROADMAP'!$A$1:$U$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TOPIC DETAIL'!$A$1:$Q$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ROADMAP'!$A$1:$V$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TOPIC DETAIL'!$A$1:$Z$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'WRITTEN BY TOPIC'!$A$1:$S$361</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'OFFICIAL SYLLABUS'!$A$1:$H$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'COVERAGE'!$A$1:$H$26</definedName>
@@ -10237,7 +10237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10261,6 +10261,7 @@
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
     <col width="46" customWidth="1" min="21" max="21"/>
+    <col width="62" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10369,6 +10370,11 @@
           <t>Gaps</t>
         </is>
       </c>
+      <c r="V1" s="11" t="inlineStr">
+        <is>
+          <t>Answer Readiness</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="21" t="n">
@@ -10458,6 +10464,11 @@
           <t>N6 duty of care (zero coverage); N7 in-water survey; N8 official log book</t>
         </is>
       </c>
+      <c r="V2" s="22" t="inlineStr">
+        <is>
+          <t>25 of 39 mapped families are ready to study; 2 answers independently verified against current authority</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="25" t="n">
@@ -10547,6 +10558,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="V3" s="26" t="inlineStr">
+        <is>
+          <t>13 of 25 mapped families are ready to study; 3 answers independently verified against current authority</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="25" t="n">
@@ -10636,6 +10652,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="V4" s="26" t="inlineStr">
+        <is>
+          <t>25 of 28 mapped families are ready to study</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="25" t="n">
@@ -10725,6 +10746,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="V5" s="26" t="inlineStr">
+        <is>
+          <t>6 of 14 mapped families are ready to study; 2 answers independently verified against current authority</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="25" t="n">
@@ -10814,6 +10840,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="V6" s="26" t="inlineStr">
+        <is>
+          <t>7 of 19 mapped families are ready to study; 1 answer independently verified against current authority</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="25" t="n">
@@ -10903,6 +10934,11 @@
           <t>No Annexure III edge — Class II subject, examined orally anyway</t>
         </is>
       </c>
+      <c r="V7" s="26" t="inlineStr">
+        <is>
+          <t>Every mapped family is ready to study</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="25" t="n">
@@ -10992,6 +11028,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="V8" s="26" t="inlineStr">
+        <is>
+          <t>No longitudinal families mapped yet</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="25" t="n">
@@ -11081,6 +11122,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="V9" s="26" t="inlineStr">
+        <is>
+          <t>3 of 6 mapped families are ready to study; 1 answer independently verified against current authority</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="25" t="n">
@@ -11170,6 +11216,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="V10" s="26" t="inlineStr">
+        <is>
+          <t>No longitudinal families mapped yet</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="25" t="n">
@@ -11259,9 +11310,14 @@
           <t>Supporting-only under official item 12</t>
         </is>
       </c>
+      <c r="V11" s="26" t="inlineStr">
+        <is>
+          <t>No longitudinal families mapped yet</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U11"/>
+  <autoFilter ref="A1:V11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
@@ -11307,7 +11363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11327,6 +11383,15 @@
     <col width="15" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11415,6 +11480,51 @@
           <t>Topic Pack</t>
         </is>
       </c>
+      <c r="R1" s="11" t="inlineStr">
+        <is>
+          <t>QI Families Mapped</t>
+        </is>
+      </c>
+      <c r="S1" s="11" t="inlineStr">
+        <is>
+          <t>Ready To Study Now</t>
+        </is>
+      </c>
+      <c r="T1" s="11" t="inlineStr">
+        <is>
+          <t>Phase-2 Verified Answers</t>
+        </is>
+      </c>
+      <c r="U1" s="11" t="inlineStr">
+        <is>
+          <t>Verify Current Answer</t>
+        </is>
+      </c>
+      <c r="V1" s="11" t="inlineStr">
+        <is>
+          <t>New Answer Required</t>
+        </is>
+      </c>
+      <c r="W1" s="11" t="inlineStr">
+        <is>
+          <t>Modernise Required</t>
+        </is>
+      </c>
+      <c r="X1" s="11" t="inlineStr">
+        <is>
+          <t>Currentness Hold</t>
+        </is>
+      </c>
+      <c r="Y1" s="11" t="inlineStr">
+        <is>
+          <t>Historical Only</t>
+        </is>
+      </c>
+      <c r="Z1" s="11" t="inlineStr">
+        <is>
+          <t>Readiness %</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
@@ -11482,6 +11592,33 @@
           <t>PACK ▸</t>
         </is>
       </c>
+      <c r="R2" s="25" t="n">
+        <v>39</v>
+      </c>
+      <c r="S2" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T2" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="V2" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="25" t="n">
+        <v>64.09999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
@@ -11549,6 +11686,33 @@
           <t>PACK ▸</t>
         </is>
       </c>
+      <c r="R3" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="S3" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="T3" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="V3" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="25" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
@@ -11616,6 +11780,33 @@
           <t>PACK ▸</t>
         </is>
       </c>
+      <c r="R4" s="25" t="n">
+        <v>28</v>
+      </c>
+      <c r="S4" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="25" t="n">
+        <v>89.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
@@ -11683,6 +11874,33 @@
           <t>NOT YET AVAILABLE</t>
         </is>
       </c>
+      <c r="R5" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="S5" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="V5" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="25" t="n">
+        <v>42.9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="25" t="inlineStr">
@@ -11750,6 +11968,33 @@
           <t>NOT YET AVAILABLE</t>
         </is>
       </c>
+      <c r="R6" s="25" t="n">
+        <v>19</v>
+      </c>
+      <c r="S6" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="T6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="V6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="25" t="n">
+        <v>36.8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
@@ -11817,6 +12062,33 @@
           <t>NOT YET AVAILABLE</t>
         </is>
       </c>
+      <c r="R7" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="S7" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="25" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="25" t="inlineStr">
@@ -11884,6 +12156,33 @@
           <t>NOT YET AVAILABLE</t>
         </is>
       </c>
+      <c r="R8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
@@ -11951,6 +12250,33 @@
           <t>NOT YET AVAILABLE</t>
         </is>
       </c>
+      <c r="R9" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="S9" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="25" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
@@ -12018,6 +12344,33 @@
           <t>NOT YET AVAILABLE</t>
         </is>
       </c>
+      <c r="R10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
@@ -12085,9 +12438,36 @@
           <t>NOT YET AVAILABLE</t>
         </is>
       </c>
+      <c r="R11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="25" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q11"/>
+  <autoFilter ref="A1:Z11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId2"/>
@@ -46605,7 +46985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -46805,7 +47185,7 @@
     <row r="16">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>RESERVED FIELDS (populate themselves when the layer is validated)</t>
+          <t>RESERVED FIELDS — these await the HISTORICAL WRITTEN QUESTION CORPUS (ingested 2010–2020 question and answer text), NOT the longitudinal recurrence layer, which is live below</t>
         </is>
       </c>
       <c r="B16" s="26" t="inlineStr"/>
@@ -46936,20 +47316,180 @@
     <row r="27">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>PUBLIC CLAIM (generated, never hand-written)</t>
+          <t>CANONICAL LONGITUDINAL QI — LIVE, and feeding this workbook</t>
         </is>
       </c>
       <c r="B27" s="26" t="inlineStr"/>
       <c r="C27" s="26" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="inlineStr"/>
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
       <c r="B28" s="26" t="inlineStr">
         <is>
+          <t>CANONICAL_LONGITUDINAL_QI</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>Horizon</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>2010 through August 2026</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>Governed families</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n">
+        <v>270</v>
+      </c>
+      <c r="C31" s="26" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>Recurrence-bearing occurrences</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n">
+        <v>1584</v>
+      </c>
+      <c r="C32" s="26" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>Present-day answer decisions (Phase 2)</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" s="26" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>Families ready to study now</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="C34" s="26" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>Answers independently verified against current authority</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="C35" s="26" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>Reaches this workbook via</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="inlineStr">
+        <is>
+          <t>tools/study/study_qi_adapter.py -&gt; docs/study/study_qi.json -&gt; tools/study/qi_projection.py</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>Sheets carrying it</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>ROADMAP (Answer Readiness), TOPIC DETAIL (readiness partition), WRITTEN BY TOPIC (QI Family, 3Y/5Y/10Y/Full, Recurrence Labels, Currentness, Answer Readiness, Phase-2)</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>Why the reserved fields above are still blank</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="inlineStr">
+        <is>
+          <t>They hold per-topic counts of INGESTED historical questions and papers. The 2010-2020 question text is not ingested, so a number there would be invented. The recurrence intelligence above is a different artefact and is live.</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>Why no dated historical claim appears anywhere</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>The 2010-2020 sitting dates are SECONDARY_CLAIMED. Exact counts and family ids stay in this workbook, which is internal. No candidate-facing surface prints a historical count or date; it prints qualitative labels that survive on printed evidence alone. See tools/study/qi_projection.py.</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="26" t="inlineStr"/>
+      <c r="B40" s="26" t="inlineStr"/>
+      <c r="C40" s="26" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>PUBLIC CLAIM (generated, never hand-written)</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="inlineStr"/>
+      <c r="C41" s="26" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="26" t="inlineStr"/>
+      <c r="B42" s="26" t="inlineStr">
+        <is>
           <t>Based on MIW's currently mapped Oral corpus and 360 solved Written questions across 40 papers (2023-01 to 2026-08).</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr"/>
+      <c r="C42" s="26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
+++ b/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
@@ -10466,7 +10466,7 @@
       </c>
       <c r="V2" s="22" t="inlineStr">
         <is>
-          <t>25 of 39 mapped families are ready to study; 2 answers independently verified against current authority</t>
+          <t>26 of 39 mapped families are ready to study; 3 answers independently verified against current authority</t>
         </is>
       </c>
     </row>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="V3" s="26" t="inlineStr">
         <is>
-          <t>13 of 25 mapped families are ready to study; 3 answers independently verified against current authority</t>
+          <t>14 of 25 mapped families are ready to study; 4 answers independently verified against current authority</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="V6" s="26" t="inlineStr">
         <is>
-          <t>7 of 19 mapped families are ready to study; 1 answer independently verified against current authority</t>
+          <t>9 of 19 mapped families are ready to study; 3 answers independently verified against current authority</t>
         </is>
       </c>
     </row>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="V9" s="26" t="inlineStr">
         <is>
-          <t>3 of 6 mapped families are ready to study; 1 answer independently verified against current authority</t>
+          <t>4 of 6 mapped families are ready to study; 2 answers independently verified against current authority</t>
         </is>
       </c>
     </row>
@@ -11596,13 +11596,13 @@
         <v>39</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V2" s="25" t="n">
         <v>0</v>
@@ -11617,7 +11617,7 @@
         <v>0</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>64.09999999999999</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="3">
@@ -11690,13 +11690,13 @@
         <v>25</v>
       </c>
       <c r="S3" s="25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T3" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U3" s="25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V3" s="25" t="n">
         <v>0</v>
@@ -11711,7 +11711,7 @@
         <v>0</v>
       </c>
       <c r="Z3" s="25" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -11972,13 +11972,13 @@
         <v>19</v>
       </c>
       <c r="S6" s="25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T6" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U6" s="25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V6" s="25" t="n">
         <v>0</v>
@@ -11993,7 +11993,7 @@
         <v>0</v>
       </c>
       <c r="Z6" s="25" t="n">
-        <v>36.8</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="7">
@@ -12254,13 +12254,13 @@
         <v>6</v>
       </c>
       <c r="S9" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T9" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" s="25" t="n">
         <v>1</v>
-      </c>
-      <c r="U9" s="25" t="n">
-        <v>3</v>
       </c>
       <c r="V9" s="25" t="n">
         <v>0</v>
@@ -12269,13 +12269,13 @@
         <v>0</v>
       </c>
       <c r="X9" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="25" t="n">
         <v>0</v>
       </c>
       <c r="Z9" s="25" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="10">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="P25" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q25" s="25" t="inlineStr">
@@ -32995,7 +32995,7 @@
       </c>
       <c r="P230" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q230" s="25" t="inlineStr">
@@ -41540,7 +41540,7 @@
       </c>
       <c r="P326" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q326" s="25" t="inlineStr">
@@ -41629,7 +41629,7 @@
       </c>
       <c r="P327" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q327" s="25" t="inlineStr">
@@ -41896,7 +41896,7 @@
       </c>
       <c r="P330" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>CURRENTNESS_HOLD</t>
         </is>
       </c>
       <c r="Q330" s="25" t="inlineStr">
@@ -41985,7 +41985,7 @@
       </c>
       <c r="P331" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>CURRENTNESS_HOLD</t>
         </is>
       </c>
       <c r="Q331" s="25" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="P337" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>CURRENTNESS_HOLD</t>
         </is>
       </c>
       <c r="Q337" s="25" t="inlineStr">
@@ -42786,7 +42786,7 @@
       </c>
       <c r="P340" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>CURRENTNESS_HOLD</t>
         </is>
       </c>
       <c r="Q340" s="25" t="inlineStr">
@@ -43409,7 +43409,7 @@
       </c>
       <c r="P347" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q347" s="25" t="inlineStr">
@@ -47390,7 +47390,7 @@
         </is>
       </c>
       <c r="B33" s="26" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C33" s="26" t="inlineStr"/>
     </row>
@@ -47401,7 +47401,7 @@
         </is>
       </c>
       <c r="B34" s="26" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C34" s="26" t="inlineStr"/>
     </row>
@@ -47412,7 +47412,7 @@
         </is>
       </c>
       <c r="B35" s="26" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C35" s="26" t="inlineStr"/>
     </row>

--- a/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
+++ b/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
@@ -10560,7 +10560,7 @@
       </c>
       <c r="V3" s="26" t="inlineStr">
         <is>
-          <t>14 of 25 mapped families are ready to study; 4 answers independently verified against current authority</t>
+          <t>16 of 25 mapped families are ready to study; 6 answers independently verified against current authority</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="V6" s="26" t="inlineStr">
         <is>
-          <t>9 of 19 mapped families are ready to study; 3 answers independently verified against current authority</t>
+          <t>10 of 19 mapped families are ready to study; 4 answers independently verified against current authority</t>
         </is>
       </c>
     </row>
@@ -11690,13 +11690,13 @@
         <v>25</v>
       </c>
       <c r="S3" s="25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T3" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U3" s="25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V3" s="25" t="n">
         <v>0</v>
@@ -11711,7 +11711,7 @@
         <v>0</v>
       </c>
       <c r="Z3" s="25" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
@@ -11972,13 +11972,13 @@
         <v>19</v>
       </c>
       <c r="S6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" s="25" t="n">
         <v>9</v>
-      </c>
-      <c r="T6" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" s="25" t="n">
-        <v>10</v>
       </c>
       <c r="V6" s="25" t="n">
         <v>0</v>
@@ -11993,7 +11993,7 @@
         <v>0</v>
       </c>
       <c r="Z6" s="25" t="n">
-        <v>47.4</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="7">
@@ -31215,7 +31215,7 @@
       </c>
       <c r="P210" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q210" s="25" t="inlineStr">
@@ -32906,7 +32906,7 @@
       </c>
       <c r="P229" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q229" s="25" t="inlineStr">
@@ -41718,7 +41718,7 @@
       </c>
       <c r="P328" s="25" t="inlineStr">
         <is>
-          <t>VERIFY_CURRENT_ANSWER</t>
+          <t>READY_TO_STUDY_NOW</t>
         </is>
       </c>
       <c r="Q328" s="25" t="inlineStr">
@@ -47390,7 +47390,7 @@
         </is>
       </c>
       <c r="B33" s="26" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C33" s="26" t="inlineStr"/>
     </row>
@@ -47401,7 +47401,7 @@
         </is>
       </c>
       <c r="B34" s="26" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C34" s="26" t="inlineStr"/>
     </row>
@@ -47412,7 +47412,7 @@
         </is>
       </c>
       <c r="B35" s="26" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C35" s="26" t="inlineStr"/>
     </row>

--- a/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
+++ b/docs/study/MIW_MEO_Class1_Study_Roadmap.xlsx
@@ -636,7 +636,7 @@
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Study order #1 of 10, and study order is dependency-first, not priority-first. Prerequisites: —. It unlocks: D02, D03, D04, D05, D06, D07, D08, D09. Priority rank #2 (score 0.6757).</t>
+          <t>Study order #1 of 10, and study order is dependency-first, not priority-first. Prerequisites: —. It unlocks: D02, D03, D04, D05, D06, D07, D08, D09. Priority rank #2 (score 0.6743).</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
         </is>
       </c>
       <c r="F2" s="21" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G2" s="21" t="n">
         <v>71</v>
@@ -10427,7 +10427,7 @@
         <v>2</v>
       </c>
       <c r="N2" s="21" t="n">
-        <v>0.6757</v>
+        <v>0.6743</v>
       </c>
       <c r="O2" s="21" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         </is>
       </c>
       <c r="F3" s="25" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G3" s="25" t="n">
         <v>177</v>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L3" s="25" t="inlineStr">
         <is>
-          <t>STRONG×6, PARTIAL×2</t>
+          <t>STRONG×7, PARTIAL×1</t>
         </is>
       </c>
       <c r="M3" s="25" t="n">
@@ -10589,7 +10589,7 @@
         </is>
       </c>
       <c r="F4" s="25" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G4" s="25" t="n">
         <v>104</v>
@@ -10615,7 +10615,7 @@
         <v>3</v>
       </c>
       <c r="N4" s="25" t="n">
-        <v>0.537</v>
+        <v>0.5389</v>
       </c>
       <c r="O4" s="25" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         </is>
       </c>
       <c r="F5" s="25" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G5" s="25" t="n">
         <v>44</v>
@@ -10709,7 +10709,7 @@
         <v>5</v>
       </c>
       <c r="N5" s="25" t="n">
-        <v>0.2837</v>
+        <v>0.2883</v>
       </c>
       <c r="O5" s="25" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         </is>
       </c>
       <c r="F6" s="25" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G6" s="25" t="n">
         <v>59</v>
@@ -10803,7 +10803,7 @@
         <v>4</v>
       </c>
       <c r="N6" s="25" t="n">
-        <v>0.3416</v>
+        <v>0.3434</v>
       </c>
       <c r="O6" s="25" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         </is>
       </c>
       <c r="F7" s="25" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G7" s="25" t="n">
         <v>94</v>
@@ -10897,7 +10897,7 @@
         <v>6</v>
       </c>
       <c r="N7" s="25" t="n">
-        <v>0.2805</v>
+        <v>0.283</v>
       </c>
       <c r="O7" s="25" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="F8" s="25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="25" t="n">
         <v>18</v>
@@ -10991,7 +10991,7 @@
         <v>7</v>
       </c>
       <c r="N8" s="25" t="n">
-        <v>0.1005</v>
+        <v>0.1007</v>
       </c>
       <c r="O8" s="25" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>8</v>
       </c>
       <c r="N9" s="25" t="n">
-        <v>0.0951</v>
+        <v>0.0949</v>
       </c>
       <c r="O9" s="25" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="F10" s="25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G10" s="25" t="n">
         <v>24</v>
@@ -11179,7 +11179,7 @@
         <v>9</v>
       </c>
       <c r="N10" s="25" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="O10" s="25" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         </is>
       </c>
       <c r="F11" s="25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G11" s="25" t="n">
         <v>21</v>
@@ -11273,7 +11273,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="25" t="n">
-        <v>0.0594</v>
+        <v>0.0607</v>
       </c>
       <c r="O11" s="25" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="C2" s="25" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D2" s="25" t="n">
         <v>71</v>
@@ -11570,7 +11570,7 @@
         </is>
       </c>
       <c r="M2" s="25" t="n">
-        <v>0.6757</v>
+        <v>0.6743</v>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         </is>
       </c>
       <c r="C3" s="25" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D3" s="25" t="n">
         <v>177</v>
@@ -11726,7 +11726,7 @@
         </is>
       </c>
       <c r="C4" s="25" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D4" s="25" t="n">
         <v>104</v>
@@ -11758,7 +11758,7 @@
         </is>
       </c>
       <c r="M4" s="25" t="n">
-        <v>0.537</v>
+        <v>0.5389</v>
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>44</v>
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="M5" s="25" t="n">
-        <v>0.2837</v>
+        <v>0.2883</v>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>59</v>
@@ -11946,7 +11946,7 @@
         </is>
       </c>
       <c r="M6" s="25" t="n">
-        <v>0.3416</v>
+        <v>0.3434</v>
       </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D7" s="25" t="n">
         <v>94</v>
@@ -12040,7 +12040,7 @@
         </is>
       </c>
       <c r="M7" s="25" t="n">
-        <v>0.2805</v>
+        <v>0.283</v>
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>18</v>
@@ -12134,7 +12134,7 @@
         </is>
       </c>
       <c r="M8" s="25" t="n">
-        <v>0.1005</v>
+        <v>0.1007</v>
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="M9" s="25" t="n">
-        <v>0.0951</v>
+        <v>0.0949</v>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D10" s="25" t="n">
         <v>24</v>
@@ -12322,7 +12322,7 @@
         </is>
       </c>
       <c r="M10" s="25" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D11" s="25" t="n">
         <v>21</v>
@@ -12416,7 +12416,7 @@
         </is>
       </c>
       <c r="M11" s="25" t="n">
-        <v>0.0594</v>
+        <v>0.0607</v>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>STRONG</t>
         </is>
       </c>
       <c r="H16" s="26" t="inlineStr">
@@ -46143,7 +46143,7 @@
         </is>
       </c>
       <c r="E2" s="25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="25" t="n">
         <v>69</v>
@@ -46245,7 +46245,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>13</v>
@@ -46313,7 +46313,7 @@
         </is>
       </c>
       <c r="E7" s="25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7" s="25" t="n">
         <v>25</v>
@@ -46483,7 +46483,7 @@
         </is>
       </c>
       <c r="E12" s="25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12" s="25" t="n">
         <v>79</v>
@@ -46517,7 +46517,7 @@
         </is>
       </c>
       <c r="E13" s="25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F13" s="25" t="n">
         <v>43</v>
@@ -46551,7 +46551,7 @@
         </is>
       </c>
       <c r="E14" s="25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" s="25" t="n">
         <v>44</v>
@@ -46615,11 +46615,11 @@
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>STRONG</t>
         </is>
       </c>
       <c r="E16" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="25" t="n">
         <v>18</v>
@@ -46687,7 +46687,7 @@
         </is>
       </c>
       <c r="E18" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="25" t="n">
         <v>7</v>
@@ -46857,7 +46857,7 @@
         </is>
       </c>
       <c r="E23" s="25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F23" s="25" t="n">
         <v>97</v>
@@ -46891,7 +46891,7 @@
         </is>
       </c>
       <c r="E24" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" s="25" t="n">
         <v>22</v>
